--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Neuralink" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="1X" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Positron AI" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Databricks" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Kalshi" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="220">
   <si>
     <t xml:space="preserve">Veligera Capital — Pipeline сделок: расчёт upside</t>
   </si>
@@ -131,7 +133,7 @@
     <t xml:space="preserve">Series E / клиническая стадия (pre-revenue)</t>
   </si>
   <si>
-    <t xml:space="preserve">4–5 лет (IPO 2029–2030, после одобрения Telepathy)</t>
+    <t xml:space="preserve">4–6 лет (IPO 2029–2031, после одобрения Telepathy)</t>
   </si>
   <si>
     <t xml:space="preserve">1X Technologies</t>
@@ -164,7 +166,37 @@
     <t xml:space="preserve">3–4 года (IPO/M&amp;A 2028–2030)</t>
   </si>
   <si>
-    <t xml:space="preserve">Примечание по 1X: формальный индикатив (+10% к Series B янв 2024) — $0.9 млрд, но раунд устарел; расчёт ведётся от альтернативного входа по оценке Series C в процессе ($10 млрд +10% = $11 млрд). См. лист «1X».</t>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данные и ИИ для корпораций (data/AI-платформа)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стратегический раунд $5 млрд, закрыт 13.08.2026; лид Coatue (спрос ~$15 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late-stage / Pre-IPO (IPO не раньше 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 года (IPO 2027–2028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рынки предсказаний / регулируемая биржа событий (США)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series F $1 млрд, закрыт 07.05.2026; лид Coatue (с Sequoia, a16z, IVP, Paradigm, Morgan Stanley, ARK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series F (раунд ~$750 млн по оценке $40 млрд — в переговорах)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–3 года (IPO ~2027, «pre-IPO» раунд уже в переговорах)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примечания: по 1X расчёт ведётся от входа по оценке Series C в процессе ($10 млрд +10% = $11 млрд) — закрытый раунд 01.2024 устарел. По Neuralink вход зафиксирован на уровне вторичного рынка (~$50 млрд) — раунд 06.2025 ($9 млрд) устарел. См. листы компаний.</t>
   </si>
   <si>
     <t xml:space="preserve">Дисклеймер: оценки и upside — модельные оценки на основе публичных данных; не является инвестиционной рекомендацией или офертой. Цены входа индикативны и подтверждаются по запросу.</t>
@@ -467,7 +499,13 @@
     <t xml:space="preserve">• ICE: инвестиции до $2 млрд (окт 2025) + дистрибуция данных</t>
   </si>
   <si>
-    <t xml:space="preserve">Вторичный рынок (авг 2026) имплай-оценка $29–42 млрд после IPO SpaceX; готовится раунд по слухам на $12–15 млрд — фактическая цена входа, вероятно, существенно выше индикатива.</t>
+    <t xml:space="preserve">Вход считается НЕ от раунда: последний раунд ($9 млрд, 06.2025) устарел. Вторичный рынок (авг 2026) оценивает компанию в $29–42 млрд после IPO SpaceX; вход зафиксирован на уровне ~$50 млрд (решение по пайплайну).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ориентир входа: вторичный рынок, $ млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вход (фикс., по вторичному рынку), $ млрд — используется в расчётах ниже</t>
   </si>
   <si>
     <t xml:space="preserve">EV/Revenue 6–10x — платформенная робохирургия</t>
@@ -482,16 +520,22 @@
     <t xml:space="preserve">2031</t>
   </si>
   <si>
-    <t xml:space="preserve">План компании (Bloomberg, июль 2025): $100 млн выручки к 2029, &gt;$500 млн к 2030, ≥$1 млрд и 20 тыс. имплантов/год к 2031; в базе — форвардная выручка 2031.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка готовящегося раунда ($12–15 млрд, середина)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вторичный рынок $29–42 млрд (середина диапазона)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO с «Musk-премией» (шаблон SpaceX)</t>
+    <t xml:space="preserve">2032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">План компании (Bloomberg, июль 2025): $100 млн выручки к 2029, &gt;$500 млн к 2030, ≥$1 млрд и 20 тыс. имплантов/год к 2031; в базе — форвардная выручка ~$1.5 млрд с платформенной премией к мультипликатору.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Остаёмся на уровне вторичного рынка ($42 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2030–31 с «Musk-премией» (шаблон SpaceX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blindsight/речь одобрены, консьюмерская опциональность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Справочно: MOIC (база) от формального входа (+10% к последнему закрытому раунду)</t>
   </si>
   <si>
     <t xml:space="preserve">• Series E $9 млрд: TechCrunch/Semafor, июнь 2025</t>
@@ -536,9 +580,6 @@
     <t xml:space="preserve">Лидер домашнего сегмента гуманоидов</t>
   </si>
   <si>
-    <t xml:space="preserve">Справочно: MOIC (база) от формального входа (+10% к Series B)</t>
-  </si>
-  <si>
     <t xml:space="preserve">• Series B $100 млн: 1x.tech, янв 2024; Series C talks: The Information, сент 2025</t>
   </si>
   <si>
@@ -579,6 +620,75 @@
   </si>
   <si>
     <t xml:space="preserve">• Oracle-контракт: EE Times, апр 2026; TAM инференс-чипов $37 млрд к 2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Последовательность: Series J $10 млрд @ $62 млрд (12.2024) → Series K ~$1 млрд @ &gt;$100 млрд (09.2025) → Series L ~$5 млрд @ $134 млрд (02.2026) → $5 млрд @ $190 млрд (08.2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snowflake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue — прямой аналог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">верх диапазона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MongoDB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">инфраструктура данных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">мегакэп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-rate $7 млрд (Q2 FY, июль 2026), рост &gt;80% г/г с ускорением; положительный adjusted FCF 12 мес. подряд; текущий имплайд ~27x run-rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка остаётся на уровне раунда ($190 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2027–28 со степ-апом к раунду</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ре-рейтинг к Palantir-подобным мультипликаторам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд $5 млрд @ $190 млрд: CNBC, 13.08.2026; пресс-релиз Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Run-rate $7 млрд, &gt;80% г/г: данные компании, Q2 (июль 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Всего привлечено ~$25 млрд (Tracxn); IPO: Ghodsi — не раньше 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В переговорах раунд $750 млн+ по оценке $40 млрд (Sequoia + Wellington; CoinDesk, 13.08.2026) — не закрыт; фактическая цена входа может быть выше индикатива.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">биржа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$1.5 млрд (май 2026) → ~$4 млрд (июль 2026, пик ЧМ по футболу); ~90% рынка США, объёмы $21.1 млрд/мес (июнь).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка остаётся на уровне Series F ($22–24 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка раунда в переговорах ($40 млрд), pre-IPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лидер категории после IPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series F $1 млрд @ $22 млрд: TechCrunch/BusinessWire, 07.05.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд @ $40 млрд в переговорах: CoinDesk, 13.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка 2025 $263.5 млн (89% спорт); run-rate ~$4 млрд к июлю 2026; всего привлечено ~$2.8 млрд (Tracxn)</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1260,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1377,8 +1487,8 @@
         <v>9</v>
       </c>
       <c r="E8" s="6" t="n">
-        <f aca="false">Neuralink!B8</f>
-        <v>9.9</v>
+        <f aca="false">Neuralink!B11</f>
+        <v>50</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>33</v>
@@ -1388,27 +1498,27 @@
       </c>
       <c r="H8" s="6" t="n">
         <f aca="false">Neuralink!B36</f>
-        <v>27.5</v>
+        <v>62.5</v>
       </c>
       <c r="I8" s="8" t="n">
         <f aca="false">Neuralink!B37</f>
-        <v>2.77777777777778</v>
+        <v>1.25</v>
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">Neuralink!B38</f>
-        <v>1.77777777777778</v>
+        <v>0.25</v>
       </c>
       <c r="K8" s="9" t="n">
         <f aca="false">Neuralink!B39</f>
-        <v>0.290994448735806</v>
+        <v>0.0456395525912732</v>
       </c>
       <c r="L8" s="8" t="n">
         <f aca="false">Neuralink!B40</f>
-        <v>0.454545454545455</v>
+        <v>0.2</v>
       </c>
       <c r="M8" s="8" t="n">
         <f aca="false">Neuralink!C40</f>
-        <v>6.06060606060606</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,14 +1619,648 @@
         <v>16.3636363636364</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <f aca="false">Databricks!B6</f>
+        <v>190</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <f aca="false">Databricks!B8</f>
+        <v>209</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <f aca="false">Databricks!B36</f>
+        <v>270</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <f aca="false">Databricks!B37</f>
+        <v>1.29186602870813</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <f aca="false">Databricks!B38</f>
+        <v>0.291866028708134</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <f aca="false">Databricks!B39</f>
+        <v>0.136602845636124</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <f aca="false">Databricks!B40</f>
+        <v>0.861244019138756</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <f aca="false">Databricks!C40</f>
+        <v>2.39234449760766</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <f aca="false">Kalshi!B6</f>
+        <v>22</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <f aca="false">Kalshi!B8</f>
+        <v>24.2</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <f aca="false">Kalshi!B36</f>
+        <v>38</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <f aca="false">Kalshi!B37</f>
+        <v>1.5702479338843</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <f aca="false">Kalshi!B38</f>
+        <v>0.570247933884297</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <f aca="false">Kalshi!B39</f>
+        <v>0.253095341099111</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <f aca="false">Kalshi!B40</f>
+        <v>0.661157024793388</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <f aca="false">Kalshi!C40</f>
+        <v>3.71900826446281</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <f aca="false">B6*(1+B7)</f>
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>46</v>
+      <c r="A13" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <f aca="false">D23*E23</f>
+        <v>16</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <f aca="false">F23/B8</f>
+        <v>0.661157024793388</v>
+      </c>
+      <c r="H23" s="30" t="n">
+        <f aca="false">G23-1</f>
+        <v>-0.338842975206612</v>
+      </c>
+      <c r="I23" s="30" t="n">
+        <f aca="false">G23^(1/C23)-1</f>
+        <v>-0.186884371818258</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <f aca="false">D24*E24</f>
+        <v>36</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <f aca="false">F24/B8</f>
+        <v>1.48760330578512</v>
+      </c>
+      <c r="H24" s="30" t="n">
+        <f aca="false">G24-1</f>
+        <v>0.487603305785124</v>
+      </c>
+      <c r="I24" s="30" t="n">
+        <f aca="false">G24^(1/C24)-1</f>
+        <v>0.219673442272613</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <f aca="false">D25*E25</f>
+        <v>90</v>
+      </c>
+      <c r="G25" s="29" t="n">
+        <f aca="false">F25/B8</f>
+        <v>3.71900826446281</v>
+      </c>
+      <c r="H25" s="30" t="n">
+        <f aca="false">G25-1</f>
+        <v>2.71900826446281</v>
+      </c>
+      <c r="I25" s="30" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>0.388694725128484</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <f aca="false">E30/B8</f>
+        <v>0.991735537190083</v>
+      </c>
+      <c r="G30" s="30" t="n">
+        <f aca="false">F30-1</f>
+        <v>-0.00826446280991744</v>
+      </c>
+      <c r="H30" s="30" t="n">
+        <f aca="false">F30^(1/C30)-1</f>
+        <v>-0.00414080453606169</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31" s="29" t="n">
+        <f aca="false">E31/B8</f>
+        <v>1.65289256198347</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <f aca="false">F31-1</f>
+        <v>0.652892561983471</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <f aca="false">F31^(1/C31)-1</f>
+        <v>0.28564869306645</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <f aca="false">E32/B8</f>
+        <v>3.30578512396694</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <f aca="false">F32-1</f>
+        <v>2.30578512396694</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.348399724926484</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="18" t="n">
+        <f aca="false">AVERAGE(F24,E31)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="31" t="n">
+        <f aca="false">B36/B8</f>
+        <v>1.5702479338843</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="32" t="n">
+        <f aca="false">B37-1</f>
+        <v>0.570247933884297</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="32" t="n">
+        <f aca="false">B37^(1/C24)-1</f>
+        <v>0.253095341099111</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="31" t="n">
+        <f aca="false">MIN(G23,F30)</f>
+        <v>0.661157024793388</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <f aca="false">MAX(G25,F32)</f>
+        <v>3.71900826446281</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1544,63 +2288,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1641,7 +2385,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1670,7 +2414,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.1</v>
@@ -1678,7 +2422,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -1687,10 +2431,10 @@
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1701,7 +2445,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -1717,70 +2461,70 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>10.5</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>24.7</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>9.4</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>7</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>61</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -1793,39 +2537,39 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>1.5</v>
@@ -1855,10 +2599,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>1.5</v>
@@ -1888,10 +2632,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>2.5</v>
@@ -1921,12 +2665,12 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -1939,42 +2683,42 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>1000</v>
@@ -1994,16 +2738,16 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>1200</v>
@@ -2023,16 +2767,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>1800</v>
@@ -2052,7 +2796,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2065,12 +2809,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">AVERAGE(F24,E31)</f>
@@ -2106,7 +2850,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B40" s="31" t="n">
         <f aca="false">MIN(G23,F30)</f>
@@ -2119,7 +2863,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2132,22 +2876,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2188,7 +2932,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2217,7 +2961,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.1</v>
@@ -2225,7 +2969,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -2234,10 +2978,10 @@
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2248,7 +2992,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2264,70 +3008,70 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>15</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>15.7</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>7.3</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>6.3</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>2.6</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2340,39 +3084,39 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>2.5</v>
@@ -2402,10 +3146,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>2.5</v>
@@ -2435,10 +3179,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>3.5</v>
@@ -2468,12 +3212,12 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2486,42 +3230,42 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>35</v>
@@ -2541,16 +3285,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>70</v>
@@ -2570,16 +3314,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>3.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>150</v>
@@ -2599,7 +3343,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2612,12 +3356,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">AVERAGE(F24,E31)</f>
@@ -2653,7 +3397,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B40" s="31" t="n">
         <f aca="false">MIN(G23,F30)</f>
@@ -2666,7 +3410,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2679,22 +3423,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2735,7 +3479,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2764,7 +3508,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.1</v>
@@ -2772,7 +3516,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -2781,10 +3525,10 @@
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2795,7 +3539,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2811,70 +3555,70 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>20.7</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>17</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>9</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>5.9</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>2.1</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2887,39 +3631,39 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>2.5</v>
@@ -2949,10 +3693,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>2.5</v>
@@ -2982,10 +3726,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>4</v>
@@ -3015,12 +3759,12 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -3033,42 +3777,42 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>20</v>
@@ -3088,16 +3832,16 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>40</v>
@@ -3117,16 +3861,16 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>80</v>
@@ -3146,7 +3890,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -3159,12 +3903,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">AVERAGE(F24,E31)</f>
@@ -3200,7 +3944,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B40" s="31" t="n">
         <f aca="false">MIN(G23,F30)</f>
@@ -3213,7 +3957,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3226,22 +3970,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3282,7 +4026,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3311,7 +4055,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.1</v>
@@ -3319,7 +4063,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -3328,21 +4072,32 @@
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
+      <c r="A10" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
+      <c r="A11" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="18" t="n">
+        <f aca="false">B10</f>
+        <v>50</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3358,37 +4113,37 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3401,140 +4156,140 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F23" s="28" t="n">
         <f aca="false">D23*E23</f>
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="G23" s="29" t="n">
-        <f aca="false">F23/B8</f>
-        <v>0.454545454545455</v>
+        <f aca="false">F23/B11</f>
+        <v>0.2</v>
       </c>
       <c r="H23" s="30" t="n">
         <f aca="false">G23-1</f>
-        <v>-0.545454545454545</v>
+        <v>-0.8</v>
       </c>
       <c r="I23" s="30" t="n">
         <f aca="false">G23^(1/C23)-1</f>
-        <v>-0.178903256331361</v>
+        <v>-0.331259695023578</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F24" s="28" t="n">
         <f aca="false">D24*E24</f>
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G24" s="29" t="n">
-        <f aca="false">F24/B8</f>
-        <v>2.02020202020202</v>
+        <f aca="false">F24/B11</f>
+        <v>0.9</v>
       </c>
       <c r="H24" s="30" t="n">
         <f aca="false">G24-1</f>
-        <v>1.02020202020202</v>
+        <v>-0.1</v>
       </c>
       <c r="I24" s="30" t="n">
         <f aca="false">G24^(1/C24)-1</f>
-        <v>0.19219885465362</v>
+        <v>-0.0208516376390232</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="26" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F25" s="28" t="n">
         <f aca="false">D25*E25</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="G25" s="29" t="n">
-        <f aca="false">F25/B8</f>
-        <v>4.54545454545455</v>
+        <f aca="false">F25/B11</f>
+        <v>2.4</v>
       </c>
       <c r="H25" s="30" t="n">
         <f aca="false">G25-1</f>
-        <v>3.54545454545455</v>
+        <v>1.4</v>
       </c>
       <c r="I25" s="30" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.353678289961735</v>
+        <v>0.157093730068718</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -3547,120 +4302,120 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="F30" s="29" t="n">
-        <f aca="false">E30/B8</f>
-        <v>1.36363636363636</v>
+        <f aca="false">E30/B11</f>
+        <v>0.84</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">F30-1</f>
-        <v>0.363636363636364</v>
+        <v>-0.16</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">F30^(1/C30)-1</f>
-        <v>0.0806240864622092</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-0.0426520282618405</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F31" s="29" t="n">
-        <f aca="false">E31/B8</f>
-        <v>3.53535353535354</v>
+        <f aca="false">E31/B11</f>
+        <v>1.6</v>
       </c>
       <c r="G31" s="30" t="n">
         <f aca="false">F31-1</f>
-        <v>2.53535353535354</v>
+        <v>0.6</v>
       </c>
       <c r="H31" s="30" t="n">
         <f aca="false">F31^(1/C31)-1</f>
-        <v>0.371223389067546</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0985605433061179</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B32" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="C32" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" s="26" t="n">
-        <v>60</v>
-      </c>
       <c r="F32" s="29" t="n">
-        <f aca="false">E32/B8</f>
-        <v>6.06060606060606</v>
+        <f aca="false">E32/B11</f>
+        <v>3</v>
       </c>
       <c r="G32" s="30" t="n">
         <f aca="false">F32-1</f>
-        <v>5.06060606060606</v>
+        <v>2</v>
       </c>
       <c r="H32" s="30" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.433848317837657</v>
+        <v>0.200936955176003</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -3673,16 +4428,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">AVERAGE(F24,E31)</f>
-        <v>27.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3690,8 +4445,8 @@
         <v>10</v>
       </c>
       <c r="B37" s="31" t="n">
-        <f aca="false">B36/B8</f>
-        <v>2.77777777777778</v>
+        <f aca="false">B36/B11</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3700,7 +4455,7 @@
       </c>
       <c r="B38" s="32" t="n">
         <f aca="false">B37-1</f>
-        <v>1.77777777777778</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3709,25 +4464,34 @@
       </c>
       <c r="B39" s="32" t="n">
         <f aca="false">B37^(1/C24)-1</f>
-        <v>0.290994448735806</v>
+        <v>0.0456395525912732</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B40" s="31" t="n">
         <f aca="false">MIN(G23,F30)</f>
-        <v>0.454545454545455</v>
+        <v>0.2</v>
       </c>
       <c r="C40" s="31" t="n">
         <f aca="false">MAX(G25,F32)</f>
-        <v>6.06060606060606</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" s="31" t="n">
+        <f aca="false">B36/B8</f>
+        <v>6.31313131313131</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3740,22 +4504,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3796,7 +4560,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3825,7 +4589,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.1</v>
@@ -3833,7 +4597,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -3842,15 +4606,15 @@
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>10</v>
@@ -3858,7 +4622,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">B10*(1+B7)</f>
@@ -3867,7 +4631,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3883,48 +4647,48 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>15</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>16.8</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3937,39 +4701,39 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>4</v>
@@ -3999,10 +4763,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>4</v>
@@ -4032,10 +4796,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>5</v>
@@ -4065,12 +4829,12 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -4083,42 +4847,42 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>10</v>
@@ -4138,16 +4902,16 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>25</v>
@@ -4167,16 +4931,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>60</v>
@@ -4196,7 +4960,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -4209,12 +4973,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">AVERAGE(F24,E31)</f>
@@ -4250,7 +5014,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B40" s="31" t="n">
         <f aca="false">MIN(G23,F30)</f>
@@ -4263,7 +5027,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B41" s="31" t="n">
         <f aca="false">B36/B8</f>
@@ -4272,7 +5036,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4285,22 +5049,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -4341,7 +5105,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4370,7 +5134,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.1</v>
@@ -4378,7 +5142,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">B6*(1+B7)</f>
@@ -4387,10 +5151,10 @@
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4401,7 +5165,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4417,59 +5181,59 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>20.6</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>24.5</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>18</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>16.9</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -4482,39 +5246,39 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>3</v>
@@ -4544,10 +5308,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>3</v>
@@ -4577,10 +5341,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>4</v>
@@ -4610,12 +5374,12 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -4628,42 +5392,42 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>3.5</v>
@@ -4683,16 +5447,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>8</v>
@@ -4712,16 +5476,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E32" s="26" t="n">
         <v>15</v>
@@ -4741,7 +5505,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -4754,12 +5518,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">AVERAGE(F24,E31)</f>
@@ -4795,7 +5559,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B40" s="31" t="n">
         <f aca="false">MIN(G23,F30)</f>
@@ -4808,7 +5572,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4821,22 +5585,558 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <f aca="false">B6*(1+B7)</f>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <f aca="false">D23*E23</f>
+        <v>180</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <f aca="false">F23/B8</f>
+        <v>0.861244019138756</v>
+      </c>
+      <c r="H23" s="30" t="n">
+        <f aca="false">G23-1</f>
+        <v>-0.138755980861244</v>
+      </c>
+      <c r="I23" s="30" t="n">
+        <f aca="false">G23^(1/C23)-1</f>
+        <v>-0.0719676626653811</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <f aca="false">D24*E24</f>
+        <v>280</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <f aca="false">F24/B8</f>
+        <v>1.33971291866029</v>
+      </c>
+      <c r="H24" s="30" t="n">
+        <f aca="false">G24-1</f>
+        <v>0.339712918660287</v>
+      </c>
+      <c r="I24" s="30" t="n">
+        <f aca="false">G24^(1/C24)-1</f>
+        <v>0.157459683384388</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <f aca="false">D25*E25</f>
+        <v>500</v>
+      </c>
+      <c r="G25" s="29" t="n">
+        <f aca="false">F25/B8</f>
+        <v>2.39234449760766</v>
+      </c>
+      <c r="H25" s="30" t="n">
+        <f aca="false">G25-1</f>
+        <v>1.39234449760766</v>
+      </c>
+      <c r="I25" s="30" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>0.337440815638592</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>190</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <f aca="false">E30/B8</f>
+        <v>0.909090909090909</v>
+      </c>
+      <c r="G30" s="30" t="n">
+        <f aca="false">F30-1</f>
+        <v>-0.0909090909090911</v>
+      </c>
+      <c r="H30" s="30" t="n">
+        <f aca="false">F30^(1/C30)-1</f>
+        <v>-0.0465374107544078</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>260</v>
+      </c>
+      <c r="F31" s="29" t="n">
+        <f aca="false">E31/B8</f>
+        <v>1.24401913875598</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <f aca="false">F31-1</f>
+        <v>0.244019138755981</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <f aca="false">F31^(1/C31)-1</f>
+        <v>0.115356059182888</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <f aca="false">E32/B8</f>
+        <v>1.91387559808612</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <f aca="false">F32-1</f>
+        <v>0.913875598086124</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.241570071097211</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="18" t="n">
+        <f aca="false">AVERAGE(F24,E31)</f>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="31" t="n">
+        <f aca="false">B36/B8</f>
+        <v>1.29186602870813</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="32" t="n">
+        <f aca="false">B37-1</f>
+        <v>0.291866028708134</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="32" t="n">
+        <f aca="false">B37^(1/C24)-1</f>
+        <v>0.136602845636124</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="31" t="n">
+        <f aca="false">MIN(G23,F30)</f>
+        <v>0.861244019138756</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <f aca="false">MAX(G25,F32)</f>
+        <v>2.39234449760766</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Домашние роботы-помощники</t>
   </si>
   <si>
-    <t xml:space="preserve">Series B $100 млн, закрыт в январе 2024; лид EQT Ventures (оценка $0.82 млрд)</t>
+    <t xml:space="preserve">Series C, до $1 млрд, в процессе — оценка $10+ млрд (предыдущий закрытый: Series B $100 млн, январь 2024, лид EQT Ventures)</t>
   </si>
   <si>
     <t xml:space="preserve">4–5 лет (IPO ~2030)</t>
@@ -348,7 +348,7 @@
     <t xml:space="preserve">IPO по нижней границе: $1 трлн («ниже $1 трлн — nonstarter», С. Альтман)</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO 2026–27 при $1.2–1.4 трлн + пост-IPO ре-рейтинг</t>
+    <t xml:space="preserve">IPO 2026–27 в диапазоне $1.5–1.6 трлн</t>
   </si>
   <si>
     <t xml:space="preserve">Траектория крупнейшей публичной компании мира</t>
@@ -441,126 +441,126 @@
     <t xml:space="preserve">• TAM: Goldman Sachs $38 млрд к 2035; Morgan Stanley $5 трлн к 2050</t>
   </si>
   <si>
+    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Оценка идущего Series C — $10+ млрд (The Information); Nasdaq Private Market ~$662/акция (31.07.2026). Закрытый Series B (01.2024, $0.82 млрд) устарел и в расчёте не используется.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iRobot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">предостерегающий комп: консьюмер-железо без ИИ-рва</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 250–400 тыс. штук к 2030 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $4–6 млрд (целевой сценарий — $5 млрд).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка на уровне идущего Series C ($10 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Паритет с текущей оценкой Figure AI при лидерстве в домашнем сегменте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Массовое проникновение домашних роботов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series B $100 млн: 1x.tech, январь 2024; Series C в процессе: The Information, сентябрь 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• NEO: 10 тыс.+ предзаказов за 5 дней (бэклог &gt;$200 млн); производство в Hayward, CA с апреля 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• EQT: контракт до 10 тыс. роботов для портфельных компаний 2026–2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Bloomberg/CNBC (04.08.2026): раунд ~$1 млрд по оценке &gt;$20 млрд в переговорах — вторичные сделки идут с премией к апрельской отметке.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robinhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CME Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">биржевой оператор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–10x, стратегический акционер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">крипто-биржа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DraftKings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">беттинг — нижняя граница</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized-выручка &gt;$1 млрд уже через 6 недель после запуска биржи в США. Bernstein: объёмы отрасли $1 трлн к 2030; при доле ~30% и комиссии ~2% выручка Polymarket выходит на $6 млрд.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка идущего раунда (&gt;$20 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Паритет с Kalshi по обороту + премия за глобальный рынок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ре-рейтинг категории до биржевой инфраструктуры (CME/ICE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд $15 млрд: Bloomberg 20.04.2026; раунд &gt;$20 млрд в переговорах: Bloomberg/CNBC 04.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка &gt;$1 млрд annualized: CNBC, 26.06.2026; обороты ~$9–10.5 млрд/мес</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ICE: инвестиции до $2 млрд (окт 2025) + дистрибуция данных; партнёрство с X/xAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Фактические сделки на вторичном рынке идут около $35 млрд: рынок уже отыгрывает раунд по оценке $40 млрд, который обсуждают Sequoia и Wellington (CoinDesk, 13.08.2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">биржа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026. ~90% рынка США и обороты $21 млрд/мес; целевой сценарий — $8 млрд выручки к 2029 при сохранении доли.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка идущего раунда ($40 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO ~2027–28 при мультипликаторах биржевых операторов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Категория выходит на объёмы $1.5 трлн (Macquarie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series F $1 млрд @ $22 млрд: TechCrunch/BusinessWire, 07.05.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд @ $40 млрд в переговорах: CoinDesk, 13.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка 2025 $263.5 млн, run-rate ~$4 млрд (июль 2026); всего привлечено ~$2.8 млрд</t>
+  </si>
+  <si>
     <t xml:space="preserve">База для вторичного рынка, $ млрд (оценка идущего раунда)</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке идущего раунда (закрытый раунд устарел). Раунд Series C в процессе по оценке $10+ млрд (The Information); Nasdaq Private Market ~$662/акция (31.07.2026). Раунд января 2024 устарел — цена определяется вторичным рынком и Series C.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iRobot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">предостерегающий комп: консьюмер-железо без ИИ-рва</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 250–400 тыс. штук к 2030 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $4–6 млрд (целевой сценарий — $5 млрд).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка на уровне идущего Series C ($10 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Паритет с текущей оценкой Figure AI при лидерстве в домашнем сегменте</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Массовое проникновение домашних роботов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Series B $100 млн: 1x.tech, январь 2024; Series C в процессе: The Information, сентябрь 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• NEO: 10 тыс.+ предзаказов за 5 дней (бэклог &gt;$200 млн); производство в Hayward, CA с апреля 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• EQT: контракт до 10 тыс. роботов для портфельных компаний 2026–2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Bloomberg/CNBC (04.08.2026): раунд ~$1 млрд по оценке &gt;$20 млрд в переговорах — вторичные сделки идут с премией к апрельской отметке.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robinhood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV/Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CME Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">биржевой оператор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8–10x, стратегический акционер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coinbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">крипто-биржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DraftKings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">беттинг — нижняя граница</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annualized-выручка &gt;$1 млрд уже через 6 недель после запуска биржи в США. Bernstein: объёмы отрасли $1 трлн к 2030; при доле ~30% и комиссии ~2% выручка Polymarket выходит на $6 млрд.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка идущего раунда (&gt;$20 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Паритет с Kalshi по обороту + премия за глобальный рынок</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ре-рейтинг категории до биржевой инфраструктуры (CME/ICE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Раунд $15 млрд: Bloomberg 20.04.2026; раунд &gt;$20 млрд в переговорах: Bloomberg/CNBC 04.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Выручка &gt;$1 млрд annualized: CNBC, 26.06.2026; обороты ~$9–10.5 млрд/мес</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• ICE: инвестиции до $2 млрд (окт 2025) + дистрибуция данных; партнёрство с X/xAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. CoinDesk (13.08.2026): Sequoia и Wellington обсуждают раунд $750 млн+ по оценке $40 млрд — вторичный рынок идёт между Series F и этой отметкой.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">биржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026. ~90% рынка США и обороты $21 млрд/мес; целевой сценарий — $8 млрд выручки к 2029 при сохранении доли.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка идущего раунда ($40 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO ~2027–28 при мультипликаторах биржевых операторов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Категория выходит на объёмы $1.5 трлн (Macquarie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Series F $1 млрд @ $22 млрд: TechCrunch/BusinessWire, 07.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Раунд @ $40 млрд в переговорах: CoinDesk, 13.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Выручка 2025 $263.5 млн, run-rate ~$4 млрд (июль 2026); всего привлечено ~$2.8 млрд</t>
-  </si>
-  <si>
     <t xml:space="preserve">Диапазон = премия 8–15% к оценке идущего раунда (закрытый раунд устарел). Bloomberg (08.07.2026): раунд ~$750 млн двумя траншами по оценкам ~$3.5 и ~$5 млрд. Бумага торгуется на Forge/Caplight — цена уже кратно выше Series B.</t>
   </si>
   <si>
@@ -579,7 +579,7 @@
     <t xml:space="preserve">Оценка верхнего транша идущего раунда ($5 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">Путь Cerebras: IPO при выручке $1.5 млрд+ или продажа стратегу (Arm в капитале)</t>
+    <t xml:space="preserve">Путь Cerebras: IPO при выручке $1 млрд+ или продажа стратегу (Arm в капитале)</t>
   </si>
   <si>
     <t xml:space="preserve">Закрепление доли в инференсе против Nvidia</t>
@@ -1310,19 +1310,19 @@
       </c>
       <c r="J5" s="6" t="n">
         <f aca="false">OpenAI!B36</f>
-        <v>1850</v>
+        <v>1600</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">OpenAI!B37</f>
-        <v>1.94740941914567</v>
+        <v>1.68424598412598</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">OpenAI!B38</f>
-        <v>0.947409419145666</v>
+        <v>0.684245984125982</v>
       </c>
       <c r="M5" s="9" t="n">
         <f aca="false">OpenAI!B39</f>
-        <v>0.39549611935887</v>
+        <v>0.297785030013053</v>
       </c>
       <c r="N5" s="8" t="n">
         <f aca="false">OpenAI!B40</f>
@@ -1368,19 +1368,19 @@
       </c>
       <c r="J6" s="6" t="n">
         <f aca="false">'Figure AI'!B36</f>
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6" s="8" t="n">
         <f aca="false">'Figure AI'!B37</f>
-        <v>2.75957226629872</v>
+        <v>2.29964355524894</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">'Figure AI'!B38</f>
-        <v>1.75957226629872</v>
+        <v>1.29964355524894</v>
       </c>
       <c r="M6" s="9" t="n">
         <f aca="false">'Figure AI'!B39</f>
-        <v>0.402643350537443</v>
+        <v>0.319937928526136</v>
       </c>
       <c r="N6" s="8" t="n">
         <f aca="false">'Figure AI'!B40</f>
@@ -1391,7 +1391,7 @@
         <v>4.9672300793377</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D7" s="6" t="n">
         <f aca="false">1X!B6</f>
-        <v>0.82</v>
+        <v>10</v>
       </c>
       <c r="E7" s="6" t="n">
         <f aca="false">1X!B7</f>
@@ -1484,19 +1484,19 @@
       </c>
       <c r="J8" s="6" t="n">
         <f aca="false">Polymarket!B36</f>
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K8" s="8" t="n">
         <f aca="false">Polymarket!B37</f>
-        <v>5.38116591928251</v>
+        <v>2.98953662182362</v>
       </c>
       <c r="L8" s="9" t="n">
         <f aca="false">Polymarket!B38</f>
-        <v>4.38116591928251</v>
+        <v>1.98953662182362</v>
       </c>
       <c r="M8" s="9" t="n">
         <f aca="false">Polymarket!B39</f>
-        <v>0.752368593443366</v>
+        <v>0.440570861275843</v>
       </c>
       <c r="N8" s="8" t="n">
         <f aca="false">Polymarket!B40</f>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="O8" s="8" t="n">
         <f aca="false">Polymarket!C40</f>
-        <v>10.762331838565</v>
+        <v>6.45739910313901</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1527,42 +1527,42 @@
       </c>
       <c r="F9" s="6" t="n">
         <f aca="false">Kalshi!B10</f>
-        <v>23.76</v>
+        <v>30</v>
       </c>
       <c r="G9" s="6" t="n">
         <f aca="false">Kalshi!B11</f>
-        <v>25.3</v>
+        <v>40</v>
       </c>
       <c r="H9" s="6" t="n">
         <f aca="false">Kalshi!B12</f>
-        <v>24.53</v>
+        <v>35</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">Kalshi!B36</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K9" s="8" t="n">
         <f aca="false">Kalshi!B37</f>
-        <v>4.89196901752956</v>
+        <v>3.57142857142857</v>
       </c>
       <c r="L9" s="9" t="n">
         <f aca="false">Kalshi!B38</f>
-        <v>3.89196901752956</v>
+        <v>2.57142857142857</v>
       </c>
       <c r="M9" s="9" t="n">
         <f aca="false">Kalshi!B39</f>
-        <v>0.887093762487619</v>
+        <v>0.663936649275048</v>
       </c>
       <c r="N9" s="8" t="n">
         <f aca="false">Kalshi!B40</f>
-        <v>1.63065633917652</v>
+        <v>1.14285714285714</v>
       </c>
       <c r="O9" s="8" t="n">
         <f aca="false">Kalshi!C40</f>
-        <v>9.1316754993885</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1600,19 +1600,19 @@
       </c>
       <c r="J10" s="6" t="n">
         <f aca="false">'Positron AI'!B36</f>
-        <v>31.3</v>
+        <v>20</v>
       </c>
       <c r="K10" s="8" t="n">
         <f aca="false">'Positron AI'!B37</f>
-        <v>8.02049967969251</v>
+        <v>5.1249199231262</v>
       </c>
       <c r="L10" s="9" t="n">
         <f aca="false">'Positron AI'!B38</f>
-        <v>7.02049967969251</v>
+        <v>4.1249199231262</v>
       </c>
       <c r="M10" s="9" t="n">
         <f aca="false">'Positron AI'!B39</f>
-        <v>1.00170684955895</v>
+        <v>0.724099640552506</v>
       </c>
       <c r="N10" s="8" t="n">
         <f aca="false">'Positron AI'!B40</f>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O10" s="8" t="n">
         <f aca="false">'Positron AI'!C40</f>
-        <v>17.9372197309417</v>
+        <v>10.2498398462524</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="J11" s="6" t="n">
         <f aca="false">Databricks!B36</f>
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="K11" s="8" t="n">
         <f aca="false">Databricks!B37</f>
-        <v>1.88812839273071</v>
+        <v>2.07694123200378</v>
       </c>
       <c r="L11" s="9" t="n">
         <f aca="false">Databricks!B38</f>
-        <v>0.888128392730706</v>
+        <v>1.07694123200378</v>
       </c>
       <c r="M11" s="9" t="n">
         <f aca="false">Databricks!B39</f>
-        <v>0.374091842902324</v>
+        <v>0.441159683034388</v>
       </c>
       <c r="N11" s="8" t="n">
         <f aca="false">Databricks!B40</f>
@@ -2083,23 +2083,23 @@
         <v>110</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>2200</v>
+        <v>1650</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.31583822817322</v>
+        <v>1.73687867112992</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.31583822817322</v>
+        <v>0.736878671129918</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.521787839409037</v>
+        <v>0.31790692809846</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2208,7 +2208,7 @@
         <v>0.0348014419921376</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
         <v>99</v>
       </c>
@@ -2222,19 +2222,19 @@
         <v>106</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>1.57898061011811</v>
+        <v>1.63161329712204</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>0.578980610118108</v>
+        <v>0.631613297122045</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.256574952049462</v>
+        <v>0.277346193137179</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>1850</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>1.94740941914567</v>
+        <v>1.68424598412598</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>0.947409419145666</v>
+        <v>0.684245984125982</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.39549611935887</v>
+        <v>0.297785030013053</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>1.88814043682384</v>
+        <v>1.63298632373954</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2659,26 +2659,26 @@
         <v>3</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.75957226629872</v>
+        <v>2.41462573301138</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.75957226629872</v>
+        <v>1.41462573301138</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.402643350537443</v>
+        <v>0.341580101775709</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2801,19 +2801,19 @@
         <v>132</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.75957226629872</v>
+        <v>2.18466137748649</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.75957226629872</v>
+        <v>1.18466137748649</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.402643350537443</v>
+        <v>0.297561776477154</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.75957226629872</v>
+        <v>2.29964355524894</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.75957226629872</v>
+        <v>1.29964355524894</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.402643350537443</v>
+        <v>0.319937928526136</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.67558528428094</v>
+        <v>2.22965440356745</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3011,12 +3011,12 @@
         <v>67</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>0.82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -3070,7 +3070,7 @@
         <v>74</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3121,13 +3121,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3177,7 +3177,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>4</v>
@@ -3210,7 +3210,7 @@
         <v>99</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>4</v>
@@ -3243,7 +3243,7 @@
         <v>101</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>5</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3320,13 +3320,13 @@
         <v>97</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>4</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -3349,13 +3349,13 @@
         <v>99</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>4</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>60</v>
@@ -3378,13 +3378,13 @@
         <v>101</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>110</v>
@@ -3488,17 +3488,17 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3627,7 +3627,7 @@
         <v>74</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3656,57 +3656,57 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3795,26 +3795,26 @@
         <v>3</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>90</v>
+        <v>52.5</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>5.38116591928251</v>
+        <v>3.1390134529148</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>4.38116591928251</v>
+        <v>2.1390134529148</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.752368593443366</v>
+        <v>0.464190975134403</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3822,37 +3822,37 @@
         <v>101</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>18</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>10.762331838565</v>
+        <v>6.45739910313901</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>9.76233183856502</v>
+        <v>5.45739910313901</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.811242477108697</v>
+        <v>0.594095762282103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3905,7 +3905,7 @@
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
@@ -3934,22 +3934,22 @@
         <v>3</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>90</v>
+        <v>47.5</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>5.38116591928251</v>
+        <v>2.84005979073244</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>4.38116591928251</v>
+        <v>1.84005979073244</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.752368593443366</v>
+        <v>0.416149688179292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3957,28 +3957,28 @@
         <v>101</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>8.96860986547085</v>
+        <v>5.97907324364723</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>7.96860986547085</v>
+        <v>4.97907324364723</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.730538569687887</v>
+        <v>0.56371811889409</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>5.38116591928251</v>
+        <v>2.98953662182362</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>4.38116591928251</v>
+        <v>1.98953662182362</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.752368593443366</v>
+        <v>0.440570861275843</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>10.762331838565</v>
+        <v>6.45739910313901</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>5.21739130434783</v>
+        <v>2.89855072463768</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4067,17 +4067,17 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4178,18 +4178,16 @@
       <c r="A10" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>23.76</v>
+      <c r="B10" s="15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>25.3</v>
+      <c r="B11" s="15" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4198,7 +4196,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>24.53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4206,7 +4204,7 @@
         <v>74</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4235,46 +4233,46 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4341,15 +4339,15 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>2.44598450876478</v>
+        <v>1.71428571428571</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>1.44598450876478</v>
+        <v>0.714285714285714</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.563964356615833</v>
+        <v>0.309307341415954</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4374,15 +4372,15 @@
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>4.89196901752956</v>
+        <v>3.42857142857143</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>3.89196901752956</v>
+        <v>2.42857142857143</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.887093762487619</v>
+        <v>0.636987189097755</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4390,7 +4388,7 @@
         <v>101</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -4407,20 +4405,20 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>9.1316754993885</v>
+        <v>6.4</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>8.1316754993885</v>
+        <v>5.4</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.881234745963403</v>
+        <v>0.699562481967873</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4473,22 +4471,22 @@
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>40</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.63065633917652</v>
+        <v>1.14285714285714</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.630656339176519</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.276971549869659</v>
+        <v>0.0690449676496976</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4502,22 +4500,22 @@
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>4.89196901752956</v>
+        <v>3.71428571428571</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>3.89196901752956</v>
+        <v>2.71428571428571</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.887093762487619</v>
+        <v>0.690246803060484</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4525,28 +4523,28 @@
         <v>101</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>200</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>8.15328169588259</v>
+        <v>5.71428571428571</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>7.15328169588259</v>
+        <v>4.71428571428571</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.821296694030952</v>
+        <v>0.645412693099038</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4568,7 +4566,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4577,7 +4575,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>4.89196901752956</v>
+        <v>3.57142857142857</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4586,7 +4584,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>3.89196901752956</v>
+        <v>2.57142857142857</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4595,7 +4593,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.887093762487619</v>
+        <v>0.663936649275048</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4604,11 +4602,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.63065633917652</v>
+        <v>1.14285714285714</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>9.1316754993885</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4617,7 +4615,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>4.74308300395257</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4635,17 +4633,17 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4720,7 +4718,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>3.5</v>
@@ -4809,7 +4807,7 @@
         <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4820,7 +4818,7 @@
         <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4831,7 +4829,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4842,7 +4840,7 @@
         <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4931,26 +4929,26 @@
         <v>3</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>30.6</v>
+        <v>19.2</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>7.84112748238309</v>
+        <v>4.91992312620115</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>6.84112748238309</v>
+        <v>3.91992312620115</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.986672003074689</v>
+        <v>0.700798140351766</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4958,32 +4956,32 @@
         <v>101</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>17.9372197309417</v>
+        <v>9.22485586162716</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>16.9372197309417</v>
+        <v>8.22485586162716</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>1.05796877985947</v>
+        <v>0.742769285165229</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5073,19 +5071,19 @@
         <v>183</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>32</v>
+        <v>20.8</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>8.19987187700192</v>
+        <v>5.32991672005125</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>7.19987187700192</v>
+        <v>4.32991672005125</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>1.01651917256878</v>
+        <v>0.746787763948759</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5093,7 +5091,7 @@
         <v>101</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4</v>
@@ -5102,19 +5100,19 @@
         <v>184</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>15.3747597693786</v>
+        <v>10.2498398462524</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>14.3747597693786</v>
+        <v>9.2498398462524</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.980168213089453</v>
+        <v>0.789283964832156</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5136,7 +5134,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>31.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5145,7 +5143,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>8.02049967969251</v>
+        <v>5.1249199231262</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5154,7 +5152,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>7.02049967969251</v>
+        <v>4.1249199231262</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5163,7 +5161,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>1.00170684955895</v>
+        <v>0.724099640552506</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5176,7 +5174,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>17.9372197309417</v>
+        <v>10.2498398462524</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5185,7 +5183,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>7.77639751552795</v>
+        <v>4.96894409937888</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5502,23 +5500,23 @@
         <v>16</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>1.88812839273071</v>
+        <v>2.07694123200378</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>0.888128392730706</v>
+        <v>1.07694123200378</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.374091842902324</v>
+        <v>0.441159683034388</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5641,19 +5639,19 @@
         <v>197</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>1.88812839273071</v>
+        <v>2.07694123200378</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>0.888128392730706</v>
+        <v>1.07694123200378</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.374091842902324</v>
+        <v>0.441159683034388</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5704,7 +5702,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5713,7 +5711,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>1.88812839273071</v>
+        <v>2.07694123200378</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5722,7 +5720,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>0.888128392730706</v>
+        <v>1.07694123200378</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5731,7 +5729,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.374091842902324</v>
+        <v>0.441159683034388</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5753,7 +5751,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>1.83066361556064</v>
+        <v>2.01372997711671</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="201">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Series C &gt;$1 млрд, закрыт 16.09.2025; лид Parkway Venture Capital</t>
   </si>
   <si>
-    <t xml:space="preserve">2–3 года (IPO 2027–2029)</t>
+    <t xml:space="preserve">3–4 года (IPO 2029–2030)</t>
   </si>
   <si>
     <t xml:space="preserve">1X Technologies</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Series C, до $1 млрд, в процессе — оценка $10+ млрд (предыдущий закрытый: Series B $100 млн, январь 2024, лид EQT Ventures)</t>
   </si>
   <si>
-    <t xml:space="preserve">4–5 лет (IPO ~2030)</t>
+    <t xml:space="preserve">2–3 года (IPO 2029)</t>
   </si>
   <si>
     <t xml:space="preserve">Polymarket</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Раунд ~$1 млрд, закрыт в апреле 2026; новые инвесторы D.E. Shaw и G Squared, ICE добавила $600 млн</t>
   </si>
   <si>
-    <t xml:space="preserve">2–4 года (IPO 2028–2030 или продажа ICE)</t>
+    <t xml:space="preserve">2–3 года (IPO 2029 или продажа ICE)</t>
   </si>
   <si>
     <t xml:space="preserve">Kalshi</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Series F $1 млрд, закрыт 07.05.2026; лид Coatue (Sequoia, a16z, IVP, Paradigm, Morgan Stanley, ARK)</t>
   </si>
   <si>
-    <t xml:space="preserve">1–3 года (IPO ~2027)</t>
+    <t xml:space="preserve">1–2 года (IPO 2027–2028)</t>
   </si>
   <si>
     <t xml:space="preserve">Positron AI</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Series B $230 млн (переподписан), закрыт 04.02.2026; со-лиды ARENA, Jump Trading, Unless; стратеги QIA и Arm</t>
   </si>
   <si>
-    <t xml:space="preserve">3–4 года (IPO / M&amp;A 2028–2030)</t>
+    <t xml:space="preserve">3–4 года (IPO / M&amp;A 2029–2030)</t>
   </si>
   <si>
     <t xml:space="preserve">Databricks</t>
@@ -162,9 +162,6 @@
     <t xml:space="preserve">Стратегический раунд $5 млрд, закрыт 13.08.2026; лид Coatue (спрос ~$15 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">1–2 года (IPO 2027–2028)</t>
-  </si>
-  <si>
     <t xml:space="preserve">По 1X Technologies и Positron AI последние закрытые раунды устарели, поэтому премия 8–15% считается не от них, а от оценки идущего раунда (1X — Series C ~$10 млрд; Positron — первый транш ~$3.5 млрд).</t>
   </si>
   <si>
@@ -384,7 +381,7 @@
     <t xml:space="preserve">• Цена на вторичном рынке индикативна; реальная цена — по запросу на момент сделки.</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Forge: $174.00/акция (13–15.08.2026), Nasdaq Private Market $162.71 (16.06.2026) — торгуется вблизи отметки Series C.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Бумага торгуется с дисконтом к Series C: Forge $174.00/акция (13–15.08.2026), Nasdaq Private Market $162.71 (16.06.2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Tesla</t>
@@ -420,6 +417,9 @@
     <t xml:space="preserve">2029</t>
   </si>
   <si>
+    <t xml:space="preserve">2030</t>
+  </si>
+  <si>
     <t xml:space="preserve">Мощность BotQ до 100 тыс. роботов/год; заказ UPS до ~100 тыс. роботов к 2029. При 60–80 тыс. поставок/год и ASP/RaaS ~$100–130 тыс. выручка выходит на $8–12 млрд.</t>
   </si>
   <si>
@@ -441,7 +441,7 @@
     <t xml:space="preserve">• TAM: Goldman Sachs $38 млрд к 2035; Morgan Stanley $5 трлн к 2050</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Оценка идущего Series C — $10+ млрд (The Information); Nasdaq Private Market ~$662/акция (31.07.2026). Закрытый Series B (01.2024, $0.82 млрд) устарел и в расчёте не используется.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Оценка идущего Series C — $10+ млрд (The Information); Nasdaq Private Market ~$662/акция (31.07.2026). Закрытый Series B (01.2024, $0.82 млрд) устарел и в расчёте не используется.</t>
   </si>
   <si>
     <t xml:space="preserve">iRobot</t>
@@ -450,129 +450,126 @@
     <t xml:space="preserve">предостерегающий комп: консьюмер-железо без ИИ-рва</t>
   </si>
   <si>
-    <t xml:space="preserve">2030</t>
+    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 250–400 тыс. штук к 2030 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $4–6 млрд (целевой сценарий — $5 млрд).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка на уровне идущего Series C ($10 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Паритет с текущей оценкой Figure AI при лидерстве в домашнем сегменте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Массовое проникновение домашних роботов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series B $100 млн: 1x.tech, январь 2024; Series C в процессе: The Information, сентябрь 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• NEO: 10 тыс.+ предзаказов за 5 дней (бэклог &gt;$200 млн); производство в Hayward, CA с апреля 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• EQT: контракт до 10 тыс. роботов для портфельных компаний 2026–2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Вторичные сделки идут вблизи апрельской отметки раунда; для справки: Bloomberg/CNBC (04.08.2026) сообщали о переговорах по раунду выше $20 млрд.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robinhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CME Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">биржевой оператор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–10x, стратегический акционер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">крипто-биржа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DraftKings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">беттинг — нижняя граница</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized-выручка &gt;$1 млрд уже через 6 недель после запуска биржи в США. Bernstein: объёмы отрасли $1 трлн к 2030; при доле ~30% и комиссии ~2% выручка Polymarket выходит на $6 млрд.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка идущего раунда (&gt;$20 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Паритет с Kalshi по обороту + премия за глобальный рынок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ре-рейтинг категории до биржевой инфраструктуры (CME/ICE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд $15 млрд: Bloomberg 20.04.2026; раунд &gt;$20 млрд в переговорах: Bloomberg/CNBC 04.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка &gt;$1 млрд annualized: CNBC, 26.06.2026; обороты ~$9–10.5 млрд/мес</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ICE: инвестиции до $2 млрд (окт 2025) + дистрибуция данных; партнёрство с X/xAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Фактические сделки на вторичном рынке идут около $35 млрд: рынок уже отыгрывает раунд по оценке $40 млрд, который обсуждают Sequoia и Wellington (CoinDesk, 13.08.2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">биржа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026. ~90% рынка США и обороты $21 млрд/мес; целевой сценарий — $8 млрд выручки к 2029 при сохранении доли.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка идущего раунда ($40 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO ~2027–28 при мультипликаторах биржевых операторов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Категория выходит на объёмы $1.5 трлн (Macquarie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series F $1 млрд @ $22 млрд: TechCrunch/BusinessWire, 07.05.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд @ $40 млрд в переговорах: CoinDesk, 13.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка 2025 $263.5 млн, run-rate ~$4 млрд (июль 2026); всего привлечено ~$2.8 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">База для вторичного рынка, $ млрд (оценка идущего раунда)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Bloomberg (08.07.2026): раунд ~$750 млн двумя траншами по оценкам ~$3.5 и ~$5 млрд — вторичный рынок торгуется по верхней границе этих переговоров, кратно выше Series B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broadcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marvell</t>
   </si>
   <si>
     <t xml:space="preserve">2031</t>
   </si>
   <si>
-    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 250–400 тыс. штук к 2030 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $4–6 млрд (целевой сценарий — $5 млрд).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка на уровне идущего Series C ($10 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Паритет с текущей оценкой Figure AI при лидерстве в домашнем сегменте</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Массовое проникновение домашних роботов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Series B $100 млн: 1x.tech, январь 2024; Series C в процессе: The Information, сентябрь 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• NEO: 10 тыс.+ предзаказов за 5 дней (бэклог &gt;$200 млн); производство в Hayward, CA с апреля 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• EQT: контракт до 10 тыс. роботов для портфельных компаний 2026–2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Bloomberg/CNBC (04.08.2026): раунд ~$1 млрд по оценке &gt;$20 млрд в переговорах — вторичные сделки идут с премией к апрельской отметке.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robinhood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV/Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CME Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">биржевой оператор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8–10x, стратегический акционер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coinbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">крипто-биржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DraftKings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">беттинг — нижняя граница</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annualized-выручка &gt;$1 млрд уже через 6 недель после запуска биржи в США. Bernstein: объёмы отрасли $1 трлн к 2030; при доле ~30% и комиссии ~2% выручка Polymarket выходит на $6 млрд.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка идущего раунда (&gt;$20 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Паритет с Kalshi по обороту + премия за глобальный рынок</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ре-рейтинг категории до биржевой инфраструктуры (CME/ICE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Раунд $15 млрд: Bloomberg 20.04.2026; раунд &gt;$20 млрд в переговорах: Bloomberg/CNBC 04.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Выручка &gt;$1 млрд annualized: CNBC, 26.06.2026; обороты ~$9–10.5 млрд/мес</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• ICE: инвестиции до $2 млрд (окт 2025) + дистрибуция данных; партнёрство с X/xAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Фактические сделки на вторичном рынке идут около $35 млрд: рынок уже отыгрывает раунд по оценке $40 млрд, который обсуждают Sequoia и Wellington (CoinDesk, 13.08.2026).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">биржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026. ~90% рынка США и обороты $21 млрд/мес; целевой сценарий — $8 млрд выручки к 2029 при сохранении доли.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка идущего раунда ($40 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO ~2027–28 при мультипликаторах биржевых операторов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Категория выходит на объёмы $1.5 трлн (Macquarie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Series F $1 млрд @ $22 млрд: TechCrunch/BusinessWire, 07.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Раунд @ $40 млрд в переговорах: CoinDesk, 13.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Выручка 2025 $263.5 млн, run-rate ~$4 млрд (июль 2026); всего привлечено ~$2.8 млрд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">База для вторичного рынка, $ млрд (оценка идущего раунда)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке идущего раунда (закрытый раунд устарел). Bloomberg (08.07.2026): раунд ~$750 млн двумя траншами по оценкам ~$3.5 и ~$5 млрд. Бумага торгуется на Forge/Caplight — цена уже кратно выше Series B.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broadcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marvell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Букинги: контракт Oracle $50.4 млн (344 сервера Atlas), Cloudflare, Parasail. Целевой сценарий — ramp собственного чипа Asimov (производство с 2027) до выручки ~$1.8 млрд к 2029; рынок инференс-чипов $37 млрд к 2030.</t>
   </si>
   <si>
@@ -594,7 +591,7 @@
     <t xml:space="preserve">• Контракт Oracle: EE Times, апрель 2026; TAM инференс-чипов $37 млрд к 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Раунд закрыт в августе 2026 при переподписке втрое; вторичные сделки перед IPO идут с премией к раунду.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Раунд закрыт в августе 2026 при переподписке втрое; вторичные сделки перед IPO идут с премией к раунду.</t>
   </si>
   <si>
     <t xml:space="preserve">Snowflake</t>
@@ -1353,15 +1350,15 @@
       </c>
       <c r="F6" s="6" t="n">
         <f aca="false">'Figure AI'!B10</f>
-        <v>42.12</v>
+        <v>30</v>
       </c>
       <c r="G6" s="6" t="n">
         <f aca="false">'Figure AI'!B11</f>
-        <v>44.85</v>
+        <v>33</v>
       </c>
       <c r="H6" s="6" t="n">
         <f aca="false">'Figure AI'!B12</f>
-        <v>43.485</v>
+        <v>31.5</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>24</v>
@@ -1372,23 +1369,23 @@
       </c>
       <c r="K6" s="8" t="n">
         <f aca="false">'Figure AI'!B37</f>
-        <v>2.29964355524894</v>
+        <v>3.17460317460317</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">'Figure AI'!B38</f>
-        <v>1.29964355524894</v>
+        <v>2.17460317460317</v>
       </c>
       <c r="M6" s="9" t="n">
         <f aca="false">'Figure AI'!B39</f>
-        <v>0.319937928526136</v>
+        <v>0.39104071511099</v>
       </c>
       <c r="N6" s="8" t="n">
         <f aca="false">'Figure AI'!B40</f>
-        <v>0.896860986547085</v>
+        <v>1.23809523809524</v>
       </c>
       <c r="O6" s="8" t="n">
         <f aca="false">'Figure AI'!C40</f>
-        <v>4.9672300793377</v>
+        <v>6.85714285714286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1411,15 +1408,15 @@
       </c>
       <c r="F7" s="6" t="n">
         <f aca="false">1X!B10</f>
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="G7" s="6" t="n">
         <f aca="false">1X!B11</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H7" s="6" t="n">
         <f aca="false">1X!B12</f>
-        <v>11.15</v>
+        <v>11.25</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>28</v>
@@ -1430,23 +1427,23 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">1X!B37</f>
-        <v>5.38116591928251</v>
+        <v>5.33333333333333</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">1X!B38</f>
-        <v>4.38116591928251</v>
+        <v>4.33333333333333</v>
       </c>
       <c r="M7" s="9" t="n">
         <f aca="false">1X!B39</f>
-        <v>0.523067306155961</v>
+        <v>0.953437367722348</v>
       </c>
       <c r="N7" s="8" t="n">
         <f aca="false">1X!B40</f>
-        <v>0.896860986547085</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="O7" s="8" t="n">
         <f aca="false">1X!C40</f>
-        <v>12.1076233183857</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1469,42 +1466,42 @@
       </c>
       <c r="F8" s="6" t="n">
         <f aca="false">Polymarket!B10</f>
-        <v>16.2</v>
+        <v>13.5</v>
       </c>
       <c r="G8" s="6" t="n">
         <f aca="false">Polymarket!B11</f>
-        <v>17.25</v>
+        <v>15</v>
       </c>
       <c r="H8" s="6" t="n">
         <f aca="false">Polymarket!B12</f>
-        <v>16.725</v>
+        <v>14.25</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="J8" s="6" t="n">
         <f aca="false">Polymarket!B36</f>
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K8" s="8" t="n">
         <f aca="false">Polymarket!B37</f>
-        <v>2.98953662182362</v>
+        <v>3.15789473684211</v>
       </c>
       <c r="L8" s="9" t="n">
         <f aca="false">Polymarket!B38</f>
-        <v>1.98953662182362</v>
+        <v>2.15789473684211</v>
       </c>
       <c r="M8" s="9" t="n">
         <f aca="false">Polymarket!B39</f>
-        <v>0.440570861275843</v>
+        <v>0.584014160754065</v>
       </c>
       <c r="N8" s="8" t="n">
         <f aca="false">Polymarket!B40</f>
-        <v>1.31539611360239</v>
+        <v>1.54385964912281</v>
       </c>
       <c r="O8" s="8" t="n">
         <f aca="false">Polymarket!C40</f>
-        <v>6.45739910313901</v>
+        <v>7.57894736842105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1554,7 +1551,7 @@
       </c>
       <c r="M9" s="9" t="n">
         <f aca="false">Kalshi!B39</f>
-        <v>0.663936649275048</v>
+        <v>0.889822365046136</v>
       </c>
       <c r="N9" s="8" t="n">
         <f aca="false">Kalshi!B40</f>
@@ -1585,42 +1582,42 @@
       </c>
       <c r="F10" s="6" t="n">
         <f aca="false">'Positron AI'!B10</f>
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="G10" s="6" t="n">
         <f aca="false">'Positron AI'!B11</f>
-        <v>4.025</v>
+        <v>5</v>
       </c>
       <c r="H10" s="6" t="n">
         <f aca="false">'Positron AI'!B12</f>
-        <v>3.9025</v>
+        <v>4.75</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>40</v>
       </c>
       <c r="J10" s="6" t="n">
         <f aca="false">'Positron AI'!B36</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" s="8" t="n">
         <f aca="false">'Positron AI'!B37</f>
-        <v>5.1249199231262</v>
+        <v>5.05263157894737</v>
       </c>
       <c r="L10" s="9" t="n">
         <f aca="false">'Positron AI'!B38</f>
-        <v>4.1249199231262</v>
+        <v>4.05263157894737</v>
       </c>
       <c r="M10" s="9" t="n">
         <f aca="false">'Positron AI'!B39</f>
-        <v>0.724099640552506</v>
+        <v>0.588565175565576</v>
       </c>
       <c r="N10" s="8" t="n">
         <f aca="false">'Positron AI'!B40</f>
-        <v>1.28122998078155</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="O10" s="8" t="n">
         <f aca="false">'Positron AI'!C40</f>
-        <v>10.2498398462524</v>
+        <v>8.42105263157895</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1643,52 +1640,52 @@
       </c>
       <c r="F11" s="6" t="n">
         <f aca="false">Databricks!B10</f>
-        <v>205.2</v>
+        <v>195</v>
       </c>
       <c r="G11" s="6" t="n">
         <f aca="false">Databricks!B11</f>
-        <v>218.5</v>
+        <v>210</v>
       </c>
       <c r="H11" s="6" t="n">
         <f aca="false">Databricks!B12</f>
-        <v>211.85</v>
+        <v>202.5</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J11" s="6" t="n">
         <f aca="false">Databricks!B36</f>
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="K11" s="8" t="n">
         <f aca="false">Databricks!B37</f>
-        <v>2.07694123200378</v>
+        <v>2.09876543209877</v>
       </c>
       <c r="L11" s="9" t="n">
         <f aca="false">Databricks!B38</f>
-        <v>1.07694123200378</v>
+        <v>1.09876543209877</v>
       </c>
       <c r="M11" s="9" t="n">
         <f aca="false">Databricks!B39</f>
-        <v>0.441159683034388</v>
+        <v>0.448711645600589</v>
       </c>
       <c r="N11" s="8" t="n">
         <f aca="false">Databricks!B40</f>
-        <v>0.896860986547085</v>
+        <v>0.938271604938272</v>
       </c>
       <c r="O11" s="8" t="n">
         <f aca="false">Databricks!C40</f>
-        <v>2.95020061364173</v>
+        <v>3.08641975308642</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1716,7 +1713,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1724,71 +1721,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1829,7 +1826,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1842,7 +1839,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>19</v>
@@ -1850,7 +1847,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>852</v>
@@ -1858,7 +1855,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>852</v>
@@ -1866,7 +1863,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -1874,7 +1871,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -1882,7 +1879,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B7*(1+B8)</f>
@@ -1891,7 +1888,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B7*(1+B9)</f>
@@ -1900,7 +1897,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -1909,15 +1906,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>74</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -1933,70 +1930,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2009,39 +2006,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="23" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>98</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -2071,10 +2068,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>99</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>100</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -2104,10 +2101,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -2137,12 +2134,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2155,42 +2152,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="23" t="s">
         <v>97</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>98</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>1000</v>
@@ -2210,16 +2207,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="23" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>100</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1550</v>
@@ -2239,16 +2236,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>2200</v>
@@ -2268,7 +2265,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2281,7 +2278,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -2308,7 +2305,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -2317,7 +2314,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -2330,7 +2327,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -2339,7 +2336,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2352,22 +2349,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2408,7 +2405,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2421,7 +2418,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>23</v>
@@ -2429,7 +2426,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>39</v>
@@ -2437,7 +2434,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>39</v>
@@ -2445,7 +2442,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2453,7 +2450,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2461,42 +2458,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>42.12</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>44.85</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>43.485</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2512,70 +2507,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.6</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2588,42 +2583,42 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="25" t="n">
         <v>3.5</v>
@@ -2637,26 +2632,26 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.20731286650569</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.207312866505692</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.0782710162424243</v>
+        <v>0.185631101496688</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
         <v>7</v>
@@ -2670,26 +2665,26 @@
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.41462573301138</v>
+        <v>3.33333333333333</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.41462573301138</v>
+        <v>2.33333333333333</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.341580101775709</v>
+        <v>0.4105676750826</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>12</v>
@@ -2703,15 +2698,15 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>4.9672300793377</v>
+        <v>6.85714285714286</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>3.9672300793377</v>
+        <v>5.85714285714286</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.70623203714332</v>
+        <v>0.733397063047994</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2721,7 +2716,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2734,39 +2729,39 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>131</v>
@@ -2776,26 +2771,26 @@
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.896860986547085</v>
+        <v>1.23809523809524</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.103139013452915</v>
+        <v>0.238095238095238</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.0426074293387877</v>
+        <v>0.0737866932948026</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>132</v>
@@ -2805,26 +2800,26 @@
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.18466137748649</v>
+        <v>3.01587301587302</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.18466137748649</v>
+        <v>2.01587301587302</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.297561776477154</v>
+        <v>0.370803351494498</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>133</v>
@@ -2834,20 +2829,20 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>4.13935839944809</v>
+        <v>5.71428571428571</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>3.13935839944809</v>
+        <v>4.71428571428571</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.605625820582937</v>
+        <v>0.645412693099038</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2860,7 +2855,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -2873,7 +2868,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.29964355524894</v>
+        <v>3.17460317460317</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2882,43 +2877,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.29964355524894</v>
+        <v>2.17460317460317</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.319937928526136</v>
+        <v>0.39104071511099</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.896860986547085</v>
+        <v>1.23809523809524</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>4.9672300793377</v>
+        <v>6.85714285714286</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.22965440356745</v>
+        <v>3.03030303030303</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2946,7 +2941,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2987,7 +2982,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3000,7 +2995,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -3008,7 +3003,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>10</v>
@@ -3016,7 +3011,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3032,7 +3027,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3040,34 +3035,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>10.8</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>11.5</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>11.15</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>137</v>
@@ -3075,7 +3068,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3091,32 +3084,32 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3132,7 +3125,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3145,42 +3138,42 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D25" s="25" t="n">
         <v>2</v>
@@ -3194,26 +3187,26 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>2.152466367713</v>
+        <v>2.13333333333333</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>1.152466367713</v>
+        <v>1.13333333333333</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.21125084652792</v>
+        <v>0.354015037863309</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
         <v>5</v>
@@ -3227,26 +3220,26 @@
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>5.38116591928251</v>
+        <v>5.33333333333333</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>4.38116591928251</v>
+        <v>4.33333333333333</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.523067306155961</v>
+        <v>0.953437367722348</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>9</v>
@@ -3260,25 +3253,25 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>12.1076233183857</v>
+        <v>12</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>11.1076233183857</v>
+        <v>11</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.646689742514757</v>
+        <v>1.03393700979443</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3291,120 +3284,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.896860986547085</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.103139013452915</v>
+        <v>-0.111111111111111</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.0268466474287021</v>
+        <v>-0.0460206125964964</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>60</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>5.38116591928251</v>
+        <v>5.33333333333333</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>4.38116591928251</v>
+        <v>4.33333333333333</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.523067306155961</v>
+        <v>0.953437367722348</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>110</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>9.86547085201794</v>
+        <v>9.77777777777778</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>8.86547085201794</v>
+        <v>8.77777777777778</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.580605772027474</v>
+        <v>0.918340787372848</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3417,7 +3410,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3430,7 +3423,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>5.38116591928251</v>
+        <v>5.33333333333333</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,43 +3432,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>4.38116591928251</v>
+        <v>4.33333333333333</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.523067306155961</v>
+        <v>0.953437367722348</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.896860986547085</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>12.1076233183857</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>5.21739130434783</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3488,22 +3481,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3544,7 +3537,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3557,7 +3550,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>31</v>
@@ -3565,7 +3558,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>15</v>
@@ -3573,7 +3566,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>15</v>
@@ -3581,7 +3574,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3589,7 +3582,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3597,42 +3590,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>16.2</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>17.25</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>16.725</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3648,70 +3639,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3724,42 +3715,42 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
         <v>2.5</v>
@@ -3773,59 +3764,59 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>2.24215246636771</v>
+        <v>2.63157894736842</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>1.24215246636771</v>
+        <v>1.63157894736842</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.381230171609196</v>
+        <v>0.622214211307625</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C26" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
         <v>3</v>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>3.5</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>52.5</v>
+        <v>45</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.1390134529148</v>
+        <v>3.15789473684211</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.1390134529148</v>
+        <v>2.15789473684211</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.464190975134403</v>
+        <v>0.584014160754065</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>6</v>
@@ -3839,25 +3830,25 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>6.45739910313901</v>
+        <v>7.57894736842105</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>5.45739910313901</v>
+        <v>6.57894736842105</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.594095762282103</v>
+        <v>0.783679520883073</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3870,120 +3861,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.31539611360239</v>
+        <v>1.54385964912281</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.315396113602392</v>
+        <v>0.543859649122807</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.115893175988942</v>
+        <v>0.242521488394791</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>47.5</v>
+        <v>45</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.84005979073244</v>
+        <v>3.15789473684211</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.84005979073244</v>
+        <v>2.15789473684211</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.416149688179292</v>
+        <v>0.584014160754065</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>5.97907324364723</v>
+        <v>7.01754385964912</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>4.97907324364723</v>
+        <v>6.01754385964912</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.56371811889409</v>
+        <v>0.744886496169584</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3996,11 +3987,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4009,7 +4000,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.98953662182362</v>
+        <v>3.15789473684211</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4018,43 +4009,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.98953662182362</v>
+        <v>2.15789473684211</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.440570861275843</v>
+        <v>0.584014160754065</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.31539611360239</v>
+        <v>1.54385964912281</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>6.45739910313901</v>
+        <v>7.57894736842105</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.89855072463768</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4067,22 +4058,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -4123,7 +4114,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4136,7 +4127,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>35</v>
@@ -4144,7 +4135,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>22</v>
@@ -4152,7 +4143,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>22</v>
@@ -4160,7 +4151,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4168,7 +4159,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4176,7 +4167,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -4184,7 +4175,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>40</v>
@@ -4192,7 +4183,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4201,15 +4192,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4225,59 +4216,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4290,39 +4281,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -4352,13 +4343,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>129</v>
-      </c>
       <c r="C26" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="25" t="n">
         <v>8</v>
@@ -4380,18 +4371,18 @@
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.636987189097755</v>
+        <v>0.851640199545103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>14</v>
@@ -4413,17 +4404,17 @@
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.699562481967873</v>
+        <v>0.856635533445112</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4436,42 +4427,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>40</v>
@@ -4491,16 +4482,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="23" t="s">
-        <v>129</v>
-      </c>
       <c r="C33" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>130</v>
@@ -4515,21 +4506,21 @@
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.690246803060484</v>
+        <v>0.927248223318863</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>200</v>
@@ -4544,12 +4535,12 @@
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.645412693099038</v>
+        <v>0.787807070193135</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4562,7 +4553,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4589,16 +4580,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.663936649275048</v>
+        <v>0.889822365046136</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4611,7 +4602,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4620,7 +4611,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4633,22 +4624,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -4689,7 +4680,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4702,7 +4693,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>39</v>
@@ -4710,7 +4701,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -4718,7 +4709,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>3.5</v>
@@ -4726,7 +4717,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4734,7 +4725,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4742,42 +4733,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>3.78</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>4.025</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>3.9025</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4793,59 +4782,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4858,39 +4847,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -4907,59 +4896,59 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>2.30621396540679</v>
+        <v>1.89473684210526</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>1.30621396540679</v>
+        <v>0.894736842105263</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.32119381694172</v>
+        <v>0.237417631815703</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>19.2</v>
+        <v>23.8</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>4.91992312620115</v>
+        <v>5.01052631578947</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>3.91992312620115</v>
+        <v>4.01052631578947</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.700798140351766</v>
+        <v>0.584771566780115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>2</v>
@@ -4973,25 +4962,25 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>9.22485586162716</v>
+        <v>7.57894736842105</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>8.22485586162716</v>
+        <v>6.57894736842105</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.742769285165229</v>
+        <v>0.568442646751593</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5004,120 +4993,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.28122998078155</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.28122998078155</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0861147146241434</v>
+        <v>0.017244768191101</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>20.8</v>
+        <v>24.2</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>5.32991672005125</v>
+        <v>5.09473684210526</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>4.32991672005125</v>
+        <v>4.09473684210526</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.746787763948759</v>
+        <v>0.592336270065984</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>40</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>10.2498398462524</v>
+        <v>8.42105263157895</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>9.2498398462524</v>
+        <v>7.42105263157895</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.789283964832156</v>
+        <v>0.605598573805891</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5130,11 +5119,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5143,7 +5132,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>5.1249199231262</v>
+        <v>5.05263157894737</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5152,43 +5141,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>4.1249199231262</v>
+        <v>4.05263157894737</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.724099640552506</v>
+        <v>0.588565175565576</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.28122998078155</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>10.2498398462524</v>
+        <v>8.42105263157895</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>4.96894409937888</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5201,22 +5190,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -5257,7 +5246,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5270,7 +5259,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -5278,7 +5267,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>190</v>
@@ -5286,7 +5275,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>190</v>
@@ -5294,7 +5283,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5302,7 +5291,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5310,42 +5299,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>205.2</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>218.5</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>211.85</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5361,59 +5348,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5426,39 +5413,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -5475,23 +5462,23 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.18952088742034</v>
+        <v>1.24444444444444</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.189520887420345</v>
+        <v>0.244444444444444</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.0906515884645951</v>
+        <v>0.115546702045434</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>99</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>100</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -5500,31 +5487,31 @@
         <v>16</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.07694123200378</v>
+        <v>2.09382716049383</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.07694123200378</v>
+        <v>1.09382716049383</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.441159683034388</v>
+        <v>0.447006275208863</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -5541,25 +5528,25 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>2.95020061364173</v>
+        <v>3.08641975308642</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>1.95020061364173</v>
+        <v>2.08641975308642</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.434224651846131</v>
+        <v>0.455967441227165</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5572,120 +5559,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>190</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.896860986547085</v>
+        <v>0.938271604938272</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.103139013452915</v>
+        <v>-0.0617283950617285</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.0529725523792433</v>
+        <v>-0.0313557903242948</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="23" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>100</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.07694123200378</v>
+        <v>2.1037037037037</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.07694123200378</v>
+        <v>1.1037037037037</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.441159683034388</v>
+        <v>0.45041501085162</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>600</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>2.83219258909606</v>
+        <v>2.96296296296296</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>1.83219258909606</v>
+        <v>1.96296296296296</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.414840861474137</v>
+        <v>0.436289793354589</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5698,11 +5685,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>440</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5711,7 +5698,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.07694123200378</v>
+        <v>2.09876543209877</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5720,43 +5707,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.07694123200378</v>
+        <v>1.09876543209877</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.441159683034388</v>
+        <v>0.448711645600589</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.896860986547085</v>
+        <v>0.938271604938272</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>2.95020061364173</v>
+        <v>3.08641975308642</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.01372997711671</v>
+        <v>2.02380952380952</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5769,22 +5756,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -450,13 +450,13 @@
     <t xml:space="preserve">предостерегающий комп: консьюмер-железо без ИИ-рва</t>
   </si>
   <si>
-    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 250–400 тыс. штук к 2030 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $4–6 млрд (целевой сценарий — $5 млрд).</t>
+    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 150–250 тыс. штук к 2029 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $3–4 млрд (базовый сценарий — $3.5 млрд).</t>
   </si>
   <si>
     <t xml:space="preserve">Оценка на уровне идущего Series C ($10 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">Паритет с текущей оценкой Figure AI при лидерстве в домашнем сегменте</t>
+    <t xml:space="preserve">Кратный рост к идущему Series C при выходе NEO на серийные поставки</t>
   </si>
   <si>
     <t xml:space="preserve">Массовое проникновение домашних роботов</t>
@@ -531,7 +531,7 @@
     <t xml:space="preserve">биржа</t>
   </si>
   <si>
-    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026. ~90% рынка США и обороты $21 млрд/мес; целевой сценарий — $8 млрд выручки к 2029 при сохранении доли.</t>
+    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026 (пик ЧМ по футболу). Базовый сценарий консервативен: $6 млрд выручки к 2028 при мультипликаторе биржевых операторов 12x.</t>
   </si>
   <si>
     <t xml:space="preserve">Оценка идущего раунда ($40 млрд)</t>
@@ -1423,19 +1423,19 @@
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">1X!B36</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">1X!B37</f>
-        <v>5.33333333333333</v>
+        <v>3.55555555555556</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">1X!B38</f>
-        <v>4.33333333333333</v>
+        <v>2.55555555555556</v>
       </c>
       <c r="M7" s="9" t="n">
         <f aca="false">1X!B39</f>
-        <v>0.953437367722348</v>
+        <v>0.660974586154023</v>
       </c>
       <c r="N7" s="8" t="n">
         <f aca="false">1X!B40</f>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="O7" s="8" t="n">
         <f aca="false">1X!C40</f>
-        <v>12</v>
+        <v>9.33333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1539,19 +1539,19 @@
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">Kalshi!B36</f>
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="K9" s="8" t="n">
         <f aca="false">Kalshi!B37</f>
-        <v>3.57142857142857</v>
+        <v>2.14285714285714</v>
       </c>
       <c r="L9" s="9" t="n">
         <f aca="false">Kalshi!B38</f>
-        <v>2.57142857142857</v>
+        <v>1.14285714285714</v>
       </c>
       <c r="M9" s="9" t="n">
         <f aca="false">Kalshi!B39</f>
-        <v>0.889822365046136</v>
+        <v>0.4638501094228</v>
       </c>
       <c r="N9" s="8" t="n">
         <f aca="false">Kalshi!B40</f>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="O9" s="8" t="n">
         <f aca="false">Kalshi!C40</f>
-        <v>6.4</v>
+        <v>4.28571428571429</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3209,26 +3209,26 @@
         <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>12</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>5.33333333333333</v>
+        <v>3.73333333333333</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>4.33333333333333</v>
+        <v>2.73333333333333</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.953437367722348</v>
+        <v>0.693708656418214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3242,26 +3242,26 @@
         <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>12</v>
+        <v>9.33333333333333</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>11</v>
+        <v>8.33333333333333</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>1.03393700979443</v>
+        <v>0.893011990144175</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3351,19 +3351,19 @@
         <v>142</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>5.33333333333333</v>
+        <v>3.37777777777778</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>4.33333333333333</v>
+        <v>2.37777777777778</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.953437367722348</v>
+        <v>0.62724306623747</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3380,19 +3380,19 @@
         <v>143</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>9.77777777777778</v>
+        <v>8</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>8.77777777777778</v>
+        <v>7</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.918340787372848</v>
+        <v>0.811447328527813</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>5.33333333333333</v>
+        <v>3.55555555555556</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>4.33333333333333</v>
+        <v>2.55555555555556</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.953437367722348</v>
+        <v>0.660974586154023</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>12</v>
+        <v>9.33333333333333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>5</v>
+        <v>3.33333333333333</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4319,26 +4319,26 @@
         <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.71428571428571</v>
+        <v>1.14285714285714</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.309307341415954</v>
+        <v>0.0690449676496976</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4352,26 +4352,26 @@
         <v>2</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.42857142857143</v>
+        <v>2.05714285714286</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.42857142857143</v>
+        <v>1.05714285714286</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.851640199545103</v>
+        <v>0.434274331201272</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4385,26 +4385,26 @@
         <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>6.4</v>
+        <v>4.28571428571429</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>5.4</v>
+        <v>3.28571428571429</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.856635533445112</v>
+        <v>0.62433052162942</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4494,19 +4494,19 @@
         <v>169</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.71428571428571</v>
+        <v>2.22857142857143</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.71428571428571</v>
+        <v>1.22857142857143</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.927248223318863</v>
+        <v>0.492840054584358</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4523,19 +4523,19 @@
         <v>170</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>5.71428571428571</v>
+        <v>4.28571428571429</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>4.71428571428571</v>
+        <v>3.28571428571429</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.787807070193135</v>
+        <v>0.62433052162942</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>125</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.57142857142857</v>
+        <v>2.14285714285714</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.57142857142857</v>
+        <v>1.14285714285714</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.889822365046136</v>
+        <v>0.4638501094228</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>6.4</v>
+        <v>4.28571428571429</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>3.125</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -17,6 +17,8 @@
     <sheet name="Kalshi" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Positron AI" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Databricks" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="VAST Data" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="ByteDance" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,12 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="241">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
   <si>
-    <t xml:space="preserve">Данные на 24.08.2026. Все суммы в $ млрд. Цена на вторичном рынке — премия 8–15% к оценке раунда; индикативна, фактическая цена подтверждается по запросу на момент сделки.</t>
+    <t xml:space="preserve">Данные на 24.08.2026. Все суммы в $ млрд. Цена на вторичном рынке — индикативный диапазон фактических сделок; подтверждается по запросу на момент сделки.</t>
   </si>
   <si>
     <t xml:space="preserve">Компания</t>
@@ -51,10 +53,10 @@
     <t xml:space="preserve">База для вторички</t>
   </si>
   <si>
-    <t xml:space="preserve">Вторичный рынок: низ (+8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вторичный рынок: верх (+15%)</t>
+    <t xml:space="preserve">Вторичный рынок: низ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вторичный рынок: верх</t>
   </si>
   <si>
     <t xml:space="preserve">Цена входа (середина)</t>
@@ -162,6 +164,30 @@
     <t xml:space="preserve">Стратегический раунд $5 млрд, закрыт 13.08.2026; лид Coatue (спрос ~$15 млрд)</t>
   </si>
   <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инфраструктура данных для ИИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series F ~$1 млрд ($500 млн первичных + $500 млн выкуп акций), закрыт 22.04.2026; лид Drive Capital, со-лид Access Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–3 года (IPO 2028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ByteDance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Соцсети и цифровая реклама</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выкуп акций у сотрудников по $229.50 за акцию, 15.04.2026 (+14.5% к октябрю 2025) — имплайд-оценка $400–450 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 года (выкуп акций / блок-трейд)</t>
+  </si>
+  <si>
     <t xml:space="preserve">По 1X Technologies и Positron AI последние закрытые раунды устарели, поэтому премия 8–15% считается не от них, а от оценки идущего раунда (1X — Series C ~$10 млрд; Positron — первый транш ~$3.5 млрд).</t>
   </si>
   <si>
@@ -177,7 +203,7 @@
     <t xml:space="preserve">Цена на вторичном рынке</t>
   </si>
   <si>
-    <t xml:space="preserve">Премия 8% (нижняя граница) — 15% (верхняя граница) к оценке раунда. Для 1X и Positron AI, где закрытый раунд устарел, премия считается от оценки идущего раунда. Диапазон индикативен; фактическая цена подтверждается по запросу на момент сделки.</t>
+    <t xml:space="preserve">Индикативный диапазон: котировки площадок (Forge, Caplight, Nasdaq Private Market) и фактические сделки. Где котировок нет, применяется премия 8–15% к оценке раунда (для 1X и Positron AI — к оценке идущего раунда). Фактическая цена подтверждается по запросу на момент сделки.</t>
   </si>
   <si>
     <t xml:space="preserve">Цена входа в расчётах</t>
@@ -631,6 +657,102 @@
   </si>
   <si>
     <t xml:space="preserve">• Всего привлечено ~$25 млрд; IPO: CEO исключил 2026 год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Бумага торгуется с дисконтом к апрельскому раунду ($30 млрд): половина сделки Series F пришлась на выкуп акций, что уже удовлетворило часть спроса на выход.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue — ближайший аналог по профилю роста</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">хранение данных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nutanix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">инфраструктурный софт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetApp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">традиционное хранение — нижняя граница</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARR превысил $500 млн на конец FY2026, цель компании — более $1 млрд к концу FY2027 при валовой марже ~90% и положительном денежном потоке пятый год подряд. Контракт с CoreWeave на $1.17 млрд превышает весь текущий CARR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка остаётся на уровне Series F ($30 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2028 с удвоением к оценке раунда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ре-рейтинг как инфраструктуры ИИ первого эшелона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series F $30 млрд post-money: анонс 22.04.2026; лид Drive Capital, со-лид Access Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• CARR &gt;$500 млн (FY2026), цель &gt;$1 млрд (FY2027), маржа ~90%: данные компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• IPO: CEO Ренен Халлак — готовность к листингу к концу 2026 (Axios Pro, 22.04.2026); S-1 не подана</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Риск концентрации: контракт CoreWeave $1.17 млрд (06.11.2025) больше всего CARR компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Reuters (февраль 2026): General Atlantic продавал пакет по оценке $550 млрд; к апрелю 2026 биды поднялись выше $600 млрд. Официальный выкуп для сотрудников идёт по более низкой оценке.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue — прямой аналог по рекламе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">соцсети — верх диапазона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tencent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">китайский технологический холдинг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuaishou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">прямой конкурент в Китае — нижняя граница</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка 2025 — около $186 млрд (+20% г/г), фактически вровень с Meta; зарубежная выручка выросла примерно в полтора раза. При сохранении темпа выручка 2027 выходит на $250 млрд; текущая вторичка соответствует ~3.2x EV/Revenue против 7.5x у Meta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка остаётся на уровне текущей вторички ($600 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Следующие раунды выкупа и блок-трейды при росте выручки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сокращение разрыва в мультипликаторах с Meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выкуп по $229.50/акция, имплайд $400–450 млрд: китайские деловые СМИ, 15.04.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Вторичный рынок: $550 млрд (Reuters, февраль 2026), биды выше $600 млрд к апрелю 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка 2025 ~$186 млрд (+20%): eMarketer, Bloomberg; капзатраты на ИИ в 2026 — около $70 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• СП по TikTok в США закрыто 22.01.2026 (Oracle, Silver Lake, MGX по 15%); IPO отложено решением совета (май 2026)</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1320,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1678,14 +1800,1272 @@
         <v>3.08641975308642</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>45</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <f aca="false">'VAST Data'!B6</f>
+        <v>30</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <f aca="false">'VAST Data'!B7</f>
+        <v>30</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <f aca="false">'VAST Data'!B10</f>
+        <v>23</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <f aca="false">'VAST Data'!B11</f>
+        <v>28</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <f aca="false">'VAST Data'!B12</f>
+        <v>25.5</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <f aca="false">'VAST Data'!B36</f>
+        <v>60</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <f aca="false">'VAST Data'!B37</f>
+        <v>2.35294117647059</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <f aca="false">'VAST Data'!B38</f>
+        <v>1.35294117647059</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <f aca="false">'VAST Data'!B39</f>
+        <v>0.408135436805908</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <f aca="false">'VAST Data'!B40</f>
+        <v>1.17647058823529</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <f aca="false">'VAST Data'!C40</f>
+        <v>4.3921568627451</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <f aca="false">ByteDance!B6</f>
+        <v>425</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <f aca="false">ByteDance!B7</f>
+        <v>425</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <f aca="false">ByteDance!B10</f>
+        <v>590</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <f aca="false">ByteDance!B11</f>
+        <v>610</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <f aca="false">ByteDance!B12</f>
+        <v>600</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <f aca="false">ByteDance!B36</f>
+        <v>850</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <f aca="false">ByteDance!B37</f>
+        <v>1.41666666666667</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <f aca="false">ByteDance!B38</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <f aca="false">ByteDance!B39</f>
+        <v>0.190238071423808</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <f aca="false">ByteDance!B40</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <f aca="false">ByteDance!C40</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>30</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>1.17647058823529</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>0.176470588235294</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>0.0846522890932808</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>60</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>2.35294117647059</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>1.35294117647059</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.408135436805908</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>112</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>4.3921568627451</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>3.3921568627451</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.526237923738988</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>1.17647058823529</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>0.176470588235294</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.0846522890932808</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.35294117647059</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.35294117647059</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.408135436805908</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>3.92156862745098</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>2.92156862745098</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.477610431539711</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.35294117647059</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.35294117647059</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.408135436805908</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>1.17647058823529</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>4.3921568627451</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.14285714285714</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>220</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>660</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>1.1</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>0.1</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>0.0488088481701516</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>850</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>1.41666666666667</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.190238071423808</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>1260</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>2.1</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>1.1</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.280579164987494</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>600</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>1</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>850</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>1.41666666666667</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.190238071423808</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>2</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.259921049894873</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>1.41666666666667</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.190238071423808</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>1</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>1.39344262295082</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1713,7 +3093,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1721,71 +3101,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1826,7 +3206,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1839,7 +3219,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>19</v>
@@ -1847,7 +3227,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>852</v>
@@ -1855,7 +3235,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>852</v>
@@ -1863,7 +3243,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -1871,7 +3251,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -1879,7 +3259,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B7*(1+B8)</f>
@@ -1888,7 +3268,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B7*(1+B9)</f>
@@ -1897,7 +3277,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -1906,15 +3286,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -1930,70 +3310,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2006,39 +3386,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -2068,10 +3448,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -2101,10 +3481,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -2134,12 +3514,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2152,42 +3532,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>1000</v>
@@ -2207,16 +3587,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1550</v>
@@ -2236,16 +3616,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>2200</v>
@@ -2265,7 +3645,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2278,7 +3658,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -2305,7 +3685,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -2314,7 +3694,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -2327,7 +3707,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -2336,7 +3716,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2349,22 +3729,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +3785,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2418,7 +3798,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>23</v>
@@ -2426,7 +3806,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>39</v>
@@ -2434,7 +3814,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>39</v>
@@ -2442,7 +3822,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2450,7 +3830,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2458,7 +3838,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -2466,7 +3846,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>33</v>
@@ -2474,7 +3854,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -2483,15 +3863,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2507,70 +3887,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.6</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2583,39 +3963,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -2645,10 +4025,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -2678,10 +4058,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -2711,12 +4091,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2729,42 +4109,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>39</v>
@@ -2784,16 +4164,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>95</v>
@@ -2813,16 +4193,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>180</v>
@@ -2842,7 +4222,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2855,7 +4235,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -2882,7 +4262,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -2891,7 +4271,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -2904,7 +4284,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -2913,7 +4293,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2926,22 +4306,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2982,7 +4362,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2995,7 +4375,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -3003,7 +4383,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>10</v>
@@ -3011,7 +4391,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -3019,7 +4399,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3027,7 +4407,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3035,7 +4415,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>10.5</v>
@@ -3043,7 +4423,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>12</v>
@@ -3051,7 +4431,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3060,15 +4440,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3084,48 +4464,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3138,39 +4518,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -3200,10 +4580,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -3233,10 +4613,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -3266,12 +4646,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3284,42 +4664,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -3339,16 +4719,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>38</v>
@@ -3368,16 +4748,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>90</v>
@@ -3397,7 +4777,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3410,7 +4790,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3437,7 +4817,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3446,7 +4826,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3459,7 +4839,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3468,7 +4848,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3481,22 +4861,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3537,7 +4917,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3550,7 +4930,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>31</v>
@@ -3558,7 +4938,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>15</v>
@@ -3566,7 +4946,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>15</v>
@@ -3574,7 +4954,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3582,7 +4962,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3590,7 +4970,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>13.5</v>
@@ -3598,7 +4978,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>15</v>
@@ -3606,7 +4986,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3615,15 +4995,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3639,70 +5019,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3715,39 +5095,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -3777,10 +5157,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -3810,10 +5190,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -3843,12 +5223,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3861,42 +5241,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
@@ -3916,16 +5296,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>45</v>
@@ -3945,16 +5325,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
@@ -3974,7 +5354,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3987,7 +5367,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4014,7 +5394,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4023,7 +5403,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4036,7 +5416,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4045,7 +5425,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4058,22 +5438,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4114,7 +5494,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4127,7 +5507,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>35</v>
@@ -4135,7 +5515,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>22</v>
@@ -4143,7 +5523,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>22</v>
@@ -4151,7 +5531,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4159,7 +5539,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4167,7 +5547,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -4175,7 +5555,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>40</v>
@@ -4183,7 +5563,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4192,15 +5572,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4216,59 +5596,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4281,39 +5661,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -4343,10 +5723,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -4376,10 +5756,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -4409,12 +5789,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4427,42 +5807,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>40</v>
@@ -4482,16 +5862,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>78</v>
@@ -4511,16 +5891,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>150</v>
@@ -4540,7 +5920,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4553,7 +5933,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4580,7 +5960,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4589,7 +5969,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4602,7 +5982,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4611,7 +5991,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4624,22 +6004,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4680,7 +6060,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4693,7 +6073,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>39</v>
@@ -4701,7 +6081,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -4709,7 +6089,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>3.5</v>
@@ -4717,7 +6097,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4725,7 +6105,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4733,7 +6113,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>4.5</v>
@@ -4741,7 +6121,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5</v>
@@ -4749,7 +6129,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4758,15 +6138,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4782,59 +6162,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4847,39 +6227,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -4909,10 +6289,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -4942,10 +6322,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -4975,12 +6355,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4993,42 +6373,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5</v>
@@ -5048,16 +6428,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>24.2</v>
@@ -5077,16 +6457,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>40</v>
@@ -5106,7 +6486,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5119,7 +6499,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5146,7 +6526,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5155,7 +6535,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5168,7 +6548,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5177,7 +6557,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5190,22 +6570,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -5246,7 +6626,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5259,7 +6639,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -5267,7 +6647,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>190</v>
@@ -5275,7 +6655,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>190</v>
@@ -5283,7 +6663,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5291,7 +6671,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5299,7 +6679,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>195</v>
@@ -5307,7 +6687,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>210</v>
@@ -5315,7 +6695,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5324,15 +6704,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5348,59 +6728,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5413,39 +6793,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -5475,10 +6855,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -5508,10 +6888,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -5541,12 +6921,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5559,42 +6939,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>190</v>
@@ -5614,16 +6994,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>426</v>
@@ -5643,16 +7023,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>600</v>
@@ -5672,7 +7052,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5685,7 +7065,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5712,7 +7092,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5721,7 +7101,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5734,7 +7114,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5743,7 +7123,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5756,22 +7136,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -19,6 +19,9 @@
     <sheet name="Databricks" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="VAST Data" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="ByteDance" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Glean" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Lightmatter" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="PsiQuantum" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="295">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
@@ -188,6 +191,36 @@
     <t xml:space="preserve">1–2 года (выкуп акций / блок-трейд)</t>
   </si>
   <si>
+    <t xml:space="preserve">Glean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корпоративный ИИ-поиск</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series F $150 млн, закрыт 10.06.2025; лид Wellington Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightmatter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фотоника для ИИ-дата-центров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series D $400 млн, закрыт в октябре 2024; лид T. Rowe Price (Fidelity, GV, Viking Global, Lockheed Martin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PsiQuantum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квантовые вычисления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series E $1.0 млрд, объявлен 10.09.2025; лиды BlackRock, Baillie Gifford, Temasek (с NVentures/NVIDIA, QIA, Macquarie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–5 лет (IPO 2029–2030)</t>
+  </si>
+  <si>
     <t xml:space="preserve">По 1X Technologies и Positron AI последние закрытые раунды устарели, поэтому премия 8–15% считается не от них, а от оценки идущего раунда (1X — Series C ~$10 млрд; Positron — первый транш ~$3.5 млрд).</t>
   </si>
   <si>
@@ -753,6 +786,138 @@
   </si>
   <si>
     <t xml:space="preserve">• СП по TikTok в США закрыто 22.01.2026 (Oracle, Silver Lake, MGX по 15%); IPO отложено решением совета (май 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Вторичные сделки идут по $44–47 за акцию против $49.09 в Series F — дисконт около 10% к раунду.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">верх диапазона корпоративного софта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datadog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ServiceNow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue — после падения мультипликаторов в 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARR превысил $300 млн (май 2026), рост 89% г/г — утроение за 15 месяцев ($100 млн в начале 2025 → $200 млн в декабре → $300 млн в мае). Триггер для IPO аналитики видят на $500 млн — $1 млрд ARR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продажа стратегу по нижней границе (прецедент: Workday купил Sana за $1.1 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2028 в диапазоне $15–20 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лидер категории корпоративного ИИ-поиска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series F $150 млн @ $7.2 млрд: 10.06.2025, лид Wellington Management; раунда 2026 года нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ARR &gt;$300 млн (28.05.2026), +89% г/г; более 1 млн пользователей; всего привлечено ~$765 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Вторичный рынок: $44–47/акция против $49.09 в раунде (дисконт ~10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Риск: часть выручки — потребление, а не подписка; мультипликаторы корпоративного софта в 2026 сжались</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Вторичный рынок оценивает компанию примерно в $4.6 млрд (Forge $84.48, Hiive $89.53 за акцию, 21.08.2026) — вблизи оценки Series D двухлетней давности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumentum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оптические компоненты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTM EV/Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coherent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оптика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка не раскрывается. Ставка на переход отрасли к оптическим соединениям между чипами: рынок оптики для ИИ-дата-центров растёт с $13.7 млрд (2024) до прогнозных $144 млрд к 2030 году.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продажа стратегу по прецеденту Celestial AI (Marvell, $3.25 млрд + earnout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO или продажа стратегу при выходе технологии в серию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стандарт отрасли по оптическим соединениям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series D $400 млн @ $4.4 млрд: октябрь 2024, лид T. Rowe Price; новых раундов нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Вторичный рынок ~$4.6 млрд: Forge и Hiive, 21.08.2026; всего привлечено ~$850 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Июнь 2026: вошла в экосистему NVIDIA NVLink Fusion; август 2026 — возглавила рабочую группу Open Compute Project из 19 компаний</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Прецедент M&amp;A: Marvell закрыл покупку Celestial AI 02.02.2026 за $3.25 млрд (до $5.5 млрд с earnout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Биржевых котировок нет; вторичное размещение открыто 12.08.2026. Диапазон рассчитан как премия 8–15% к оценке Series E.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IonQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">капитализация $16.5 млрд к выручке FY26 $280–290 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rigetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">капитализация $4.8 млрд к выручке ~$24 млн — премия за ожидания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Wave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">капитализация $6.9 млрд к выручке ~$44 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantinuum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оценка на IPO 04.06.2026, $ млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компания до выручки: все поступления — государственные и партнёрские контракты. Одна из двух компаний (вместе с Microsoft) в стадии C программы DARPA QBI. Публичные квантовые компании торгуются по 50–200 годовых выручек — сектор оценивают по ожиданиям, а не по финансам.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка остаётся вблизи Series E ($8 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2029–30 с премией к Quantinuum ($15.6 млрд на листинге в июне 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый в мире отказоустойчивый квантовый компьютер выходит в серию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series E $1.0 млрд @ $7 млрд: 10.09.2025; лиды BlackRock, Baillie Gifford, Temasek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Всего мобилизовано ~$3.5–3.7 млрд: ~$2.3 млрд частных + A$940 млн Австралия + &gt;$500 млн Иллинойс + $125 млн DARPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Окно выхода открылось: Quantinuum вышел на Nasdaq 04.06.2026, привлёк $1.68 млрд при оценке ~$15.6 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Риски: перенос площадки в Брисбене и сдвиг сроков к 2029–2030, аудит ANAO по австралийской сделке, временный CEO (Виктор Пенг с 10.02.2026), недоказанная отказоустойчивость фотонного подхода</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1485,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1916,14 +2081,188 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>53</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <f aca="false">Glean!B6</f>
+        <v>7.2</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <f aca="false">Glean!B7</f>
+        <v>7.2</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <f aca="false">Glean!B10</f>
+        <v>6.5</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <f aca="false">Glean!B11</f>
+        <v>7</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <f aca="false">Glean!B12</f>
+        <v>6.75</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <f aca="false">Glean!B36</f>
+        <v>18</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <f aca="false">Glean!B37</f>
+        <v>2.66666666666667</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <f aca="false">Glean!B38</f>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <f aca="false">Glean!B39</f>
+        <v>0.480428689948613</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <f aca="false">Glean!B40</f>
+        <v>1.06666666666667</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <f aca="false">Glean!C40</f>
+        <v>5.55555555555556</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <f aca="false">Lightmatter!B6</f>
+        <v>4.4</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <f aca="false">Lightmatter!B7</f>
+        <v>4.4</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <f aca="false">Lightmatter!B10</f>
+        <v>4.4</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <f aca="false">Lightmatter!B11</f>
+        <v>4.8</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <f aca="false">Lightmatter!B12</f>
+        <v>4.6</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <f aca="false">Lightmatter!B36</f>
+        <v>14</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <f aca="false">Lightmatter!B37</f>
+        <v>3.04347826086957</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <f aca="false">Lightmatter!B38</f>
+        <v>2.04347826086957</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <f aca="false">Lightmatter!B39</f>
+        <v>0.374376664163408</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <f aca="false">Lightmatter!B40</f>
+        <v>0.869565217391304</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <f aca="false">Lightmatter!C40</f>
+        <v>9.78260869565217</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <f aca="false">PsiQuantum!B6</f>
+        <v>7</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <f aca="false">PsiQuantum!B7</f>
+        <v>7</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <f aca="false">PsiQuantum!B10</f>
+        <v>7.56</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <f aca="false">PsiQuantum!B11</f>
+        <v>8.05</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <f aca="false">PsiQuantum!B12</f>
+        <v>7.805</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <f aca="false">PsiQuantum!B36</f>
+        <v>30</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <f aca="false">PsiQuantum!B37</f>
+        <v>3.84368994234465</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <f aca="false">PsiQuantum!B38</f>
+        <v>2.84368994234465</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <f aca="false">PsiQuantum!B39</f>
+        <v>0.348789191809236</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <f aca="false">PsiQuantum!B40</f>
+        <v>0.960922485586163</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <f aca="false">PsiQuantum!C40</f>
+        <v>11.2107623318386</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1964,7 +2303,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1977,7 +2316,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>46</v>
@@ -1985,7 +2324,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>30</v>
@@ -1993,7 +2332,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>30</v>
@@ -2001,7 +2340,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2009,7 +2348,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2017,7 +2356,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>23</v>
@@ -2025,7 +2364,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>28</v>
@@ -2033,7 +2372,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -2042,15 +2381,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2066,59 +2405,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>6.1</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>4.7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>3.2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2131,39 +2470,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -2193,10 +2532,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -2226,10 +2565,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -2259,12 +2598,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2277,42 +2616,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>30</v>
@@ -2332,16 +2671,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>60</v>
@@ -2361,16 +2700,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
@@ -2390,7 +2729,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2403,7 +2742,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -2430,7 +2769,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -2439,7 +2778,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -2452,7 +2791,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -2461,7 +2800,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2474,27 +2813,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2535,7 +2874,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2548,7 +2887,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>50</v>
@@ -2556,7 +2895,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>425</v>
@@ -2564,7 +2903,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>425</v>
@@ -2572,7 +2911,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2580,7 +2919,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2588,7 +2927,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>590</v>
@@ -2596,7 +2935,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>610</v>
@@ -2604,7 +2943,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -2613,15 +2952,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2637,59 +2976,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>7.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>10.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>4.5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2702,39 +3041,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -2764,10 +3103,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -2797,10 +3136,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -2830,12 +3169,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2848,42 +3187,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>600</v>
@@ -2903,16 +3242,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>850</v>
@@ -2932,16 +3271,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>1200</v>
@@ -2961,7 +3300,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2974,7 +3313,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3001,7 +3340,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3010,7 +3349,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3023,7 +3362,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3032,7 +3371,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3045,27 +3384,1764 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>7.2</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>1.06666666666667</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>0.0327955589886444</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>18</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>2.66666666666667</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.480428689948613</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>37.5</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>5.55555555555556</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>4.55555555555556</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.632222214349522</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>1.48148148148148</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>0.481481481481481</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.217161238900369</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.66666666666667</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.480428689948613</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>4.44444444444445</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>3.44444444444444</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.531407286347922</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.66666666666667</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.66666666666667</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.480428689948613</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>1.06666666666667</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>5.55555555555556</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.57142857142857</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>4</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.869565217391304</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.130434782608696</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.0455187827608644</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>14</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>3.04347826086957</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>2.04347826086957</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.374376664163408</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>45</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>9.78260869565217</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>8.78260869565217</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.659973062335149</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>1.19565217391304</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>0.195652173913044</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.0613736119811017</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>3.04347826086957</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>2.04347826086957</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.374376664163408</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>7.60869565217391</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>6.60869565217391</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.569808635945926</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>3.04347826086957</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>2.04347826086957</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.374376664163408</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.869565217391304</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>9.78260869565217</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.91666666666667</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="17" t="n">
+        <f aca="false">B7*(1+B8)</f>
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <f aca="false">B7*(1+B9)</f>
+        <v>8.05</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>7.805</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>7.5</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.960922485586163</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.0390775144138372</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.011324400291871</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>30</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>3.84368994234465</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>2.84368994234465</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.348789191809236</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>87.5</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>11.2107623318386</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>10.2107623318386</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.551825034479653</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>1.02498398462524</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>0.0249839846252402</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.00707548168948358</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>3.84368994234465</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>2.84368994234465</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.348789191809236</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>8.96860986547085</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>7.96860986547085</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.490125172928693</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>3.84368994234465</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>2.84368994234465</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.348789191809236</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.960922485586163</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>11.2107623318386</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>3.72670807453416</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3093,7 +5169,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3101,71 +5177,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3206,7 +5282,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3219,7 +5295,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>19</v>
@@ -3227,7 +5303,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>852</v>
@@ -3235,7 +5311,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>852</v>
@@ -3243,7 +5319,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3251,7 +5327,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3259,7 +5335,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B7*(1+B8)</f>
@@ -3268,7 +5344,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B7*(1+B9)</f>
@@ -3277,7 +5353,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3286,15 +5362,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3310,70 +5386,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3386,39 +5462,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -3448,10 +5524,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -3481,10 +5557,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -3514,12 +5590,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3532,42 +5608,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>1000</v>
@@ -3587,16 +5663,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1550</v>
@@ -3616,16 +5692,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>2200</v>
@@ -3645,7 +5721,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3658,7 +5734,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3685,7 +5761,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3694,7 +5770,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3707,7 +5783,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3716,7 +5792,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3729,22 +5805,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +5861,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3798,7 +5874,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>23</v>
@@ -3806,7 +5882,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>39</v>
@@ -3814,7 +5890,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>39</v>
@@ -3822,7 +5898,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3830,7 +5906,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3838,7 +5914,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -3846,7 +5922,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>33</v>
@@ -3854,7 +5930,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3863,15 +5939,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3887,70 +5963,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.6</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3963,39 +6039,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -4025,10 +6101,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -4058,10 +6134,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -4091,12 +6167,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4109,42 +6185,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>39</v>
@@ -4164,16 +6240,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>95</v>
@@ -4193,16 +6269,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>180</v>
@@ -4222,7 +6298,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4235,7 +6311,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4262,7 +6338,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4271,7 +6347,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4284,7 +6360,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4293,7 +6369,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4306,22 +6382,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4362,7 +6438,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4375,7 +6451,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -4383,7 +6459,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>10</v>
@@ -4391,7 +6467,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -4399,7 +6475,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4407,7 +6483,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4415,7 +6491,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>10.5</v>
@@ -4423,7 +6499,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>12</v>
@@ -4431,7 +6507,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4440,15 +6516,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4464,48 +6540,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4518,39 +6594,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -4580,10 +6656,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -4613,10 +6689,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -4646,12 +6722,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4664,42 +6740,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -4719,16 +6795,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>38</v>
@@ -4748,16 +6824,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>90</v>
@@ -4777,7 +6853,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4790,7 +6866,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4817,7 +6893,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4826,7 +6902,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4839,7 +6915,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4848,7 +6924,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4861,22 +6937,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4917,7 +6993,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4930,7 +7006,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>31</v>
@@ -4938,7 +7014,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>15</v>
@@ -4946,7 +7022,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>15</v>
@@ -4954,7 +7030,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4962,7 +7038,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4970,7 +7046,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>13.5</v>
@@ -4978,7 +7054,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>15</v>
@@ -4986,7 +7062,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4995,15 +7071,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5019,70 +7095,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5095,39 +7171,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -5157,10 +7233,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -5190,10 +7266,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -5223,12 +7299,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5241,42 +7317,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
@@ -5296,16 +7372,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>45</v>
@@ -5325,16 +7401,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
@@ -5354,7 +7430,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5367,7 +7443,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5394,7 +7470,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5403,7 +7479,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5416,7 +7492,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5425,7 +7501,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5438,22 +7514,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5494,7 +7570,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5507,7 +7583,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>35</v>
@@ -5515,7 +7591,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>22</v>
@@ -5523,7 +7599,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>22</v>
@@ -5531,7 +7607,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5539,7 +7615,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5547,7 +7623,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -5555,7 +7631,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>40</v>
@@ -5563,7 +7639,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5572,15 +7648,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5596,59 +7672,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5661,39 +7737,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -5723,10 +7799,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -5756,10 +7832,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -5789,12 +7865,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5807,42 +7883,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>40</v>
@@ -5862,16 +7938,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>78</v>
@@ -5891,16 +7967,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>150</v>
@@ -5920,7 +7996,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5933,7 +8009,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5960,7 +8036,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5969,7 +8045,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5982,7 +8058,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5991,7 +8067,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6004,22 +8080,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -6060,7 +8136,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6073,7 +8149,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>39</v>
@@ -6081,7 +8157,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -6089,7 +8165,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>3.5</v>
@@ -6097,7 +8173,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6105,7 +8181,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6113,7 +8189,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>4.5</v>
@@ -6121,7 +8197,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5</v>
@@ -6129,7 +8205,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6138,15 +8214,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6162,59 +8238,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6227,39 +8303,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -6289,10 +8365,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -6322,10 +8398,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -6355,12 +8431,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6373,42 +8449,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5</v>
@@ -6428,16 +8504,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>24.2</v>
@@ -6457,16 +8533,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>40</v>
@@ -6486,7 +8562,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6499,7 +8575,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -6526,7 +8602,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -6535,7 +8611,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6548,7 +8624,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -6557,7 +8633,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6570,22 +8646,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -6626,7 +8702,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6639,7 +8715,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -6647,7 +8723,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>190</v>
@@ -6655,7 +8731,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>190</v>
@@ -6663,7 +8739,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6671,7 +8747,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6679,7 +8755,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>195</v>
@@ -6687,7 +8763,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>210</v>
@@ -6695,7 +8771,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6704,15 +8780,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6728,59 +8804,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6793,39 +8869,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -6855,10 +8931,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -6888,10 +8964,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -6921,12 +8997,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6939,42 +9015,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>190</v>
@@ -6994,16 +9070,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>426</v>
@@ -7023,16 +9099,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>600</v>
@@ -7052,7 +9128,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -7065,7 +9141,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -7092,7 +9168,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -7101,7 +9177,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -7114,7 +9190,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -7123,7 +9199,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -7136,22 +9212,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -809,7 +809,7 @@
     <t xml:space="preserve">Продажа стратегу по нижней границе (прецедент: Workday купил Sana за $1.1 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO 2028 в диапазоне $15–20 млрд</t>
+    <t xml:space="preserve">IPO 2028 в верхней части диапазона $20–25 млрд</t>
   </si>
   <si>
     <t xml:space="preserve">Лидер категории корпоративного ИИ-поиска</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">• Риск: часть выручки — потребление, а не подписка; мультипликаторы корпоративного софта в 2026 сжались</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Вторичный рынок оценивает компанию примерно в $4.6 млрд (Forge $84.48, Hiive $89.53 за акцию, 21.08.2026) — вблизи оценки Series D двухлетней давности.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Вторичные сделки идут с небольшой премией к Series D двухлетней давности: Forge $84.48, Hiive $89.53 за акцию (21.08.2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Lumentum</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">• Прецедент M&amp;A: Marvell закрыл покупку Celestial AI 02.02.2026 за $3.25 млрд (до $5.5 млрд с earnout)</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон = премия 8–15% к оценке последнего раунда. Биржевых котировок нет; вторичное размещение открыто 12.08.2026. Диапазон рассчитан как премия 8–15% к оценке Series E.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Вторичные сделки идут с дисконтом к Series E: бумага доступна дешевле оценки раунда, размещение открыто 12.08.2026.</t>
   </si>
   <si>
     <t xml:space="preserve">IonQ</t>
@@ -2116,19 +2116,19 @@
       </c>
       <c r="J14" s="6" t="n">
         <f aca="false">Glean!B36</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K14" s="8" t="n">
         <f aca="false">Glean!B37</f>
-        <v>2.66666666666667</v>
+        <v>3.7037037037037</v>
       </c>
       <c r="L14" s="9" t="n">
         <f aca="false">Glean!B38</f>
-        <v>1.66666666666667</v>
+        <v>2.7037037037037</v>
       </c>
       <c r="M14" s="9" t="n">
         <f aca="false">Glean!B39</f>
-        <v>0.480428689948613</v>
+        <v>0.688318947040394</v>
       </c>
       <c r="N14" s="8" t="n">
         <f aca="false">Glean!B40</f>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="O14" s="8" t="n">
         <f aca="false">Glean!C40</f>
-        <v>5.55555555555556</v>
+        <v>7.40740740740741</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2159,42 +2159,42 @@
       </c>
       <c r="F15" s="6" t="n">
         <f aca="false">Lightmatter!B10</f>
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G15" s="6" t="n">
         <f aca="false">Lightmatter!B11</f>
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H15" s="6" t="n">
         <f aca="false">Lightmatter!B12</f>
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>40</v>
       </c>
       <c r="J15" s="6" t="n">
         <f aca="false">Lightmatter!B36</f>
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="K15" s="8" t="n">
         <f aca="false">Lightmatter!B37</f>
-        <v>3.04347826086957</v>
+        <v>3.89473684210526</v>
       </c>
       <c r="L15" s="9" t="n">
         <f aca="false">Lightmatter!B38</f>
-        <v>2.04347826086957</v>
+        <v>2.89473684210526</v>
       </c>
       <c r="M15" s="9" t="n">
         <f aca="false">Lightmatter!B39</f>
-        <v>0.374376664163408</v>
+        <v>0.474714783552312</v>
       </c>
       <c r="N15" s="8" t="n">
         <f aca="false">Lightmatter!B40</f>
-        <v>0.869565217391304</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="O15" s="8" t="n">
         <f aca="false">Lightmatter!C40</f>
-        <v>9.78260869565217</v>
+        <v>9.47368421052632</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2217,42 +2217,42 @@
       </c>
       <c r="F16" s="6" t="n">
         <f aca="false">PsiQuantum!B10</f>
-        <v>7.56</v>
+        <v>6</v>
       </c>
       <c r="G16" s="6" t="n">
         <f aca="false">PsiQuantum!B11</f>
-        <v>8.05</v>
+        <v>6.5</v>
       </c>
       <c r="H16" s="6" t="n">
         <f aca="false">PsiQuantum!B12</f>
-        <v>7.805</v>
+        <v>6.25</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>61</v>
       </c>
       <c r="J16" s="6" t="n">
         <f aca="false">PsiQuantum!B36</f>
-        <v>30</v>
+        <v>33.75</v>
       </c>
       <c r="K16" s="8" t="n">
         <f aca="false">PsiQuantum!B37</f>
-        <v>3.84368994234465</v>
+        <v>5.4</v>
       </c>
       <c r="L16" s="9" t="n">
         <f aca="false">PsiQuantum!B38</f>
-        <v>2.84368994234465</v>
+        <v>4.4</v>
       </c>
       <c r="M16" s="9" t="n">
         <f aca="false">PsiQuantum!B39</f>
-        <v>0.348789191809236</v>
+        <v>0.454635455255861</v>
       </c>
       <c r="N16" s="8" t="n">
         <f aca="false">PsiQuantum!B40</f>
-        <v>0.960922485586163</v>
+        <v>1.2</v>
       </c>
       <c r="O16" s="8" t="n">
         <f aca="false">PsiQuantum!C40</f>
-        <v>11.2107623318386</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3694,26 +3694,26 @@
         <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>0.9</v>
+        <v>1.25</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>20</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.66666666666667</v>
+        <v>3.7037037037037</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.66666666666667</v>
+        <v>2.7037037037037</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.480428689948613</v>
+        <v>0.688318947040394</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3727,26 +3727,26 @@
         <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>25</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>5.55555555555556</v>
+        <v>7.40740740740741</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>4.55555555555556</v>
+        <v>6.40740740740741</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.632222214349522</v>
+        <v>0.772050385209221</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3836,19 +3836,19 @@
         <v>258</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.66666666666667</v>
+        <v>3.7037037037037</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.66666666666667</v>
+        <v>2.7037037037037</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.480428689948613</v>
+        <v>0.688318947040394</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3865,19 +3865,19 @@
         <v>259</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>4.44444444444445</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>3.44444444444444</v>
+        <v>5.66666666666667</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.531407286347922</v>
+        <v>0.719501256105151</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.66666666666667</v>
+        <v>3.7037037037037</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.66666666666667</v>
+        <v>2.7037037037037</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.480428689948613</v>
+        <v>0.688318947040394</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>5.55555555555556</v>
+        <v>7.40740740740741</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.57142857142857</v>
+        <v>3.57142857142857</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4083,7 +4083,7 @@
         <v>88</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4091,7 +4091,7 @@
         <v>89</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4254,15 +4254,15 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.869565217391304</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.130434782608696</v>
+        <v>-0.157894736842105</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.0455187827608644</v>
+        <v>-0.0556736085826332</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4276,26 +4276,26 @@
         <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>14</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>14</v>
+        <v>18.2</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.04347826086957</v>
+        <v>3.83157894736842</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.04347826086957</v>
+        <v>2.83157894736842</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.374376664163408</v>
+        <v>0.467842186052743</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4320,15 +4320,15 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>9.78260869565217</v>
+        <v>9.47368421052632</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>8.78260869565217</v>
+        <v>8.47368421052632</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.659973062335149</v>
+        <v>0.648178334246327</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4393,15 +4393,15 @@
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.19565217391304</v>
+        <v>1.15789473684211</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.195652173913044</v>
+        <v>0.157894736842105</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0613736119811017</v>
+        <v>0.0500815467556952</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4418,19 +4418,19 @@
         <v>272</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>14</v>
+        <v>18.8</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.04347826086957</v>
+        <v>3.95789473684211</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.04347826086957</v>
+        <v>2.95789473684211</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.374376664163408</v>
+        <v>0.481508230254484</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4451,15 +4451,15 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>7.60869565217391</v>
+        <v>7.36842105263158</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>6.60869565217391</v>
+        <v>6.36842105263158</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.569808635945926</v>
+        <v>0.558654559754822</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>14</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.04347826086957</v>
+        <v>3.89473684210526</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.04347826086957</v>
+        <v>2.89473684210526</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.374376664163408</v>
+        <v>0.474714783552312</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4517,11 +4517,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.869565217391304</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>9.78260869565217</v>
+        <v>9.47368421052632</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.91666666666667</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4664,18 +4664,16 @@
       <c r="A10" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">B7*(1+B8)</f>
-        <v>7.56</v>
+      <c r="B10" s="15" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">B7*(1+B9)</f>
-        <v>8.05</v>
+      <c r="B11" s="15" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4684,7 +4682,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>7.805</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4827,15 +4825,15 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.960922485586163</v>
+        <v>1.2</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.0390775144138372</v>
+        <v>0.2</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.011324400291871</v>
+        <v>0.05347252413815</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4849,26 +4847,26 @@
         <v>4.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>30</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.84368994234465</v>
+        <v>5.28</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.84368994234465</v>
+        <v>4.28</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.348789191809236</v>
+        <v>0.447389161328384</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4893,15 +4891,15 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>11.2107623318386</v>
+        <v>14</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>10.2107623318386</v>
+        <v>13</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.551825034479653</v>
+        <v>0.615797439477897</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4966,15 +4964,15 @@
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.02498398462524</v>
+        <v>1.28</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.0249839846252402</v>
+        <v>0.28</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.00707548168948358</v>
+        <v>0.0730783181118904</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4991,19 +4989,19 @@
         <v>289</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>30</v>
+        <v>34.5</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.84368994234465</v>
+        <v>5.52</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.84368994234465</v>
+        <v>4.52</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.348789191809236</v>
+        <v>0.461757566673481</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5024,15 +5022,15 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>8.96860986547085</v>
+        <v>11.2</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>7.96860986547085</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.490125172928693</v>
+        <v>0.551554064036019</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5054,7 +5052,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>30</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5063,7 +5061,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.84368994234465</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5072,7 +5070,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.84368994234465</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,7 +5079,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.348789191809236</v>
+        <v>0.454635455255861</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5090,11 +5088,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.960922485586163</v>
+        <v>1.2</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>11.2107623318386</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5103,7 +5101,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>3.72670807453416</v>
+        <v>5.19230769230769</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Раунд $122 млрд (крупнейший частный раунд в истории), закрыт 31.03.2026; со-лид SoftBank</t>
   </si>
   <si>
-    <t xml:space="preserve">1–2 года (IPO 2026–2027)</t>
+    <t xml:space="preserve">1–1.5 года (IPO 2026–2027)</t>
   </si>
   <si>
     <t xml:space="preserve">Figure AI</t>
@@ -386,12 +386,12 @@
     <t xml:space="preserve">Базовый</t>
   </si>
   <si>
+    <t xml:space="preserve">Оптимистичный</t>
+  </si>
+  <si>
     <t xml:space="preserve">2028</t>
   </si>
   <si>
-    <t xml:space="preserve">Оптимистичный</t>
-  </si>
-  <si>
     <t xml:space="preserve">Run-rate выручки &gt;$40 млрд (июль 2026), удвоение за год; план компании ~$62 млрд в 2027 и &gt;$280 млрд к 2030. Целевой сценарий — выручка 2028 ~$110 млрд при мультипликаторе 20x (ниже текущих ~21x ARR).</t>
   </si>
   <si>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">Оценка остаётся на уровне Series F ($30 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO 2028 с удвоением к оценке раунда</t>
+    <t xml:space="preserve">IPO 2028 при сохранении темпа роста контрактной выручки</t>
   </si>
   <si>
     <t xml:space="preserve">Ре-рейтинг как инфраструктуры ИИ первого эшелона</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">Оценка остаётся на уровне текущей вторички ($600 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">Следующие раунды выкупа и блок-трейды при росте выручки</t>
+    <t xml:space="preserve">Сокращение разрыва в мультипликаторах с Tencent при росте выручки</t>
   </si>
   <si>
     <t xml:space="preserve">Сокращение разрыва в мультипликаторах с Meta</t>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="M5" s="9" t="n">
         <f aca="false">OpenAI!B39</f>
-        <v>0.297785030013053</v>
+        <v>0.415588460314333</v>
       </c>
       <c r="N5" s="8" t="n">
         <f aca="false">OpenAI!B40</f>
@@ -2000,19 +2000,19 @@
       </c>
       <c r="J12" s="6" t="n">
         <f aca="false">'VAST Data'!B36</f>
-        <v>60</v>
+        <v>81.6</v>
       </c>
       <c r="K12" s="8" t="n">
         <f aca="false">'VAST Data'!B37</f>
-        <v>2.35294117647059</v>
+        <v>3.2</v>
       </c>
       <c r="L12" s="9" t="n">
         <f aca="false">'VAST Data'!B38</f>
-        <v>1.35294117647059</v>
+        <v>2.2</v>
       </c>
       <c r="M12" s="9" t="n">
         <f aca="false">'VAST Data'!B39</f>
-        <v>0.408135436805908</v>
+        <v>0.592428682213989</v>
       </c>
       <c r="N12" s="8" t="n">
         <f aca="false">'VAST Data'!B40</f>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="O12" s="8" t="n">
         <f aca="false">'VAST Data'!C40</f>
-        <v>4.3921568627451</v>
+        <v>5.49019607843137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2058,19 +2058,19 @@
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">ByteDance!B36</f>
-        <v>850</v>
+        <v>1200</v>
       </c>
       <c r="K13" s="8" t="n">
         <f aca="false">ByteDance!B37</f>
-        <v>1.41666666666667</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
         <f aca="false">ByteDance!B38</f>
-        <v>0.416666666666667</v>
+        <v>1</v>
       </c>
       <c r="M13" s="9" t="n">
         <f aca="false">ByteDance!B39</f>
-        <v>0.190238071423808</v>
+        <v>0.414213562373095</v>
       </c>
       <c r="N13" s="8" t="n">
         <f aca="false">ByteDance!B40</f>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="O13" s="8" t="n">
         <f aca="false">ByteDance!C40</f>
-        <v>2.1</v>
+        <v>2.66666666666667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2502,7 +2502,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -2541,31 +2541,31 @@
         <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>24</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>60</v>
+        <v>81.6</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.35294117647059</v>
+        <v>3.2</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.35294117647059</v>
+        <v>2.2</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.408135436805908</v>
+        <v>0.592428682213989</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>147</v>
@@ -2574,26 +2574,26 @@
         <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>28</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>4.3921568627451</v>
+        <v>5.49019607843137</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>3.3921568627451</v>
+        <v>4.49019607843137</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.526237923738988</v>
+        <v>0.626712544544795</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2645,7 +2645,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
@@ -2669,7 +2669,7 @@
         <v>0.0846522890932808</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
         <v>116</v>
       </c>
@@ -2683,24 +2683,24 @@
         <v>229</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>60</v>
+        <v>81.6</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.35294117647059</v>
+        <v>3.2</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.35294117647059</v>
+        <v>2.2</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.408135436805908</v>
+        <v>0.592428682213989</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>147</v>
@@ -2712,19 +2712,19 @@
         <v>230</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>3.92156862745098</v>
+        <v>5.49019607843137</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>2.92156862745098</v>
+        <v>4.49019607843137</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.477610431539711</v>
+        <v>0.626712544544795</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>60</v>
+        <v>81.6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.35294117647059</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.35294117647059</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.408135436805908</v>
+        <v>0.592428682213989</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>4.3921568627451</v>
+        <v>5.49019607843137</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.14285714285714</v>
+        <v>2.91428571428571</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3073,7 +3073,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -3106,37 +3106,37 @@
         <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>850</v>
+        <v>1200</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>1.41666666666667</v>
+        <v>2</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>0.416666666666667</v>
+        <v>1</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.190238071423808</v>
+        <v>0.414213562373095</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>146</v>
@@ -3145,26 +3145,26 @@
         <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>1260</v>
+        <v>1530</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.280579164987494</v>
+        <v>0.366197208047234</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3216,7 +3216,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
@@ -3245,7 +3245,7 @@
         <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
@@ -3254,24 +3254,24 @@
         <v>245</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>850</v>
+        <v>1200</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>1.41666666666667</v>
+        <v>2</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>0.416666666666667</v>
+        <v>1</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.190238071423808</v>
+        <v>0.414213562373095</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>146</v>
@@ -3283,19 +3283,19 @@
         <v>246</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>2</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>1</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.259921049894873</v>
+        <v>0.386722548701269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>850</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>1.41666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>0.416666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.190238071423808</v>
+        <v>0.414213562373095</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>2.1</v>
+        <v>2.66666666666667</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>1.39344262295082</v>
+        <v>1.9672131147541</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3655,7 +3655,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>147</v>
@@ -3798,7 +3798,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>147</v>
@@ -4300,7 +4300,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>197</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>197</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>197</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>197</v>
@@ -5525,10 +5525,10 @@
         <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D26" s="25" t="n">
         <v>110</v>
@@ -5550,15 +5550,15 @@
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.31790692809846</v>
+        <v>0.444928380645306</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>117</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -5664,10 +5664,10 @@
         <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>123</v>
@@ -5685,15 +5685,15 @@
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.277346193137179</v>
+        <v>0.385941259811554</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>117</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.297785030013053</v>
+        <v>0.415588460314333</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6132,7 +6132,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>147</v>
@@ -6267,7 +6267,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>147</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>147</v>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>147</v>
@@ -7201,7 +7201,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -7264,7 +7264,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>147</v>
@@ -7344,7 +7344,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>147</v>
@@ -7767,7 +7767,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -7800,7 +7800,7 @@
         <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -7830,7 +7830,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>146</v>
@@ -7910,7 +7910,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
@@ -7939,7 +7939,7 @@
         <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>146</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>197</v>
@@ -8531,7 +8531,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>197</v>
@@ -8899,7 +8899,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -8932,7 +8932,7 @@
         <v>116</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -8962,7 +8962,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>146</v>
@@ -9042,7 +9042,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
@@ -9071,7 +9071,7 @@
         <v>116</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
@@ -9097,7 +9097,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>146</v>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -14,14 +14,13 @@
     <sheet name="Figure AI" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="1X" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Polymarket" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Kalshi" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Positron AI" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Databricks" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="VAST Data" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="ByteDance" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Glean" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Lightmatter" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="PsiQuantum" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Positron AI" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Databricks" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="VAST Data" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="ByteDance" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Glean" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Lightmatter" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="PsiQuantum" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="283">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
@@ -134,39 +133,30 @@
     <t xml:space="preserve">2–3 года (IPO 2029 или продажа ICE)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalshi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рынки предсказаний (США)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Series F $1 млрд, закрыт 07.05.2026; лид Coatue (Sequoia, a16z, IVP, Paradigm, Morgan Stanley, ARK)</t>
+    <t xml:space="preserve">Positron AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чипы для ИИ (инференс)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series B $230 млн (переподписан), закрыт 04.02.2026; со-лиды ARENA, Jump Trading, Unless; стратеги QIA и Arm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–4 года (IPO / M&amp;A 2029–2030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данные и ИИ для корпораций</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стратегический раунд $5 млрд, закрыт 13.08.2026; лид Coatue (спрос ~$15 млрд)</t>
   </si>
   <si>
     <t xml:space="preserve">1–2 года (IPO 2027–2028)</t>
   </si>
   <si>
-    <t xml:space="preserve">Positron AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чипы для ИИ (инференс)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Series B $230 млн (переподписан), закрыт 04.02.2026; со-лиды ARENA, Jump Trading, Unless; стратеги QIA и Arm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3–4 года (IPO / M&amp;A 2029–2030)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Данные и ИИ для корпораций</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стратегический раунд $5 млрд, закрыт 13.08.2026; лид Coatue (спрос ~$15 млрд)</t>
-  </si>
-  <si>
     <t xml:space="preserve">VAST Data</t>
   </si>
   <si>
@@ -509,13 +499,13 @@
     <t xml:space="preserve">предостерегающий комп: консьюмер-железо без ИИ-рва</t>
   </si>
   <si>
-    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 150–250 тыс. штук к 2029 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $3–4 млрд (базовый сценарий — $3.5 млрд).</t>
+    <t xml:space="preserve">Цель — 100 тыс. роботов/год к концу 2027. Парк 250–350 тыс. штук к 2029 при $20 тыс. за робота или $6 тыс./год подписки даёт выручку $4–6 млрд (базовый сценарий — $5 млрд).</t>
   </si>
   <si>
     <t xml:space="preserve">Оценка на уровне идущего Series C ($10 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">Кратный рост к идущему Series C при выходе NEO на серийные поставки</t>
+    <t xml:space="preserve">Паритет с оценкой Figure AI при лидерстве в домашнем сегменте</t>
   </si>
   <si>
     <t xml:space="preserve">Массовое проникновение домашних роботов</t>
@@ -584,33 +574,6 @@
     <t xml:space="preserve">• ICE: инвестиции до $2 млрд (окт 2025) + дистрибуция данных; партнёрство с X/xAI</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Фактические сделки на вторичном рынке идут около $35 млрд: рынок уже отыгрывает раунд по оценке $40 млрд, который обсуждают Sequoia и Wellington (CoinDesk, 13.08.2026).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">биржа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выручка: $263.5 млн за 2025 → run-rate ~$4 млрд к июлю 2026 (пик ЧМ по футболу). Базовый сценарий консервативен: $6 млрд выручки к 2028 при мультипликаторе биржевых операторов 12x.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка идущего раунда ($40 млрд)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO ~2027–28 при мультипликаторах биржевых операторов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Категория выходит на объёмы $1.5 трлн (Macquarie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Series F $1 млрд @ $22 млрд: TechCrunch/BusinessWire, 07.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Раунд @ $40 млрд в переговорах: CoinDesk, 13.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Выручка 2025 $263.5 млн, run-rate ~$4 млрд (июль 2026); всего привлечено ~$2.8 млрд</t>
-  </si>
-  <si>
     <t xml:space="preserve">База для вторичного рынка, $ млрд (оценка идущего раунда)</t>
   </si>
   <si>
@@ -902,7 +865,7 @@
     <t xml:space="preserve">Оценка остаётся вблизи Series E ($8 млрд)</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO 2029–30 с премией к Quantinuum ($15.6 млрд на листинге в июне 2026)</t>
+    <t xml:space="preserve">IPO 2029–30 с кратной премией к Quantinuum ($15.6 млрд на листинге в июне 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Первый в мире отказоустойчивый квантовый компьютер выходит в серию</t>
@@ -1485,7 +1448,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1652,19 +1615,19 @@
       </c>
       <c r="J6" s="6" t="n">
         <f aca="false">'Figure AI'!B36</f>
-        <v>100</v>
+        <v>72.45</v>
       </c>
       <c r="K6" s="8" t="n">
         <f aca="false">'Figure AI'!B37</f>
-        <v>3.17460317460317</v>
+        <v>2.3</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">'Figure AI'!B38</f>
-        <v>2.17460317460317</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="9" t="n">
         <f aca="false">'Figure AI'!B39</f>
-        <v>0.39104071511099</v>
+        <v>0.268676251376101</v>
       </c>
       <c r="N6" s="8" t="n">
         <f aca="false">'Figure AI'!B40</f>
@@ -1672,7 +1635,7 @@
       </c>
       <c r="O6" s="8" t="n">
         <f aca="false">'Figure AI'!C40</f>
-        <v>6.85714285714286</v>
+        <v>5.71428571428571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1710,19 +1673,19 @@
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">1X!B36</f>
-        <v>40</v>
+        <v>60.75</v>
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">1X!B37</f>
-        <v>3.55555555555556</v>
+        <v>5.4</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">1X!B38</f>
-        <v>2.55555555555556</v>
+        <v>4.4</v>
       </c>
       <c r="M7" s="9" t="n">
         <f aca="false">1X!B39</f>
-        <v>0.660974586154023</v>
+        <v>0.963168169823712</v>
       </c>
       <c r="N7" s="8" t="n">
         <f aca="false">1X!B40</f>
@@ -1730,7 +1693,7 @@
       </c>
       <c r="O7" s="8" t="n">
         <f aca="false">1X!C40</f>
-        <v>9.33333333333333</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1791,7 +1754,7 @@
         <v>7.57894736842105</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
@@ -1802,54 +1765,54 @@
         <v>35</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">Kalshi!B6</f>
-        <v>22</v>
+        <f aca="false">'Positron AI'!B6</f>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">Kalshi!B7</f>
-        <v>22</v>
+        <f aca="false">'Positron AI'!B7</f>
+        <v>3.5</v>
       </c>
       <c r="F9" s="6" t="n">
-        <f aca="false">Kalshi!B10</f>
-        <v>30</v>
+        <f aca="false">'Positron AI'!B10</f>
+        <v>4.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <f aca="false">Kalshi!B11</f>
-        <v>40</v>
+        <f aca="false">'Positron AI'!B11</f>
+        <v>5</v>
       </c>
       <c r="H9" s="6" t="n">
-        <f aca="false">Kalshi!B12</f>
-        <v>35</v>
+        <f aca="false">'Positron AI'!B12</f>
+        <v>4.75</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J9" s="6" t="n">
-        <f aca="false">Kalshi!B36</f>
-        <v>75</v>
+        <f aca="false">'Positron AI'!B36</f>
+        <v>24</v>
       </c>
       <c r="K9" s="8" t="n">
-        <f aca="false">Kalshi!B37</f>
-        <v>2.14285714285714</v>
+        <f aca="false">'Positron AI'!B37</f>
+        <v>5.05263157894737</v>
       </c>
       <c r="L9" s="9" t="n">
-        <f aca="false">Kalshi!B38</f>
-        <v>1.14285714285714</v>
+        <f aca="false">'Positron AI'!B38</f>
+        <v>4.05263157894737</v>
       </c>
       <c r="M9" s="9" t="n">
-        <f aca="false">Kalshi!B39</f>
-        <v>0.4638501094228</v>
+        <f aca="false">'Positron AI'!B39</f>
+        <v>0.588565175565576</v>
       </c>
       <c r="N9" s="8" t="n">
-        <f aca="false">Kalshi!B40</f>
-        <v>1.14285714285714</v>
+        <f aca="false">'Positron AI'!B40</f>
+        <v>1.05263157894737</v>
       </c>
       <c r="O9" s="8" t="n">
-        <f aca="false">Kalshi!C40</f>
-        <v>4.28571428571429</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">'Positron AI'!C40</f>
+        <v>8.42105263157895</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>37</v>
       </c>
@@ -1860,54 +1823,54 @@
         <v>39</v>
       </c>
       <c r="D10" s="6" t="n">
-        <f aca="false">'Positron AI'!B6</f>
-        <v>1</v>
+        <f aca="false">Databricks!B6</f>
+        <v>190</v>
       </c>
       <c r="E10" s="6" t="n">
-        <f aca="false">'Positron AI'!B7</f>
-        <v>3.5</v>
+        <f aca="false">Databricks!B7</f>
+        <v>190</v>
       </c>
       <c r="F10" s="6" t="n">
-        <f aca="false">'Positron AI'!B10</f>
-        <v>4.5</v>
+        <f aca="false">Databricks!B10</f>
+        <v>195</v>
       </c>
       <c r="G10" s="6" t="n">
-        <f aca="false">'Positron AI'!B11</f>
-        <v>5</v>
+        <f aca="false">Databricks!B11</f>
+        <v>210</v>
       </c>
       <c r="H10" s="6" t="n">
-        <f aca="false">'Positron AI'!B12</f>
-        <v>4.75</v>
+        <f aca="false">Databricks!B12</f>
+        <v>202.5</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>40</v>
       </c>
       <c r="J10" s="6" t="n">
-        <f aca="false">'Positron AI'!B36</f>
-        <v>24</v>
+        <f aca="false">Databricks!B36</f>
+        <v>425</v>
       </c>
       <c r="K10" s="8" t="n">
-        <f aca="false">'Positron AI'!B37</f>
-        <v>5.05263157894737</v>
+        <f aca="false">Databricks!B37</f>
+        <v>2.09876543209877</v>
       </c>
       <c r="L10" s="9" t="n">
-        <f aca="false">'Positron AI'!B38</f>
-        <v>4.05263157894737</v>
+        <f aca="false">Databricks!B38</f>
+        <v>1.09876543209877</v>
       </c>
       <c r="M10" s="9" t="n">
-        <f aca="false">'Positron AI'!B39</f>
-        <v>0.588565175565576</v>
+        <f aca="false">Databricks!B39</f>
+        <v>0.448711645600589</v>
       </c>
       <c r="N10" s="8" t="n">
-        <f aca="false">'Positron AI'!B40</f>
-        <v>1.05263157894737</v>
+        <f aca="false">Databricks!B40</f>
+        <v>0.938271604938272</v>
       </c>
       <c r="O10" s="8" t="n">
-        <f aca="false">'Positron AI'!C40</f>
-        <v>8.42105263157895</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">Databricks!C40</f>
+        <v>3.08641975308642</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
@@ -1918,167 +1881,167 @@
         <v>43</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">Databricks!B6</f>
-        <v>190</v>
+        <f aca="false">'VAST Data'!B6</f>
+        <v>30</v>
       </c>
       <c r="E11" s="6" t="n">
-        <f aca="false">Databricks!B7</f>
-        <v>190</v>
+        <f aca="false">'VAST Data'!B7</f>
+        <v>30</v>
       </c>
       <c r="F11" s="6" t="n">
-        <f aca="false">Databricks!B10</f>
-        <v>195</v>
+        <f aca="false">'VAST Data'!B10</f>
+        <v>23</v>
       </c>
       <c r="G11" s="6" t="n">
-        <f aca="false">Databricks!B11</f>
-        <v>210</v>
+        <f aca="false">'VAST Data'!B11</f>
+        <v>28</v>
       </c>
       <c r="H11" s="6" t="n">
-        <f aca="false">Databricks!B12</f>
-        <v>202.5</v>
+        <f aca="false">'VAST Data'!B12</f>
+        <v>25.5</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J11" s="6" t="n">
-        <f aca="false">Databricks!B36</f>
-        <v>425</v>
+        <f aca="false">'VAST Data'!B36</f>
+        <v>81.6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <f aca="false">Databricks!B37</f>
-        <v>2.09876543209877</v>
+        <f aca="false">'VAST Data'!B37</f>
+        <v>3.2</v>
       </c>
       <c r="L11" s="9" t="n">
-        <f aca="false">Databricks!B38</f>
-        <v>1.09876543209877</v>
+        <f aca="false">'VAST Data'!B38</f>
+        <v>2.2</v>
       </c>
       <c r="M11" s="9" t="n">
-        <f aca="false">Databricks!B39</f>
-        <v>0.448711645600589</v>
+        <f aca="false">'VAST Data'!B39</f>
+        <v>0.592428682213989</v>
       </c>
       <c r="N11" s="8" t="n">
-        <f aca="false">Databricks!B40</f>
-        <v>0.938271604938272</v>
+        <f aca="false">'VAST Data'!B40</f>
+        <v>1.17647058823529</v>
       </c>
       <c r="O11" s="8" t="n">
-        <f aca="false">Databricks!C40</f>
-        <v>3.08641975308642</v>
+        <f aca="false">'VAST Data'!C40</f>
+        <v>5.49019607843137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="6" t="n">
-        <f aca="false">'VAST Data'!B6</f>
-        <v>30</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <f aca="false">'VAST Data'!B7</f>
-        <v>30</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <f aca="false">'VAST Data'!B10</f>
-        <v>23</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <f aca="false">'VAST Data'!B11</f>
-        <v>28</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <f aca="false">'VAST Data'!B12</f>
-        <v>25.5</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <f aca="false">'VAST Data'!B36</f>
-        <v>81.6</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <f aca="false">'VAST Data'!B37</f>
-        <v>3.2</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <f aca="false">'VAST Data'!B38</f>
-        <v>2.2</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <f aca="false">'VAST Data'!B39</f>
-        <v>0.592428682213989</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <f aca="false">'VAST Data'!B40</f>
-        <v>1.17647058823529</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <f aca="false">'VAST Data'!C40</f>
-        <v>5.49019607843137</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="6" t="n">
         <f aca="false">ByteDance!B6</f>
         <v>425</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <f aca="false">ByteDance!B7</f>
         <v>425</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <f aca="false">ByteDance!B10</f>
         <v>590</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G12" s="6" t="n">
         <f aca="false">ByteDance!B11</f>
         <v>610</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H12" s="6" t="n">
         <f aca="false">ByteDance!B12</f>
         <v>600</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="6" t="n">
+      <c r="I12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <f aca="false">ByteDance!B36</f>
         <v>1200</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="K12" s="8" t="n">
         <f aca="false">ByteDance!B37</f>
         <v>2</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L12" s="9" t="n">
         <f aca="false">ByteDance!B38</f>
         <v>1</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M12" s="9" t="n">
         <f aca="false">ByteDance!B39</f>
         <v>0.414213562373095</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N12" s="8" t="n">
         <f aca="false">ByteDance!B40</f>
         <v>1</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="O12" s="8" t="n">
         <f aca="false">ByteDance!C40</f>
         <v>2.66666666666667</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <f aca="false">Glean!B6</f>
+        <v>7.2</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <f aca="false">Glean!B7</f>
+        <v>7.2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <f aca="false">Glean!B10</f>
+        <v>6.5</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <f aca="false">Glean!B11</f>
+        <v>7</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <f aca="false">Glean!B12</f>
+        <v>6.75</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <f aca="false">Glean!B36</f>
+        <v>25</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <f aca="false">Glean!B37</f>
+        <v>3.7037037037037</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <f aca="false">Glean!B38</f>
+        <v>2.7037037037037</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <f aca="false">Glean!B39</f>
+        <v>0.688318947040394</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <f aca="false">Glean!B40</f>
+        <v>1.06666666666667</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <f aca="false">Glean!C40</f>
+        <v>7.40740740740741</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2092,54 +2055,54 @@
         <v>54</v>
       </c>
       <c r="D14" s="6" t="n">
-        <f aca="false">Glean!B6</f>
-        <v>7.2</v>
+        <f aca="false">Lightmatter!B6</f>
+        <v>4.4</v>
       </c>
       <c r="E14" s="6" t="n">
-        <f aca="false">Glean!B7</f>
-        <v>7.2</v>
+        <f aca="false">Lightmatter!B7</f>
+        <v>4.4</v>
       </c>
       <c r="F14" s="6" t="n">
-        <f aca="false">Glean!B10</f>
-        <v>6.5</v>
+        <f aca="false">Lightmatter!B10</f>
+        <v>4.5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <f aca="false">Glean!B11</f>
-        <v>7</v>
+        <f aca="false">Lightmatter!B11</f>
+        <v>5</v>
       </c>
       <c r="H14" s="6" t="n">
-        <f aca="false">Glean!B12</f>
-        <v>6.75</v>
+        <f aca="false">Lightmatter!B12</f>
+        <v>4.75</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J14" s="6" t="n">
-        <f aca="false">Glean!B36</f>
-        <v>25</v>
+        <f aca="false">Lightmatter!B36</f>
+        <v>20.425</v>
       </c>
       <c r="K14" s="8" t="n">
-        <f aca="false">Glean!B37</f>
-        <v>3.7037037037037</v>
+        <f aca="false">Lightmatter!B37</f>
+        <v>4.3</v>
       </c>
       <c r="L14" s="9" t="n">
-        <f aca="false">Glean!B38</f>
-        <v>2.7037037037037</v>
+        <f aca="false">Lightmatter!B38</f>
+        <v>3.3</v>
       </c>
       <c r="M14" s="9" t="n">
-        <f aca="false">Glean!B39</f>
-        <v>0.688318947040394</v>
+        <f aca="false">Lightmatter!B39</f>
+        <v>0.517018885214634</v>
       </c>
       <c r="N14" s="8" t="n">
-        <f aca="false">Glean!B40</f>
-        <v>1.06666666666667</v>
+        <f aca="false">Lightmatter!B40</f>
+        <v>0.842105263157895</v>
       </c>
       <c r="O14" s="8" t="n">
-        <f aca="false">Glean!C40</f>
-        <v>7.40740740740741</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">Lightmatter!C40</f>
+        <v>10.6105263157895</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>55</v>
       </c>
@@ -2150,119 +2113,61 @@
         <v>57</v>
       </c>
       <c r="D15" s="6" t="n">
-        <f aca="false">Lightmatter!B6</f>
-        <v>4.4</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <f aca="false">Lightmatter!B7</f>
-        <v>4.4</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <f aca="false">Lightmatter!B10</f>
-        <v>4.5</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <f aca="false">Lightmatter!B11</f>
-        <v>5</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false">Lightmatter!B12</f>
-        <v>4.75</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <f aca="false">Lightmatter!B36</f>
-        <v>18.5</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <f aca="false">Lightmatter!B37</f>
-        <v>3.89473684210526</v>
-      </c>
-      <c r="L15" s="9" t="n">
-        <f aca="false">Lightmatter!B38</f>
-        <v>2.89473684210526</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <f aca="false">Lightmatter!B39</f>
-        <v>0.474714783552312</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <f aca="false">Lightmatter!B40</f>
-        <v>0.842105263157895</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <f aca="false">Lightmatter!C40</f>
-        <v>9.47368421052632</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="6" t="n">
         <f aca="false">PsiQuantum!B6</f>
         <v>7</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E15" s="6" t="n">
         <f aca="false">PsiQuantum!B7</f>
         <v>7</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F15" s="6" t="n">
         <f aca="false">PsiQuantum!B10</f>
         <v>6</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <f aca="false">PsiQuantum!B11</f>
         <v>6.5</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H15" s="6" t="n">
         <f aca="false">PsiQuantum!B12</f>
         <v>6.25</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="6" t="n">
+      <c r="I15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <f aca="false">PsiQuantum!B36</f>
-        <v>33.75</v>
-      </c>
-      <c r="K16" s="8" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <f aca="false">PsiQuantum!B37</f>
-        <v>5.4</v>
-      </c>
-      <c r="L16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="9" t="n">
         <f aca="false">PsiQuantum!B38</f>
-        <v>4.4</v>
-      </c>
-      <c r="M16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" s="9" t="n">
         <f aca="false">PsiQuantum!B39</f>
-        <v>0.454635455255861</v>
-      </c>
-      <c r="N16" s="8" t="n">
+        <v>0.540989091653837</v>
+      </c>
+      <c r="N15" s="8" t="n">
         <f aca="false">PsiQuantum!B40</f>
         <v>1.2</v>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="O15" s="8" t="n">
         <f aca="false">PsiQuantum!C40</f>
-        <v>14</v>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2293,17 +2198,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2316,31 +2221,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>30</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>30</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2348,7 +2253,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2356,40 +2261,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>23</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>28</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>25.5</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2405,59 +2310,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>206</v>
+        <v>98</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>21</v>
+        <v>7.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>6.1</v>
+        <v>10.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2470,140 +2375,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>1.5</v>
+        <v>220</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>30</v>
+        <v>660</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.17647058823529</v>
+        <v>1.1</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.176470588235294</v>
+        <v>0.1</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.0846522890932808</v>
+        <v>0.0488088481701516</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>3.4</v>
+        <v>300</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>81.6</v>
+        <v>1200</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.592428682213989</v>
+        <v>0.414213562373095</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>340</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>28</v>
+        <v>4.5</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>140</v>
+        <v>1530</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>5.49019607843137</v>
+        <v>2.55</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>4.49019607843137</v>
+        <v>1.55</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.626712544544795</v>
+        <v>0.366197208047234</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2616,120 +2521,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="3" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
-        <v>114</v>
-      </c>
       <c r="B32" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.17647058823529</v>
+        <v>1</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.176470588235294</v>
+        <v>0</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0846522890932808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>81.6</v>
+        <v>1200</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.592428682213989</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.414213562373095</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>140</v>
+        <v>1600</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>5.49019607843137</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>4.49019607843137</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.626712544544795</v>
+        <v>0.386722548701269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2742,11 +2647,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>81.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2755,7 +2660,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2764,43 +2669,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.592428682213989</v>
+        <v>0.414213562373095</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.17647058823529</v>
+        <v>1</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>5.49019607843137</v>
+        <v>2.66666666666667</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.91428571428571</v>
+        <v>1.9672131147541</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2813,27 +2718,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2864,17 +2769,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2887,31 +2792,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>425</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>425</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2919,7 +2824,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2927,40 +2832,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>590</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>610</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>600</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2976,59 +2881,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>7.5</v>
+        <v>61</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>10.7</v>
+        <v>21.3</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>4.5</v>
+        <v>20.9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>240</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="C20" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>242</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3041,140 +2957,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>220</v>
+        <v>0.6</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>660</v>
+        <v>7.2</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.1</v>
+        <v>1.06666666666667</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.1</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.0488088481701516</v>
+        <v>0.0327955589886444</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>300</v>
+        <v>1.25</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>1200</v>
+        <v>25</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2</v>
+        <v>3.7037037037037</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1</v>
+        <v>2.7037037037037</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.414213562373095</v>
+        <v>0.688318947040394</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>340</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>1530</v>
+        <v>50</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>2.55</v>
+        <v>7.40740740740741</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>1.55</v>
+        <v>6.40740740740741</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.366197208047234</v>
+        <v>0.772050385209221</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3187,120 +3103,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1</v>
+        <v>1.48148148148148</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0</v>
+        <v>0.481481481481481</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.217161238900369</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>1200</v>
+        <v>25</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2</v>
+        <v>3.7037037037037</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1</v>
+        <v>2.7037037037037</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.414213562373095</v>
+        <v>0.688318947040394</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>1600</v>
+        <v>45</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>2.66666666666667</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>1.66666666666667</v>
+        <v>5.66666666666667</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.386722548701269</v>
+        <v>0.719501256105151</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3313,11 +3229,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>1200</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3326,7 +3242,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2</v>
+        <v>3.7037037037037</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3335,43 +3251,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1</v>
+        <v>2.7037037037037</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.414213562373095</v>
+        <v>0.688318947040394</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1</v>
+        <v>1.06666666666667</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>2.66666666666667</v>
+        <v>7.40740740740741</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>1.9672131147541</v>
+        <v>3.57142857142857</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3384,27 +3300,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3445,7 +3361,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3458,7 +3374,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>54</v>
@@ -3466,23 +3382,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3490,7 +3406,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3498,40 +3414,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>6.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3547,62 +3463,62 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>102</v>
+        <v>253</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>61</v>
+        <v>21.1</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>206</v>
+        <v>95</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>253</v>
+        <v>182</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>20.9</v>
+        <v>14.2</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>167</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>254</v>
+        <v>184</v>
       </c>
       <c r="B21" s="21" t="n">
-        <v>8.2</v>
+        <v>9.4</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>255</v>
@@ -3610,7 +3526,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3623,140 +3539,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.06666666666667</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.0666666666666667</v>
+        <v>-0.157894736842105</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.0327955589886444</v>
+        <v>-0.0556736085826332</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.7037037037037</v>
+        <v>4.27368421052632</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.7037037037037</v>
+        <v>3.27368421052632</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.688318947040394</v>
+        <v>0.5143604724284</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>7.40740740740741</v>
+        <v>10.6105263157895</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>6.40740740740741</v>
+        <v>9.61052631578947</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.772050385209221</v>
+        <v>0.69021339543408</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3769,120 +3685,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.48148148148148</v>
+        <v>1.15789473684211</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.481481481481481</v>
+        <v>0.157894736842105</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.217161238900369</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0500815467556952</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>25</v>
+        <v>20.55</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.7037037037037</v>
+        <v>4.32631578947369</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.7037037037037</v>
+        <v>3.32631578947369</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.688318947040394</v>
+        <v>0.519665702297149</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>6.66666666666667</v>
+        <v>7.36842105263158</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>5.66666666666667</v>
+        <v>6.36842105263158</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.719501256105151</v>
+        <v>0.558654559754822</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3895,11 +3811,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>25</v>
+        <v>20.425</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3908,7 +3824,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.7037037037037</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3917,43 +3833,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.7037037037037</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.688318947040394</v>
+        <v>0.517018885214634</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.06666666666667</v>
+        <v>0.842105263157895</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>7.40740740740741</v>
+        <v>10.6105263157895</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>3.57142857142857</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3966,27 +3882,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -4027,7 +3943,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4040,7 +3956,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>57</v>
@@ -4048,23 +3964,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4072,7 +3988,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4080,40 +3996,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4129,70 +4045,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>21.1</v>
+        <v>58</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>20.6</v>
+        <v>200</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>167</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>194</v>
+        <v>271</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>14.2</v>
+        <v>157</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>10.3</v>
+        <v>15.6</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B21" s="21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4205,140 +4110,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.842105263157895</v>
+        <v>1.2</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.157894736842105</v>
+        <v>0.2</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.0556736085826332</v>
+        <v>0.05347252413815</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>18.2</v>
+        <v>43.5</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.83157894736842</v>
+        <v>6.96</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.83157894736842</v>
+        <v>5.96</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.467842186052743</v>
+        <v>0.539027916855115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>9.47368421052632</v>
+        <v>16.8</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>8.47368421052632</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.648178334246327</v>
+        <v>0.670257789268589</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4351,120 +4256,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="3" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
-        <v>114</v>
-      </c>
       <c r="B32" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.15789473684211</v>
+        <v>1.28</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.157894736842105</v>
+        <v>0.28</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0500815467556952</v>
+        <v>0.0730783181118904</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>18.8</v>
+        <v>44</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.95789473684211</v>
+        <v>7.04</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.95789473684211</v>
+        <v>6.04</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.481508230254484</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.542941569395491</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>7.36842105263158</v>
+        <v>14.4</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>6.36842105263158</v>
+        <v>13.4</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.558654559754822</v>
+        <v>0.624094748995135</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4477,11 +4382,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>18.5</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4490,7 +4395,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.89473684210526</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,43 +4404,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.89473684210526</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.474714783552312</v>
+        <v>0.540989091653837</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.842105263157895</v>
+        <v>1.2</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>9.47368421052632</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>3.7</v>
+        <v>6.73076923076923</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4548,598 +4453,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I48"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <f aca="false">AVERAGE(B10:B11)</f>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B17" s="21" t="n">
-        <v>58</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="B18" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B19" s="21" t="n">
-        <v>157</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="B20" s="21" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D25" s="25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="F25" s="27" t="n">
-        <f aca="false">D25*E25</f>
-        <v>7.5</v>
-      </c>
-      <c r="G25" s="28" t="n">
-        <f aca="false">F25/B12</f>
-        <v>1.2</v>
-      </c>
-      <c r="H25" s="29" t="n">
-        <f aca="false">G25-1</f>
-        <v>0.2</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <f aca="false">G25^(1/C25)-1</f>
-        <v>0.05347252413815</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <f aca="false">D26*E26</f>
-        <v>33</v>
-      </c>
-      <c r="G26" s="28" t="n">
-        <f aca="false">F26/B12</f>
-        <v>5.28</v>
-      </c>
-      <c r="H26" s="29" t="n">
-        <f aca="false">G26-1</f>
-        <v>4.28</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <f aca="false">G26^(1/C26)-1</f>
-        <v>0.447389161328384</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D27" s="25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E27" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F27" s="27" t="n">
-        <f aca="false">D27*E27</f>
-        <v>87.5</v>
-      </c>
-      <c r="G27" s="28" t="n">
-        <f aca="false">F27/B12</f>
-        <v>14</v>
-      </c>
-      <c r="H27" s="29" t="n">
-        <f aca="false">G27-1</f>
-        <v>13</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <f aca="false">G27^(1/C27)-1</f>
-        <v>0.615797439477897</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" s="28" t="n">
-        <f aca="false">E32/B12</f>
-        <v>1.28</v>
-      </c>
-      <c r="G32" s="29" t="n">
-        <f aca="false">F32-1</f>
-        <v>0.28</v>
-      </c>
-      <c r="H32" s="29" t="n">
-        <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0730783181118904</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F33" s="28" t="n">
-        <f aca="false">E33/B12</f>
-        <v>5.52</v>
-      </c>
-      <c r="G33" s="29" t="n">
-        <f aca="false">F33-1</f>
-        <v>4.52</v>
-      </c>
-      <c r="H33" s="29" t="n">
-        <f aca="false">F33^(1/C33)-1</f>
-        <v>0.461757566673481</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="F34" s="28" t="n">
-        <f aca="false">E34/B12</f>
-        <v>11.2</v>
-      </c>
-      <c r="G34" s="29" t="n">
-        <f aca="false">F34-1</f>
-        <v>10.2</v>
-      </c>
-      <c r="H34" s="29" t="n">
-        <f aca="false">F34^(1/C34)-1</f>
-        <v>0.551554064036019</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="17" t="n">
-        <f aca="false">AVERAGE(F26,E33)</f>
-        <v>33.75</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="30" t="n">
-        <f aca="false">B36/B12</f>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="31" t="n">
-        <f aca="false">B37-1</f>
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="31" t="n">
-        <f aca="false">B37^(1/C26)-1</f>
-        <v>0.454635455255861</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="30" t="n">
-        <f aca="false">MIN(G25,F32)</f>
-        <v>1.2</v>
-      </c>
-      <c r="C40" s="30" t="n">
-        <f aca="false">MAX(G27,F34)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B41" s="30" t="n">
-        <f aca="false">B36/B11</f>
-        <v>5.19230769230769</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -5167,7 +4501,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5175,71 +4509,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5280,7 +4614,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5293,7 +4627,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>19</v>
@@ -5301,7 +4635,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>852</v>
@@ -5309,7 +4643,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>852</v>
@@ -5317,7 +4651,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5325,7 +4659,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5333,7 +4667,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B7*(1+B8)</f>
@@ -5342,7 +4676,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B7*(1+B9)</f>
@@ -5351,7 +4685,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5360,15 +4694,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5384,70 +4718,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5460,39 +4794,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -5522,10 +4856,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>1.5</v>
@@ -5555,10 +4889,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -5588,12 +4922,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5606,42 +4940,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>1000</v>
@@ -5661,16 +4995,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1550</v>
@@ -5690,16 +5024,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>2200</v>
@@ -5719,7 +5053,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5732,7 +5066,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5759,7 +5093,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5768,7 +5102,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5781,7 +5115,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5790,7 +5124,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5803,22 +5137,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -5859,7 +5193,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5872,7 +5206,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>23</v>
@@ -5880,7 +5214,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>39</v>
@@ -5888,7 +5222,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>39</v>
@@ -5896,7 +5230,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5904,7 +5238,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5912,7 +5246,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -5920,7 +5254,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>33</v>
@@ -5928,7 +5262,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5937,15 +5271,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5961,70 +5295,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.6</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6037,39 +5371,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -6099,78 +5433,78 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.33333333333333</v>
+        <v>2.28571428571429</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.33333333333333</v>
+        <v>1.28571428571429</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.4105676750826</v>
+        <v>0.266419817374981</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>18</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>6.85714285714286</v>
+        <v>5.71428571428571</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>5.85714285714286</v>
+        <v>4.71428571428571</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.733397063047994</v>
+        <v>0.645412693099038</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6183,42 +5517,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>39</v>
@@ -6238,65 +5572,65 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>95</v>
+        <v>72.9</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.01587301587302</v>
+        <v>2.31428571428571</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.01587301587302</v>
+        <v>1.31428571428571</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.370803351494498</v>
+        <v>0.270922696665602</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>5.71428571428571</v>
+        <v>4.76190476190476</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>4.71428571428571</v>
+        <v>3.76190476190476</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.645412693099038</v>
+        <v>0.561894264347479</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6309,11 +5643,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>100</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6322,7 +5656,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.17460317460317</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6331,21 +5665,21 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.17460317460317</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.39104071511099</v>
+        <v>0.268676251376101</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6353,21 +5687,21 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>6.85714285714286</v>
+        <v>5.71428571428571</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>3.03030303030303</v>
+        <v>2.19545454545455</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6380,22 +5714,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6436,7 +5770,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6449,7 +5783,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -6457,7 +5791,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>10</v>
@@ -6465,7 +5799,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -6473,7 +5807,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6481,7 +5815,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6489,7 +5823,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>10.5</v>
@@ -6497,7 +5831,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>12</v>
@@ -6505,7 +5839,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6514,15 +5848,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6538,48 +5872,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6592,39 +5926,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -6654,78 +5988,78 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>12</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>3.73333333333333</v>
+        <v>5.33333333333333</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>2.73333333333333</v>
+        <v>4.33333333333333</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.693708656418214</v>
+        <v>0.953437367722348</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>9.33333333333333</v>
+        <v>12</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>8.33333333333333</v>
+        <v>11</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.893011990144175</v>
+        <v>1.03393700979443</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6738,42 +6072,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -6793,65 +6127,65 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>38</v>
+        <v>61.5</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>3.37777777777778</v>
+        <v>5.46666666666667</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>2.37777777777778</v>
+        <v>4.46666666666667</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.62724306623747</v>
+        <v>0.972827155851646</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>8</v>
+        <v>10.6666666666667</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>7</v>
+        <v>9.66666666666667</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.811447328527813</v>
+        <v>0.966629242074846</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6864,11 +6198,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>40</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6877,7 +6211,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>3.55555555555556</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6886,21 +6220,21 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>2.55555555555556</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.660974586154023</v>
+        <v>0.963168169823712</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6908,21 +6242,21 @@
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>9.33333333333333</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>3.33333333333333</v>
+        <v>5.0625</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6935,22 +6269,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6991,7 +6325,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7004,7 +6338,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>31</v>
@@ -7012,7 +6346,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>15</v>
@@ -7020,7 +6354,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>15</v>
@@ -7028,7 +6362,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -7036,7 +6370,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -7044,7 +6378,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>13.5</v>
@@ -7052,7 +6386,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>15</v>
@@ -7060,7 +6394,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -7069,15 +6403,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7093,70 +6427,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -7169,39 +6503,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -7231,10 +6565,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -7264,10 +6598,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -7297,12 +6631,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -7315,42 +6649,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
@@ -7370,16 +6704,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>45</v>
@@ -7399,16 +6733,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
@@ -7428,7 +6762,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -7441,7 +6775,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -7468,7 +6802,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -7477,7 +6811,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -7490,7 +6824,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -7499,7 +6833,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -7512,22 +6846,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -7568,7 +6902,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7581,7 +6915,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>35</v>
@@ -7589,23 +6923,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>22</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -7613,7 +6947,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -7621,40 +6955,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>30</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>35</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7670,59 +7004,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>13</v>
+        <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>2</v>
+        <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -7735,140 +7069,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.14285714285714</v>
+        <v>1.89473684210526</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.142857142857143</v>
+        <v>0.894736842105263</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.0690449676496976</v>
+        <v>0.237417631815703</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>72</v>
+        <v>23.8</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.05714285714286</v>
+        <v>5.01052631578947</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.05714285714286</v>
+        <v>4.01052631578947</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.434274331201272</v>
+        <v>0.584771566780115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>4.28571428571429</v>
+        <v>7.57894736842105</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>3.28571428571429</v>
+        <v>6.57894736842105</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.62433052162942</v>
+        <v>0.568442646751593</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -7881,120 +7215,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.14285714285714</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.142857142857143</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0690449676496976</v>
+        <v>0.017244768191101</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>78</v>
+        <v>24.2</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.22857142857143</v>
+        <v>5.09473684210526</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.22857142857143</v>
+        <v>4.09473684210526</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.492840054584358</v>
+        <v>0.592336270065984</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>4.28571428571429</v>
+        <v>8.42105263157895</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>3.28571428571429</v>
+        <v>7.42105263157895</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.62433052162942</v>
+        <v>0.605598573805891</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -8007,11 +7341,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8020,7 +7354,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.14285714285714</v>
+        <v>5.05263157894737</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8029,43 +7363,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.14285714285714</v>
+        <v>4.05263157894737</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.4638501094228</v>
+        <v>0.588565175565576</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.14285714285714</v>
+        <v>1.05263157894737</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>4.28571428571429</v>
+        <v>8.42105263157895</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>1.875</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -8078,22 +7412,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -8134,7 +7468,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8147,7 +7481,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>39</v>
@@ -8155,23 +7489,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>3.5</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -8179,7 +7513,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -8187,32 +7521,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4.5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>4.75</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>193</v>
@@ -8220,7 +7554,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8236,59 +7570,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>24.5</v>
+        <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>16.9</v>
+        <v>10.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8301,140 +7635,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>9</v>
+        <v>252</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.89473684210526</v>
+        <v>1.24444444444444</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.894736842105263</v>
+        <v>0.244444444444444</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.237417631815703</v>
+        <v>0.115546702045434</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>17</v>
+        <v>26.5</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>23.8</v>
+        <v>424</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>5.01052631578947</v>
+        <v>2.09382716049383</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>4.01052631578947</v>
+        <v>1.09382716049383</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.584771566780115</v>
+        <v>0.447006275208863</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>36</v>
+        <v>625</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>7.57894736842105</v>
+        <v>3.08641975308642</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>6.57894736842105</v>
+        <v>2.08641975308642</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.568442646751593</v>
+        <v>0.455967441227165</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -8447,120 +7781,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.05263157894737</v>
+        <v>0.938271604938272</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.0526315789473684</v>
+        <v>-0.0617283950617285</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.017244768191101</v>
+        <v>-0.0313557903242948</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>24.2</v>
+        <v>426</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>5.09473684210526</v>
+        <v>2.1037037037037</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>4.09473684210526</v>
+        <v>1.1037037037037</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.592336270065984</v>
+        <v>0.45041501085162</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>8.42105263157895</v>
+        <v>2.96296296296296</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>7.42105263157895</v>
+        <v>1.96296296296296</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.605598573805891</v>
+        <v>0.436289793354589</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -8573,11 +7907,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>24</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8586,7 +7920,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>5.05263157894737</v>
+        <v>2.09876543209877</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,43 +7929,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>4.05263157894737</v>
+        <v>1.09876543209877</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.588565175565576</v>
+        <v>0.448711645600589</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>1.05263157894737</v>
+        <v>0.938271604938272</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>8.42105263157895</v>
+        <v>3.08641975308642</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>4.8</v>
+        <v>2.02380952380952</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -8644,22 +7978,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -8678,7 +8012,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -8700,7 +8034,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8713,7 +8047,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -8721,23 +8055,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -8745,7 +8079,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -8753,40 +8087,40 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>202.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8802,59 +8136,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>61</v>
+        <v>6.1</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8867,140 +8201,140 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>252</v>
+        <v>30</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>1.24444444444444</v>
+        <v>1.17647058823529</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>0.244444444444444</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>0.115546702045434</v>
+        <v>0.0846522890932808</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>16</v>
+        <v>3.4</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>26.5</v>
+        <v>24</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>424</v>
+        <v>81.6</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.09382716049383</v>
+        <v>3.2</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.09382716049383</v>
+        <v>2.2</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.447006275208863</v>
+        <v>0.592428682213989</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>625</v>
+        <v>140</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>3.08641975308642</v>
+        <v>5.49019607843137</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>2.08641975308642</v>
+        <v>4.49019607843137</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.455967441227165</v>
+        <v>0.626712544544795</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -9013,120 +8347,120 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.938271604938272</v>
+        <v>1.17647058823529</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.0617283950617285</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.0313557903242948</v>
+        <v>0.0846522890932808</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>426</v>
+        <v>81.6</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.1037037037037</v>
+        <v>3.2</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.1037037037037</v>
+        <v>2.2</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.45041501085162</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.592428682213989</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>2.96296296296296</v>
+        <v>5.49019607843137</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>1.96296296296296</v>
+        <v>4.49019607843137</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.436289793354589</v>
+        <v>0.626712544544795</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -9139,11 +8473,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>425</v>
+        <v>81.6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9152,7 +8486,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.09876543209877</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9161,43 +8495,43 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.09876543209877</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.448711645600589</v>
+        <v>0.592428682213989</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.938271604938272</v>
+        <v>1.17647058823529</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>3.08641975308642</v>
+        <v>5.49019607843137</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.02380952380952</v>
+        <v>2.91428571428571</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -9210,22 +8544,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -21,6 +21,10 @@
     <sheet name="Glean" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Lightmatter" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="PsiQuantum" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Waymo" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Plata" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Moonshot AI" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Higgsfield" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="387">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
@@ -211,6 +215,54 @@
     <t xml:space="preserve">4–5 лет (IPO 2029–2030)</t>
   </si>
   <si>
+    <t xml:space="preserve">Waymo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Беспилотное такси</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Раунд $16 млрд, объявлен 02.02.2026; лиды Dragoneer, DST Global, Sequoia; Alphabet вложила ~$13 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–4 года (IPO / спин-офф 2029–30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цифровой банк (Мексика)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series C $405 млн, анонс 16.04.2026; лид Bicycle Capital, вошли QIA, BTG Pactual, Valor Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–4 года (IPO 2029–30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moonshot AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Генеративный ИИ (Китай)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series F более $3.5 млрд, объявлен 29.07.2026; среди лидов — государственный National AI Industry Investment Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 года (IPO Гонконг)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higgsfield AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИИ-видео для рекламы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series B $400 млн, закрыт 17.08.2026; лид DST Global, вошли Goldman Sachs Alternatives, Intel Capital, Mirae Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–3 года (IPO / M&amp;A 2029)</t>
+  </si>
+  <si>
     <t xml:space="preserve">По 1X Technologies и Positron AI последние закрытые раунды устарели, поэтому премия 8–15% считается не от них, а от оценки идущего раунда (1X — Series C ~$10 млрд; Positron — первый транш ~$3.5 млрд).</t>
   </si>
   <si>
@@ -881,6 +933,270 @@
   </si>
   <si>
     <t xml:space="preserve">• Риски: перенос площадки в Брисбене и сдвиг сроков к 2029–2030, аудит ANAO по австралийской сделке, временный CEO (Виктор Пенг с 10.02.2026), недоказанная отказоустойчивость фотонного подхода</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Подтверждённых закрытых сделок вторичного рынка нет: расчётные оценки площадок расходятся в 2.4 раза ($152 / $215 / $364 за акцию). Применена премия 8–15% к оценке раунда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue при выручке $53.7 млрд TTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue, максимум сектора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Revenue — нижняя граница ride-hailing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мультипликатор к текущей выручке к Waymo неприменим: при выручке около $0.4 млрд компания оценена в 250–350x. Метод построен на ПРОГНОЗНОЙ выручке года выхода. Ориентир: ~500 тыс. платных поездок в неделю (март 2026), средний чек около $25 — примерно $0.65 млрд в год; базовый сценарий предполагает рост парка и географии примерно в 20 раз к 2030 году.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замедление экспансии после отзывов и расследований, оценка возвращается к уровню раунда 2026 года</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Спин-офф или IPO при доле около 15% рынка ride-hailing США</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нижняя часть прогноза Deepwater ($350–850 млрд к 2030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунд $16 млрд @ $126 млрд post-money, объявлен 02.02.2026; лиды Dragoneer, DST Global, Sequoia. Часть источников (Fortune) даёт заголовок $110 млрд — это pre-money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Предыдущий раунд: Series C $5.6 млрд @ $45 млрд, октябрь 2024 — рост в 2.8 раза за 15 месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Всего привлечено более $27 млрд; компания сумму официально не раскрывает</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Около 81% последнего раунда — деньги Alphabet и её структур (CapitalG, GV): оценка $126 млрд установлена не полностью независимым рынком</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Флот 3 791 автомобиль (регуляторный документ NHTSA); ~500 тыс. платных поездок в неделю (март 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Безопасность: исследование Swiss Re на 25.3 млн миль — на 88% меньше претензий по ущербу имуществу, на 92% по травмам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Риски: шесть отзывов, три за последние 8 месяцев (май 2026 — весь флот США); открытое расследование NHTSA по школьным автобусам; поездки по фривеям были остановлены с конца мая до 29.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Экономика: убыток сегмента Other Bets $1.8 млрд за Q2 2026 при падении выручки сегмента с $450 до $382 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• IPO: Сундар Пичаи 22.07.2026 подтвердил сохранение Waymo внутри Alphabet. Прогноз спин-оффа за 2–4 года — мнение отдельного управляющего, не консенсус</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Конкуренция: Baidu Apollo Go более 250 тыс. поездок в неделю; Pony.ai заявила безубыточность юнит-экономики в Гуанчжоу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Публичных котировок нет: компания листингуется на EquityZen и Hiive, но цены за пейволлом. Применена премия 8–15% к оценке раунда. Единственная документированная вторичная сделка прошла внутри Series B по $3.1 млрд.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nu Holdings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/S — прибыльный аналог, выручка +39% г/г</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banorte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/S — мексиканский банк с отделениями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inter&amp;Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/S — нижняя граница для необанка Латинской Америки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аннуализированная выручка около $600 млн на кредитном портфеле $800 млн (данные компании, публично не аудированы). Базовый сценарий: рост выручки в 2.7 раза к 2030 году и выход в прибыль, мультипликатор ниже Nubank из-за одного рынка и меньшего масштаба.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост просрочки обгоняет портфель, оценка сжимается к мультипликатору Inter&amp;Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO по публичному ориентиру основателей (~$10 млрд) с поправкой на достигнутую прибыльность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля рынка карт Мексики уровня Nubank в Бразилии при мультипликаторе 8x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series C $405 млн @ $5.0 млрд post-money, анонс 16.04.2026, лид Bicycle Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Траектория оценки: $1.5 млрд (03.2025) → $3.1 млрд (10.2025) → $5.0 млрд (04.2026) — рост в 3.3 раза за 13 месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Всего привлечено более $2 млрд: акционерного минимум $815 млн, долговая линия до $500 млн под управлением Nomura (декабрь 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Третье место в Мексике по числу кредитных карт: более 6.4 млн контрактов (июль 2026), после BBVA (11.8 млн) и Banamex (~10 млн), выше Santander и Banorte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Полная лицензия banca multiple — пятый такой игрок; за первый месяц собрано вкладов около MX$3.7 млрд (~$213 млн)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК, требующий отдельного внимания: просрочка (IMOR) 6.03% в апреле 2026 против ~3.3% по сегменту карт. Системный фон — просрочка банков Мексики выросла на 14.16% в реальном выражении за 1П2026, максимум за 26 лет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Компания НЕ прибыльна: план безубыточности — примерно 2028 год. При этом оценена по 8.3x выручки, почти вровень с прибыльным Nubank (8.5x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Конкуренция: Nu Mexico около 12 млн клиентов и лицензия с апреля 2025; Stori, Klar, Hey Banco, Revolut, Openbank, Mercado Pago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• IPO официально не заявлено; основатели публично называли ориентир около $10 млрд в среднесрочной перспективе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Перед сделкой обязательно запросить квартальную отчётность Banco Plata (prime.platacard.mx): чистый результат, ICAP, стоимость риска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Ликвидного вторичного рынка нет, официальных котировок не существует (Forge показывает оценку $800 млн при реальных $35 млрд). Нижняя граница — премия 8% к закрытому раунду, верхняя отражает идущий pre-IPO раунд по pre-money $50 млрд (финальный клозинг 27.08.2026, уже после даты отсечки).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthropic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оценка / выручка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhipu AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">листинг HKEX, оценка ~$112 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MiniMax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">листинг HKEX, оценка ~$33 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baidu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/S — капитализация $35.6 млрд почти равна оценке Moonshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Годовая выручка выросла со $100 млн до $300 млн за март–июнь 2026, более 70% приходится на API. ВАЖНО: текущий мультипликатор — около 117x выручки против 15–21x у OpenAI и Anthropic, то есть тезис «дешёвая альтернатива Западу» по оценке НЕ подтверждается. Базовый сценарий закладывает четырёхкратный рост выручки к листингу и сжатие мультипликатора.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дисконт за нерешённый механизм переноса прав иностранных акционеров при демонтаже VIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO в Гонконге между MiniMax (~$33 млрд) и Zhipu AI (~$112 млрд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка на уровне Zhipu AI после листинга</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series F более $3.5 млрд @ ~$35 млрд post-money, объявлен 29.07.2026; книга переподписана более чем втрое при цели $1–2 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Идущий pre-IPO раунд по pre-money $50 млрд НЕ закрыт на дату отсечки: заявленный финальный клозинг — 27.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Оценка выросла в 8 раз за 8 месяцев: $4.3 млрд (12.2025) → $35 млрд (07.2026), шесть раундов за год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Всего привлечено ~$7.7–8.3 млрд по подтверждённым раундам; единой официальной цифры нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ГЛАВНОЕ ОГРАНИЧЕНИЕ ДОСТУПА: с мая 2026 по требованию CSRC идёт демонтаж офшорной структуры VIE. Компания сообщила акционерам, что механизм переноса прав зарубежных акционеров ЕЩЁ НЕ ОПРЕДЕЛЁН; среди вариантов — продажа офшорных долей. Риск принудительного выхода вместо участия в IPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Для инвесторов из США действует Outbound Investment Security Program (EO 14105, кодифицирован в NDAA FY2026): категория ИИ охвачена прямо. Вход требует отдельной юридической проработки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Kimi K3 — первое место среди моделей с открытыми весами (Artificial Analysis Intelligence Index 60), первое место в мире на Frontend Code Arena (Elo 1679), SWE-bench Verified 93.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Годовая выручка $100 → $200 → $300 млн за март–июнь 2026, более 70% из API, при базе всего 7.45 млн MAU против 382 млн у Doubao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• IPO: Гонконг, заявка НЕ подана на дату отсечки; таргет подачи — до 30.09.2026, листинг конец 2026 / Q1 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Риски: DeepSeek дешевле в 7–17 раз и срезал цены ещё вдвое в августе; MAU минус 47% г/г на рынке, растущем на 85%; Alibaba владеет ~36% и конкурирует напрямую через Qwen; аудированной отчётности нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Легальные прокси для западного инвестора: акции Alibaba (~36% Moonshot), Tencent, Meituan, либо публичные Zhipu AI и MiniMax на HKEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Подтверждённых сделок нет: листинги на Forge, EquityZen и Nasdaq Private Market есть, котировок нет. Данные агрегаторов противоречат друг другу вдвое и противоречат подтверждённым раундам — не использованы. Применена премия 8–15% к оценке раунда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luma AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оценка / выручка — верх сектора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kling (Kuaishou)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оценка спин-оффа / выручка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higgsfield по заявленной выручке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5.4 млрд / $700 млн — втрое ниже медианы сектора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модель построена НЕ на заявленной компанией выручке $700 млн, а на независимой оценке Sacra (~$230 млн): обратный счёт по медиане сектора (25–30x) даёт около $215 млн, что сходится с Sacra и расходится с заявлением компании втрое. Базовый сценарий: рост втрое к 2029 году от независимой оценки при сжатии мультипликатора до 20x.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потеря доступа к базовым моделям, продажа стратегу за стоимость команды и клиентской базы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO или стратег на уровне Runway и Synthesia с поправкой на более быстрый рост</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка уровня спин-оффа Kling ($15–18 млрд) с премией за рекламный воркфлоу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series B $400 млн @ $5.4 млрд, 17.08.2026, лид DST Global. Рост оценки вчетверо за 8 месяцев (с $1.3 млрд в январе 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• История: seed $8 млн (2024) → Series A $50 млн / GFT (09.2025) → extension $80 млн / Accel @ $1.3 млрд (01.2026) → Series B. Всего привлечено ~$538 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Синдикат сменился с венчурного на кроссовер-стратегический (Goldman Sachs Alternatives, Intel Capital, Mirae, NTT DOCOMO, Liberty Global) — типичная предIPO-конфигурация</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 1: собственной базовой видеомодели у компании НЕТ. Это надстройка поверх Sora 2, Veo 3.1, Kling 3.0, WAN, Seedance. Своя разработка — только Soul, и та в изображениях. Оценивать следует как дистрибуцию, а не как исследовательскую лабораторию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Риск уже реализовался: OpenAI закрывает API Sora 24.09.2026 — Higgsfield теряет компонент, не имея права голоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 2: расследование Forbes от 11.02.2026 установило, что часть роликов в маркетинговых материалах компании — стоковые шаблоны Envato с нанесёнными логотипами, а не ИИ-генерация. Это подрывает доверие ко всем неаудированным заявлениям, включая финансовые</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка $700 млн, 30 млн пользователей, 390 компаний из Fortune 500, положительный денежный поток — ИСКЛЮЧИТЕЛЬНО со слов компании. Независимая оценка Sacra: ~$230 млн. Валовая маржа, CAC, LTV, отток и число платящих не раскрыты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Капиталоэффективность (подтверждается): до Series B привлечено $138 млн против $859 млн у Runway и $1.06 млрд у Luma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Косвенное подтверждение риска ставки на одну модель: OpenAI закрыла Sora, сжигая около $1 млн в день при выручке продукта менее $2.1 млн за всё время</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Отраслевые прогнозы рынка ИИ-видео некорректны (дают «$2 млрд к 2030», хотя четыре игрока уже делают ~$1.65 млрд в год) — в модели не использованы</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1764,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -2160,14 +2476,246 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>60</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <f aca="false">Waymo!B6</f>
+        <v>126</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <f aca="false">Waymo!B7</f>
+        <v>126</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <f aca="false">Waymo!B10</f>
+        <v>136</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <f aca="false">Waymo!B11</f>
+        <v>145</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <f aca="false">Waymo!B12</f>
+        <v>140.5</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <f aca="false">Waymo!B36</f>
+        <v>310</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <f aca="false">Waymo!B37</f>
+        <v>2.20640569395018</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <f aca="false">Waymo!B38</f>
+        <v>1.20640569395018</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <f aca="false">Waymo!B39</f>
+        <v>0.253706333606649</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <f aca="false">Waymo!B40</f>
+        <v>0.889679715302491</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <f aca="false">Waymo!C40</f>
+        <v>4.98220640569395</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <f aca="false">Plata!B6</f>
+        <v>5</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <f aca="false">Plata!B7</f>
+        <v>5</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <f aca="false">Plata!B10</f>
+        <v>5.4</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <f aca="false">Plata!B11</f>
+        <v>5.75</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <f aca="false">Plata!B12</f>
+        <v>5.575</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <f aca="false">Plata!B36</f>
+        <v>12.85</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <f aca="false">Plata!B37</f>
+        <v>2.30493273542601</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <f aca="false">Plata!B38</f>
+        <v>1.30493273542601</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <f aca="false">Plata!B39</f>
+        <v>0.269453053461715</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <f aca="false">Plata!B40</f>
+        <v>0.717488789237668</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <f aca="false">Plata!C40</f>
+        <v>4.66367713004484</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <f aca="false">'Moonshot AI'!B6</f>
+        <v>35</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <f aca="false">'Moonshot AI'!B7</f>
+        <v>35</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <f aca="false">'Moonshot AI'!B10</f>
+        <v>38</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <f aca="false">'Moonshot AI'!B11</f>
+        <v>42</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <f aca="false">'Moonshot AI'!B12</f>
+        <v>40</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <f aca="false">'Moonshot AI'!B36</f>
+        <v>88</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <f aca="false">'Moonshot AI'!B37</f>
+        <v>2.2</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <f aca="false">'Moonshot AI'!B38</f>
+        <v>1.2</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <f aca="false">'Moonshot AI'!B39</f>
+        <v>0.691538111622984</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <f aca="false">'Moonshot AI'!B40</f>
+        <v>0.675</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <f aca="false">'Moonshot AI'!C40</f>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <f aca="false">Higgsfield!B6</f>
+        <v>5.4</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <f aca="false">Higgsfield!B7</f>
+        <v>5.4</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <f aca="false">Higgsfield!B10</f>
+        <v>5.85</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <f aca="false">Higgsfield!B11</f>
+        <v>6.2</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <f aca="false">Higgsfield!B12</f>
+        <v>6.025</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <f aca="false">Higgsfield!B36</f>
+        <v>15.65</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <f aca="false">Higgsfield!B37</f>
+        <v>2.59751037344398</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <f aca="false">Higgsfield!B38</f>
+        <v>1.59751037344398</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <f aca="false">Higgsfield!B39</f>
+        <v>0.464950385062174</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <f aca="false">Higgsfield!B40</f>
+        <v>0.497925311203319</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <f aca="false">Higgsfield!C40</f>
+        <v>7.46887966804979</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2208,7 +2756,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2221,7 +2769,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>47</v>
@@ -2229,7 +2777,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>425</v>
@@ -2237,7 +2785,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>425</v>
@@ -2245,7 +2793,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2253,7 +2801,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2261,7 +2809,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>590</v>
@@ -2269,7 +2817,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>610</v>
@@ -2277,7 +2825,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -2286,15 +2834,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2310,59 +2858,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>7.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>10.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>4.5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2375,39 +2923,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -2437,10 +2985,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -2470,10 +3018,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -2503,12 +3051,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2521,42 +3069,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>600</v>
@@ -2576,16 +3124,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1200</v>
@@ -2605,16 +3153,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>1600</v>
@@ -2634,7 +3182,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2647,7 +3195,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -2674,7 +3222,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -2683,7 +3231,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -2696,7 +3244,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -2705,7 +3253,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -2718,27 +3266,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2779,7 +3327,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2792,7 +3340,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>51</v>
@@ -2800,7 +3348,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>7.2</v>
@@ -2808,7 +3356,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>7.2</v>
@@ -2816,7 +3364,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2824,7 +3372,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2832,7 +3380,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>6.5</v>
@@ -2840,7 +3388,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>7</v>
@@ -2848,7 +3396,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -2857,15 +3405,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2881,70 +3429,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>21.3</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>20.9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>9.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>8.2</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2957,39 +3505,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -3019,10 +3567,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -3052,10 +3600,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -3085,12 +3633,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3103,42 +3651,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -3158,16 +3706,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>25</v>
@@ -3187,16 +3735,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>45</v>
@@ -3216,7 +3764,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3229,7 +3777,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3256,7 +3804,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3265,7 +3813,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3278,7 +3826,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3287,7 +3835,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3300,27 +3848,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +3909,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3374,7 +3922,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>54</v>
@@ -3382,7 +3930,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>4.4</v>
@@ -3390,7 +3938,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>4.4</v>
@@ -3398,7 +3946,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3406,7 +3954,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3414,7 +3962,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>4.5</v>
@@ -3422,7 +3970,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5</v>
@@ -3430,7 +3978,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3439,15 +3987,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3463,70 +4011,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21.1</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>14.2</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3539,39 +4087,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -3601,10 +4149,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -3634,10 +4182,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -3667,12 +4215,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3685,42 +4233,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5.5</v>
@@ -3740,16 +4288,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>20.55</v>
@@ -3769,16 +4317,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>35</v>
@@ -3798,7 +4346,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3811,7 +4359,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3838,7 +4386,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3847,7 +4395,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3860,7 +4408,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3869,7 +4417,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3882,27 +4430,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3943,7 +4491,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3956,7 +4504,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>57</v>
@@ -3964,7 +4512,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>7</v>
@@ -3972,7 +4520,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>7</v>
@@ -3980,7 +4528,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3988,7 +4536,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3996,7 +4544,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>6</v>
@@ -4004,7 +4552,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>6.5</v>
@@ -4012,7 +4560,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4021,15 +4569,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4045,59 +4593,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>58</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>200</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>157</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>15.6</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4110,39 +4658,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3.5</v>
@@ -4172,10 +4720,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>4.5</v>
@@ -4205,10 +4753,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>5.5</v>
@@ -4238,12 +4786,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4256,42 +4804,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>8</v>
@@ -4311,16 +4859,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>44</v>
@@ -4340,16 +4888,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>5.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>90</v>
@@ -4369,7 +4917,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4382,7 +4930,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4409,7 +4957,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4418,7 +4966,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4431,7 +4979,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4440,7 +4988,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4453,27 +5001,2436 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>140.5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>125</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.889679715302491</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.110320284697509</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.0456812087220062</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>280</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>1.99288256227758</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>0.99288256227758</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.217772610845543</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>660</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>4.69750889679715</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>3.69750889679715</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.410275345515255</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>1.06761565836299</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>0.0676156583629892</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>0.0265165931495233</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>340</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.41992882562278</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.41992882562278</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.287235130153444</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>700</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>4.98220640569395</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>3.98220640569395</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.428836722581161</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.20640569395018</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.20640569395018</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.253706333606649</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.889679715302491</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>4.98220640569395</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.13793103448276</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>5.575</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>4</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.717488789237668</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.282511210762332</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.124359081517876</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>11.2</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>2.00896860986547</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>1.00896860986547</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.220572996095137</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>23.4</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>4.19730941704036</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>3.19730941704036</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.375428429644104</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>0.896860986547085</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>-0.103139013452915</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>-0.0426074293387878</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.60089686098655</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.60089686098655</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.314034018722216</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>4.66367713004484</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>3.66367713004484</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.408011908871801</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.30493273542601</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.30493273542601</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.269453053461715</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.717488789237668</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>4.66367713004484</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.23478260869565</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>27</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.675</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.325</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.325</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>84</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>2.1</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>1.1</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.639882997800068</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="23" t="s">
         <v>131</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>200</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>5</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>4</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.903653938715879</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>0.75</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>-0.25</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>92</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.3</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.3</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.742416161578685</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>210</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>5.25</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>4.25</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.941170672751477</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.691538111622984</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.675</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.0952380952381</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>6.025</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.497925311203319</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.502074688796681</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.371783311809605</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>15</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>2.4896265560166</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>1.4896265560166</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.440302395893987</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>40</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>6.63900414937759</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>5.63900414937759</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.717459696556446</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>0.580912863070539</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>-0.419087136929461</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>-0.303789350599289</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.70539419087137</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.70539419087137</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.488991509258602</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>7.46887966804979</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>6.46887966804979</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.776239651542579</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.59751037344398</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.59751037344398</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.464950385062174</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.497925311203319</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>7.46887966804979</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.5241935483871</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -4501,7 +7458,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4509,71 +7466,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4614,7 +7571,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4627,7 +7584,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>19</v>
@@ -4635,7 +7592,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>852</v>
@@ -4643,7 +7600,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>852</v>
@@ -4651,7 +7608,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4659,7 +7616,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4667,7 +7624,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B7*(1+B8)</f>
@@ -4676,7 +7633,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B7*(1+B9)</f>
@@ -4685,7 +7642,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4694,15 +7651,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4718,70 +7675,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4794,39 +7751,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -4856,10 +7813,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>1.5</v>
@@ -4889,10 +7846,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -4922,12 +7879,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4940,42 +7897,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>1000</v>
@@ -4995,16 +7952,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1550</v>
@@ -5024,16 +7981,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>2200</v>
@@ -5053,7 +8010,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5066,7 +8023,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5093,7 +8050,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5102,7 +8059,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5115,7 +8072,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5124,7 +8081,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5137,22 +8094,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -5193,7 +8150,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5206,7 +8163,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>23</v>
@@ -5214,7 +8171,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>39</v>
@@ -5222,7 +8179,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>39</v>
@@ -5230,7 +8187,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5238,7 +8195,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5246,7 +8203,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -5254,7 +8211,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>33</v>
@@ -5262,7 +8219,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5271,15 +8228,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5295,70 +8252,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.6</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5371,39 +8328,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -5433,10 +8390,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -5466,10 +8423,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -5499,12 +8456,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5517,42 +8474,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>39</v>
@@ -5572,16 +8529,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>72.9</v>
@@ -5601,16 +8558,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>150</v>
@@ -5630,7 +8587,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5643,7 +8600,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5670,7 +8627,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5679,7 +8636,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5692,7 +8649,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5701,7 +8658,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5714,22 +8671,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -5770,7 +8727,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5783,7 +8740,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -5791,7 +8748,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>10</v>
@@ -5799,7 +8756,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -5807,7 +8764,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5815,7 +8772,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5823,7 +8780,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>10.5</v>
@@ -5831,7 +8788,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>12</v>
@@ -5839,7 +8796,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5848,15 +8805,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5872,48 +8829,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5926,39 +8883,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -5988,10 +8945,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -6021,10 +8978,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -6054,12 +9011,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6072,42 +9029,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -6127,16 +9084,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>61.5</v>
@@ -6156,16 +9113,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>120</v>
@@ -6185,7 +9142,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6198,7 +9155,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -6225,7 +9182,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -6234,7 +9191,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6247,7 +9204,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -6256,7 +9213,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6269,22 +9226,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -6325,7 +9282,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6338,7 +9295,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>31</v>
@@ -6346,7 +9303,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>15</v>
@@ -6354,7 +9311,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>15</v>
@@ -6362,7 +9319,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6370,7 +9327,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6378,7 +9335,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>13.5</v>
@@ -6386,7 +9343,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>15</v>
@@ -6394,7 +9351,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6403,15 +9360,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6427,70 +9384,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6503,39 +9460,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -6565,10 +9522,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -6598,10 +9555,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -6631,12 +9588,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6649,42 +9606,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
@@ -6704,16 +9661,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>45</v>
@@ -6733,16 +9690,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
@@ -6762,7 +9719,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6775,7 +9732,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -6802,7 +9759,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -6811,7 +9768,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6824,7 +9781,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -6833,7 +9790,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6846,22 +9803,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -6902,7 +9859,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6915,7 +9872,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>35</v>
@@ -6923,7 +9880,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -6931,7 +9888,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>3.5</v>
@@ -6939,7 +9896,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6947,7 +9904,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6955,7 +9912,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>4.5</v>
@@ -6963,7 +9920,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5</v>
@@ -6971,7 +9928,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6980,15 +9937,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7004,59 +9961,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -7069,39 +10026,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -7131,10 +10088,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -7164,10 +10121,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -7197,12 +10154,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -7215,42 +10172,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5</v>
@@ -7270,16 +10227,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>24.2</v>
@@ -7299,16 +10256,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>40</v>
@@ -7328,7 +10285,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -7341,7 +10298,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -7368,7 +10325,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -7377,7 +10334,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -7390,7 +10347,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -7399,7 +10356,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -7412,22 +10369,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -7468,7 +10425,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7481,7 +10438,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>39</v>
@@ -7489,7 +10446,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>190</v>
@@ -7497,7 +10454,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>190</v>
@@ -7505,7 +10462,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -7513,7 +10470,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -7521,7 +10478,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>195</v>
@@ -7529,7 +10486,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>210</v>
@@ -7537,7 +10494,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -7546,15 +10503,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7570,59 +10527,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -7635,39 +10592,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -7697,10 +10654,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -7730,10 +10687,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -7763,12 +10720,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -7781,42 +10738,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>190</v>
@@ -7836,16 +10793,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>426</v>
@@ -7865,16 +10822,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>600</v>
@@ -7894,7 +10851,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -7907,7 +10864,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -7934,7 +10891,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -7943,7 +10900,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -7956,7 +10913,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -7965,7 +10922,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -7978,22 +10935,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -8034,7 +10991,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8047,7 +11004,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -8055,7 +11012,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>30</v>
@@ -8063,7 +11020,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>30</v>
@@ -8071,7 +11028,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -8079,7 +11036,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -8087,7 +11044,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>23</v>
@@ -8095,7 +11052,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>28</v>
@@ -8103,7 +11060,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -8112,15 +11069,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8136,59 +11093,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>6.1</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>4.7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>3.2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8201,39 +11158,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -8263,10 +11220,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -8296,10 +11253,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -8329,12 +11286,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -8347,42 +11304,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>30</v>
@@ -8402,16 +11359,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>81.6</v>
@@ -8431,16 +11388,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>140</v>
@@ -8460,7 +11417,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -8473,7 +11430,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -8500,7 +11457,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -8509,7 +11466,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -8522,7 +11479,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -8531,7 +11488,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -8544,27 +11501,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -25,6 +25,7 @@
     <sheet name="Plata" sheetId="15" state="visible" r:id="rId17"/>
     <sheet name="Moonshot AI" sheetId="16" state="visible" r:id="rId18"/>
     <sheet name="Higgsfield" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Lambda" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="416">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
@@ -263,6 +264,18 @@
     <t xml:space="preserve">2–3 года (IPO / M&amp;A 2029)</t>
   </si>
   <si>
+    <t xml:space="preserve">Lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU-облако для ИИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series E более $1.5 млрд, закрыт 18.11.2025; лид TWG Global совместно с US Innovative Technology Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–3 года (IPO 2027)</t>
+  </si>
+  <si>
     <t xml:space="preserve">По 1X Technologies и Positron AI последние закрытые раунды устарели, поэтому премия 8–15% считается не от них, а от оценки идущего раунда (1X — Series C ~$10 млрд; Positron — первый транш ~$3.5 млрд).</t>
   </si>
   <si>
@@ -1197,6 +1210,81 @@
   </si>
   <si>
     <t xml:space="preserve">• Отраслевые прогнозы рынка ИИ-видео некорректны (дают «$2 млрд к 2030», хотя четыре игрока уже делают ~$1.65 млрд в год) — в модели не использованы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Диапазон отражает разрыв между закрытым раундом ($5.9 млрд, ноябрь 2025) и идущими переговорами о раунде $3 млрд по оценке выше $12 млрд (Bloomberg, 24.08.2026). Опорная точка внутри диапазона — котировка от 13.06.2026, соответствующая оценке около $9 млрд. Прецедент тот же, что по 1X и Positron: закрытый раунд устарел. Оговорка: оценка $5.9 млрд — расчёт Forge, эмитентом не подтверждена; котировки площадок ($39.32 Forge против $43.16 NPM) не переводятся в оценку без fully diluted share count, а данных о фактически исполненных сделках нет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoreWeave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Sales 2026E — главный аналог, выручка Q2'26 $2.58 млрд (+112%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/ARR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Together AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoreWeave TTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV/Sales по прошлой выручке — верх диапазона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка: $425 млн (2024) → run-rate $760 млн (конец 2025) → более $1.5 млрд ожидается по итогам 2026. Базовый сценарий: рост втрое к 2029 году при мультипликаторе 5x — с дисконтом к CoreWeave (6–8x на 2026E) за меньший масштаб. Консервативный сценарий закладывает сжатие мультипликаторов сектора, которое уже происходит: акции CoreWeave потеряли 51% от пика к августу 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сжатие мультипликаторов сектора продолжается, размещение по нижней границе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2027 с дисконтом к CoreWeave по масштабу выручки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мультипликатор уровня Nebius при сохранении темпа роста</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• IPO НЕ состоялось и заявка публично НЕ подана на дату отсечки. Подтверждений конфиденциальной подачи S-1 нет ни в одном первоисточнике — распространённое утверждение об этом восходит к новости о найме Morgan Stanley, J.P. Morgan и Citi (сентябрь 2025). Окно 1П2026 пропущено, ориентир сместился на 2027 год (Bloomberg, 24.08.2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series E более $1.5 млрд, 18.11.2025, лид TWG Global; post-money около $5.9 млрд — расчёт Forge, эмитентом не подтверждён</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Предыдущий раунд: Series D $480 млн @ $2.5 млрд, 19.02.2025 (Andra Capital, SGW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• На 24.08.2026 Bloomberg сообщил о переговорах о раунде $3 млрд при оценке выше $12 млрд — несколько term sheets, сделка НЕ закрыта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Привлечено раздельно: акционерный капитал ~$2.3–2.4 млрд, долг ~$2.4 млрд ($500 млн Macquarie апрель 2024 — первая в отрасли секьюритизация под залог GPU, рейтинг Moody's Baa2; $1 млрд май 2026; $917 млн Morgan Stanley август 2026). Циркулирующая цифра «$3.14 млрд всего» смешивает акции и долг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Выручка: $425 млн (2024) → run-rate $760 млн (конец 2025) → более $1.5 млрд ожидается в 2026. Валовая маржа 1П2025 около 50% (около 61% без продаж железа), убыток TTM около $175 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Контракт с Microsoft от 03.11.2025 назван многомиллиардным, сумма НЕ раскрыта. Бэклог компания не раскрывает — публичной цифры не существует</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Мощность более 320 МВт, заявленная цель — 3 ГВт к 2030 году</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 1 — структура капитала: долг примерно равен акционерному капиталу и обеспечен быстро дешевеющим железом. Цена часа H100 упала с $7–10 до менее $2–4. Срок амортизации GPU в отрасли не устоялся: Amazon сократил с 6 до 5 лет, CoreWeave держит 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 2 — сжатие мультипликаторов уже реализовалось: CoreWeave разместилась по $40, выросла втрое к июню 2025 и потеряла 51% от пика к августу 2026 (минус 33% за три месяца)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 3 — концентрация клиентов не раскрывается; круговая связь с NVIDIA, которая одновременно инвестор, поставщик чипов и держатель лизинга дата-центров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ПОСЛЕ ДАТЫ ОТСЕЧКИ (в расчёте не учтено): 28.08.2026 привлечён ещё $1 млрд долга (JPMorgan) — совокупный долг вырос примерно до $3.4 млрд, больше всего акционерного капитала. 31.08.2026 объявлен шестилетний контракт с Anthropic на сумму около $35 млрд (350 МВт, Nueces County, Техас). Контракт кратно меняет масштаб бизнеса и одновременно резко усиливает концентрацию клиентов — требует пересчёта модели</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Тезисы преимущества: статус NVIDIA Exemplar Cloud и четыре года подряд звание партнёра года NVIDIA; инвестиционный рейтинг Baa2 по долгу под залог GPU; работающий self-serve сегмент (1-Click Clusters, около 30 секунд до доступа) с маржой 61% против 50% по компании</t>
   </si>
 </sst>
 </file>
@@ -1764,7 +1852,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -2708,14 +2796,72 @@
         <v>7.46887966804979</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
         <v>75</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <f aca="false">Lambda!B6</f>
+        <v>5.9</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <f aca="false">Lambda!B7</f>
+        <v>5.9</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <f aca="false">Lambda!B10</f>
+        <v>9</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <f aca="false">Lambda!B11</f>
+        <v>12</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <f aca="false">Lambda!B12</f>
+        <v>10.5</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <f aca="false">Lambda!B36</f>
+        <v>25</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <f aca="false">Lambda!B37</f>
+        <v>2.38095238095238</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <f aca="false">Lambda!B38</f>
+        <v>1.38095238095238</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <f aca="false">Lambda!B39</f>
+        <v>0.41481704664972</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <f aca="false">Lambda!B40</f>
+        <v>0.714285714285714</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <f aca="false">Lambda!C40</f>
+        <v>5.71428571428571</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2756,7 +2902,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2769,7 +2915,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>47</v>
@@ -2777,7 +2923,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>425</v>
@@ -2785,7 +2931,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>425</v>
@@ -2793,7 +2939,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -2801,7 +2947,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -2809,7 +2955,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>590</v>
@@ -2817,7 +2963,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>610</v>
@@ -2825,7 +2971,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -2834,15 +2980,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2858,59 +3004,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>7.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>10.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>4.5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2923,39 +3069,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -2985,10 +3131,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -3018,10 +3164,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -3051,12 +3197,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3069,42 +3215,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>600</v>
@@ -3124,16 +3270,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1200</v>
@@ -3153,16 +3299,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>1600</v>
@@ -3182,7 +3328,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3195,7 +3341,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3222,7 +3368,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3231,7 +3377,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3244,7 +3390,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3253,7 +3399,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3266,27 +3412,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3473,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3340,7 +3486,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>51</v>
@@ -3348,7 +3494,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>7.2</v>
@@ -3356,7 +3502,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>7.2</v>
@@ -3364,7 +3510,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3372,7 +3518,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3380,7 +3526,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>6.5</v>
@@ -3388,7 +3534,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>7</v>
@@ -3396,7 +3542,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3405,15 +3551,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3429,70 +3575,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>21.3</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>20.9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>9.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>8.2</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3505,39 +3651,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -3567,10 +3713,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -3600,10 +3746,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -3633,12 +3779,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3651,42 +3797,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -3706,16 +3852,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>25</v>
@@ -3735,16 +3881,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>45</v>
@@ -3764,7 +3910,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -3777,7 +3923,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -3804,7 +3950,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -3813,7 +3959,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -3826,7 +3972,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -3835,7 +3981,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -3848,27 +3994,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3909,7 +4055,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3922,7 +4068,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>54</v>
@@ -3930,7 +4076,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>4.4</v>
@@ -3938,7 +4084,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>4.4</v>
@@ -3946,7 +4092,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -3954,7 +4100,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -3962,7 +4108,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>4.5</v>
@@ -3970,7 +4116,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5</v>
@@ -3978,7 +4124,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -3987,15 +4133,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4011,70 +4157,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21.1</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>14.2</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4087,39 +4233,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -4149,10 +4295,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -4182,10 +4328,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -4215,12 +4361,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4233,42 +4379,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5.5</v>
@@ -4288,16 +4434,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>20.55</v>
@@ -4317,16 +4463,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>35</v>
@@ -4346,7 +4492,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4359,7 +4505,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4386,7 +4532,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4395,7 +4541,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4408,7 +4554,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4417,7 +4563,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4430,27 +4576,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4491,7 +4637,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4504,7 +4650,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>57</v>
@@ -4512,7 +4658,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>7</v>
@@ -4520,7 +4666,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>7</v>
@@ -4528,7 +4674,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -4536,7 +4682,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -4544,7 +4690,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>6</v>
@@ -4552,7 +4698,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>6.5</v>
@@ -4560,7 +4706,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -4569,15 +4715,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4593,59 +4739,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>58</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>200</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>157</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>15.6</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -4658,39 +4804,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3.5</v>
@@ -4720,10 +4866,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>4.5</v>
@@ -4753,10 +4899,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>5.5</v>
@@ -4786,12 +4932,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4804,42 +4950,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>8</v>
@@ -4859,16 +5005,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>44</v>
@@ -4888,16 +5034,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>5.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>90</v>
@@ -4917,7 +5063,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4930,7 +5076,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -4957,7 +5103,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -4966,7 +5112,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -4979,7 +5125,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -4988,7 +5134,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5001,27 +5147,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5062,7 +5208,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5075,7 +5221,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>61</v>
@@ -5083,7 +5229,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>126</v>
@@ -5091,7 +5237,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>126</v>
@@ -5099,7 +5245,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5107,7 +5253,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5115,7 +5261,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>136</v>
@@ -5123,7 +5269,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>145</v>
@@ -5131,7 +5277,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5140,15 +5286,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5164,48 +5310,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>2.8</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.2</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>0.9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5218,39 +5364,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -5280,10 +5426,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -5313,10 +5459,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -5346,12 +5492,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5364,42 +5510,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>150</v>
@@ -5419,16 +5565,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>340</v>
@@ -5448,16 +5594,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>700</v>
@@ -5477,7 +5623,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -5490,7 +5636,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -5517,7 +5663,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -5526,7 +5672,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -5539,7 +5685,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -5548,7 +5694,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -5561,57 +5707,57 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5652,7 +5798,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5665,7 +5811,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>65</v>
@@ -5673,7 +5819,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>5</v>
@@ -5681,7 +5827,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>5</v>
@@ -5689,7 +5835,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -5697,7 +5843,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -5705,7 +5851,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>5.4</v>
@@ -5713,7 +5859,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5.75</v>
@@ -5721,7 +5867,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -5730,15 +5876,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5754,48 +5900,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>8.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5808,39 +5954,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -5870,10 +6016,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -5903,10 +6049,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -5936,12 +6082,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -5954,42 +6100,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5</v>
@@ -6009,16 +6155,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>14.5</v>
@@ -6038,16 +6184,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>26</v>
@@ -6067,7 +6213,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6080,7 +6226,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -6107,7 +6253,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -6116,7 +6262,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6129,7 +6275,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -6138,7 +6284,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6151,57 +6297,57 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -6242,7 +6388,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6255,7 +6401,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>69</v>
@@ -6263,7 +6409,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>35</v>
@@ -6271,7 +6417,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>35</v>
@@ -6279,7 +6425,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6287,7 +6433,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6295,7 +6441,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>38</v>
@@ -6303,7 +6449,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>42</v>
@@ -6311,7 +6457,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6320,15 +6466,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6344,21 +6490,21 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6369,45 +6515,45 @@
         <v>21</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>1.9</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6420,39 +6566,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1</v>
@@ -6482,10 +6628,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>1.5</v>
@@ -6515,10 +6661,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2.5</v>
@@ -6548,12 +6694,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -6566,42 +6712,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>30</v>
@@ -6621,16 +6767,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>92</v>
@@ -6650,16 +6796,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>210</v>
@@ -6679,7 +6825,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -6692,7 +6838,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -6719,7 +6865,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -6728,7 +6874,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -6741,7 +6887,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -6750,7 +6896,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -6763,62 +6909,62 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -6859,7 +7005,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6872,7 +7018,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>73</v>
@@ -6880,7 +7026,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>5.4</v>
@@ -6888,7 +7034,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>5.4</v>
@@ -6896,7 +7042,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -6904,7 +7050,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -6912,7 +7058,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>5.85</v>
@@ -6920,7 +7066,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>6.2</v>
@@ -6928,7 +7074,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -6937,15 +7083,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6961,70 +7107,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>40</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>33</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>26.7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>17.7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>7.7</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -7037,39 +7183,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -7099,10 +7245,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -7132,10 +7278,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -7165,12 +7311,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -7183,42 +7329,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>3.5</v>
@@ -7238,16 +7384,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>16.3</v>
@@ -7267,16 +7413,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>45</v>
@@ -7296,7 +7442,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -7309,7 +7455,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -7336,7 +7482,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -7345,7 +7491,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -7358,7 +7504,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -7367,7 +7513,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -7380,57 +7526,673 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I57"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">AVERAGE(B10:B11)</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <f aca="false">D25*E25</f>
+        <v>7.5</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">F25/B12</f>
+        <v>0.714285714285714</v>
+      </c>
+      <c r="H25" s="29" t="n">
+        <f aca="false">G25-1</f>
+        <v>-0.285714285714286</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <f aca="false">G25^(1/C25)-1</f>
+        <v>-0.200936469941859</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <f aca="false">D26*E26</f>
+        <v>22.5</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <f aca="false">F26/B12</f>
+        <v>2.14285714285714</v>
+      </c>
+      <c r="H26" s="29" t="n">
+        <f aca="false">G26-1</f>
+        <v>1.14285714285714</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <f aca="false">G26^(1/C26)-1</f>
+        <v>0.356429691309786</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">D27*E27</f>
+        <v>52</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <f aca="false">F27/B12</f>
+        <v>4.95238095238095</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <f aca="false">G27-1</f>
+        <v>3.95238095238095</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <f aca="false">G27^(1/C27)-1</f>
+        <v>0.579495156361438</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <f aca="false">E32/B12</f>
+        <v>0.761904761904762</v>
+      </c>
+      <c r="G32" s="29" t="n">
+        <f aca="false">F32-1</f>
+        <v>-0.238095238095238</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <f aca="false">F32^(1/C32)-1</f>
+        <v>-0.165805878116593</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F33" s="28" t="n">
+        <f aca="false">E33/B12</f>
+        <v>2.61904761904762</v>
+      </c>
+      <c r="G33" s="29" t="n">
+        <f aca="false">F33-1</f>
+        <v>1.61904761904762</v>
+      </c>
+      <c r="H33" s="29" t="n">
+        <f aca="false">F33^(1/C33)-1</f>
+        <v>0.469797004390423</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <f aca="false">E34/B12</f>
+        <v>5.71428571428571</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <f aca="false">F34-1</f>
+        <v>4.71428571428571</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <f aca="false">F34^(1/C34)-1</f>
+        <v>0.645412693099038</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <f aca="false">AVERAGE(F26,E33)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B36/B12</f>
+        <v>2.38095238095238</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="n">
+        <f aca="false">B37-1</f>
+        <v>1.38095238095238</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="31" t="n">
+        <f aca="false">B37^(1/C26)-1</f>
+        <v>0.41481704664972</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">MIN(G25,F32)</f>
+        <v>0.714285714285714</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">MAX(G27,F34)</f>
+        <v>5.71428571428571</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B36/B11</f>
+        <v>2.08333333333333</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
         <v>147</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -7458,7 +8220,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7466,71 +8228,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +8333,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7584,7 +8346,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>19</v>
@@ -7592,7 +8354,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>852</v>
@@ -7600,7 +8362,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>852</v>
@@ -7608,7 +8370,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -7616,7 +8378,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -7624,7 +8386,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">B7*(1+B8)</f>
@@ -7633,7 +8395,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">B7*(1+B9)</f>
@@ -7642,7 +8404,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -7651,15 +8413,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7675,70 +8437,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9.4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -7751,39 +8513,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1.5</v>
@@ -7813,10 +8575,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>1.5</v>
@@ -7846,10 +8608,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2</v>
@@ -7879,12 +8641,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -7897,42 +8659,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>1000</v>
@@ -7952,16 +8714,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>1550</v>
@@ -7981,16 +8743,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>2200</v>
@@ -8010,7 +8772,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -8023,7 +8785,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -8050,7 +8812,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -8059,7 +8821,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -8072,7 +8834,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -8081,7 +8843,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -8094,22 +8856,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -8150,7 +8912,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8163,7 +8925,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>23</v>
@@ -8171,7 +8933,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>39</v>
@@ -8179,7 +8941,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>39</v>
@@ -8187,7 +8949,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -8195,7 +8957,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -8203,7 +8965,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>30</v>
@@ -8211,7 +8973,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>33</v>
@@ -8219,7 +8981,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -8228,15 +8990,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8252,70 +9014,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>7.3</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.6</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8328,39 +9090,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -8390,10 +9152,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -8423,10 +9185,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -8456,12 +9218,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -8474,42 +9236,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>39</v>
@@ -8529,16 +9291,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>72.9</v>
@@ -8558,16 +9320,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>150</v>
@@ -8587,7 +9349,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -8600,7 +9362,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -8627,7 +9389,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -8636,7 +9398,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -8649,7 +9411,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -8658,7 +9420,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -8671,22 +9433,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -8727,7 +9489,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8740,7 +9502,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
@@ -8748,7 +9510,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>10</v>
@@ -8756,7 +9518,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>10</v>
@@ -8764,7 +9526,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -8772,7 +9534,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -8780,7 +9542,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>10.5</v>
@@ -8788,7 +9550,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>12</v>
@@ -8796,7 +9558,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -8805,15 +9567,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8829,48 +9591,48 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>15.7</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8883,39 +9645,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2.5</v>
@@ -8945,10 +9707,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -8978,10 +9740,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -9011,12 +9773,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -9029,42 +9791,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>10</v>
@@ -9084,16 +9846,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>61.5</v>
@@ -9113,16 +9875,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>120</v>
@@ -9142,7 +9904,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -9155,7 +9917,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -9182,7 +9944,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -9191,7 +9953,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -9204,7 +9966,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -9213,7 +9975,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -9226,22 +9988,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -9282,7 +10044,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -9295,7 +10057,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>31</v>
@@ -9303,7 +10065,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>15</v>
@@ -9311,7 +10073,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>15</v>
@@ -9319,7 +10081,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -9327,7 +10089,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -9335,7 +10097,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>13.5</v>
@@ -9343,7 +10105,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>15</v>
@@ -9351,7 +10113,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -9360,15 +10122,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -9384,70 +10146,70 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.7</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>5.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>2.1</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -9460,39 +10222,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -9522,10 +10284,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -9555,10 +10317,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -9588,12 +10350,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -9606,42 +10368,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>22</v>
@@ -9661,16 +10423,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>45</v>
@@ -9690,16 +10452,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>100</v>
@@ -9719,7 +10481,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -9732,7 +10494,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -9759,7 +10521,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -9768,7 +10530,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -9781,7 +10543,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -9790,7 +10552,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -9803,22 +10565,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -9859,7 +10621,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -9872,7 +10634,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>35</v>
@@ -9880,7 +10642,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1</v>
@@ -9888,7 +10650,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>3.5</v>
@@ -9896,7 +10658,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -9904,7 +10666,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -9912,7 +10674,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>4.5</v>
@@ -9920,7 +10682,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>5</v>
@@ -9928,7 +10690,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -9937,15 +10699,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -9961,59 +10723,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>20.6</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>24.5</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>16.9</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -10026,39 +10788,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>3</v>
@@ -10088,10 +10850,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>3.5</v>
@@ -10121,10 +10883,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>4.5</v>
@@ -10154,12 +10916,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -10172,42 +10934,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>5</v>
@@ -10227,16 +10989,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>24.2</v>
@@ -10256,16 +11018,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>40</v>
@@ -10285,7 +11047,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -10298,7 +11060,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -10325,7 +11087,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -10334,7 +11096,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -10347,7 +11109,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -10356,7 +11118,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -10369,22 +11131,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -10425,7 +11187,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -10438,7 +11200,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>39</v>
@@ -10446,7 +11208,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>190</v>
@@ -10454,7 +11216,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>190</v>
@@ -10462,7 +11224,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -10470,7 +11232,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -10478,7 +11240,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>195</v>
@@ -10486,7 +11248,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>210</v>
@@ -10494,7 +11256,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -10503,15 +11265,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -10527,59 +11289,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>10.5</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -10592,39 +11354,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -10654,10 +11416,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2</v>
@@ -10687,10 +11449,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3</v>
@@ -10720,12 +11482,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -10738,42 +11500,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>190</v>
@@ -10793,16 +11555,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>426</v>
@@ -10822,16 +11584,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>600</v>
@@ -10851,7 +11613,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -10864,7 +11626,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -10891,7 +11653,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -10900,7 +11662,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -10913,7 +11675,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -10922,7 +11684,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -10935,22 +11697,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -10991,7 +11753,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -11004,7 +11766,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -11012,7 +11774,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>30</v>
@@ -11020,7 +11782,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>30</v>
@@ -11028,7 +11790,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -11036,7 +11798,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.15</v>
@@ -11044,7 +11806,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>23</v>
@@ -11052,7 +11814,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>28</v>
@@ -11060,7 +11822,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
@@ -11069,15 +11831,15 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -11093,59 +11855,59 @@
         <v>2</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>21</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>6.1</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>4.7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>3.2</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -11158,39 +11920,39 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2</v>
@@ -11220,10 +11982,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2.5</v>
@@ -11253,10 +12015,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>3.5</v>
@@ -11286,12 +12048,12 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -11304,42 +12066,42 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>30</v>
@@ -11359,16 +12121,16 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>81.6</v>
@@ -11388,16 +12150,16 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>140</v>
@@ -11417,7 +12179,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -11430,7 +12192,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
@@ -11457,7 +12219,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
@@ -11466,7 +12228,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
@@ -11479,7 +12241,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
@@ -11488,7 +12250,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -11501,27 +12263,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -1212,7 +1212,7 @@
     <t xml:space="preserve">• Отраслевые прогнозы рынка ИИ-видео некорректны (дают «$2 млрд к 2030», хотя четыре игрока уже делают ~$1.65 млрд в год) — в модели не использованы</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Диапазон отражает разрыв между закрытым раундом ($5.9 млрд, ноябрь 2025) и идущими переговорами о раунде $3 млрд по оценке выше $12 млрд (Bloomberg, 24.08.2026). Опорная точка внутри диапазона — котировка от 13.06.2026, соответствующая оценке около $9 млрд. Прецедент тот же, что по 1X и Positron: закрытый раунд устарел. Оговорка: оценка $5.9 млрд — расчёт Forge, эмитентом не подтверждена; котировки площадок ($39.32 Forge против $43.16 NPM) не переводятся в оценку без fully diluted share count, а данных о фактически исполненных сделках нет.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Диапазон отражает идущий pre-IPO раунд до $3 млрд по оценке от $12 млрд (Bloomberg) и подписанный 31.08.2026 контракт с Anthropic примерно на $35 млрд, которого на момент этих переговоров ещё не было. Закрытый раунд ноября 2025 ($5.9 млрд) устарел — подход тот же, что по 1X и Positron. Оговорка: оценка $5.9 млрд — расчёт Forge, эмитентом не подтверждена; котировки площадок ($39.32 Forge против $43.16 NPM) не переводятся в оценку без fully diluted share count.</t>
   </si>
   <si>
     <t xml:space="preserve">CoreWeave</t>
@@ -1221,6 +1221,12 @@
     <t xml:space="preserve">EV/Sales 2026E — главный аналог, выручка Q2'26 $2.58 млрд (+112%)</t>
   </si>
   <si>
+    <t xml:space="preserve">CoreWeave по бэклогу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / законтрактованный бэклог ($95 млрд / $129 млрд)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nebius</t>
   </si>
   <si>
@@ -1230,61 +1236,55 @@
     <t xml:space="preserve">Together AI</t>
   </si>
   <si>
-    <t xml:space="preserve">CoreWeave TTM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV/Sales по прошлой выручке — верх диапазона</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выручка: $425 млн (2024) → run-rate $760 млн (конец 2025) → более $1.5 млрд ожидается по итогам 2026. Базовый сценарий: рост втрое к 2029 году при мультипликаторе 5x — с дисконтом к CoreWeave (6–8x на 2026E) за меньший масштаб. Консервативный сценарий закладывает сжатие мультипликаторов сектора, которое уже происходит: акции CoreWeave потеряли 51% от пика к августу 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сжатие мультипликаторов сектора продолжается, размещение по нижней границе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO 2027 с дисконтом к CoreWeave по масштабу выручки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мультипликатор уровня Nebius при сохранении темпа роста</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• IPO НЕ состоялось и заявка публично НЕ подана на дату отсечки. Подтверждений конфиденциальной подачи S-1 нет ни в одном первоисточнике — распространённое утверждение об этом восходит к новости о найме Morgan Stanley, J.P. Morgan и Citi (сентябрь 2025). Окно 1П2026 пропущено, ориентир сместился на 2027 год (Bloomberg, 24.08.2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Series E более $1.5 млрд, 18.11.2025, лид TWG Global; post-money около $5.9 млрд — расчёт Forge, эмитентом не подтверждён</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Предыдущий раунд: Series D $480 млн @ $2.5 млрд, 19.02.2025 (Andra Capital, SGW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• На 24.08.2026 Bloomberg сообщил о переговорах о раунде $3 млрд при оценке выше $12 млрд — несколько term sheets, сделка НЕ закрыта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Привлечено раздельно: акционерный капитал ~$2.3–2.4 млрд, долг ~$2.4 млрд ($500 млн Macquarie апрель 2024 — первая в отрасли секьюритизация под залог GPU, рейтинг Moody's Baa2; $1 млрд май 2026; $917 млн Morgan Stanley август 2026). Циркулирующая цифра «$3.14 млрд всего» смешивает акции и долг</t>
+    <t xml:space="preserve">Выручка: $425 млн (2024) → run-rate $760 млн (конец 2025) → более $1.5 млрд ожидается по итогам 2026. Базовый сценарий строится на разгоне контракта с Anthropic: $35 млрд за шесть лет дают в среднем около $5.8 млрд выручки в год после ввода площадки, плюс действующая база и контракт с Microsoft. Мультипликатор 5x — с дисконтом к CoreWeave (6–8x на 2026E) за меньший масштаб и более высокую концентрацию клиентов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сдвиг ввода мощностей Beacon Point и продолжение сжатия мультипликаторов сектора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO 2027 при законтрактованном бэклоге около $35 млрд, мультипликатор к бэклогу с дисконтом к CoreWeave (0.74x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мультипликатор уровня Nebius при полной загрузке 1 ГВт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• КЛЮЧЕВОЕ СОБЫТИЕ: 31.08.2026 подписан шестилетний контракт с Anthropic на вычислительные мощности примерно на $35 млрд (WSJ, Bloomberg). Это крупнейшая сделка в истории компании и более чем в 20 раз превышает ожидаемую выручку за 2026 год. Для сравнения: все обязательства OpenAI перед CoreWeave за 2025 год — $22.4 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Площадка Beacon Point в Техасе, проектная мощность 1 ГВт. Строит Hut 8 (бывший майнер криптовалюты), арендатор площадки — NVIDIA, Lambda размещает на ней купленные у NVIDIA чипы и продаёт вычисления Anthropic. NVIDIA при этом входит в капитал Lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• IPO НЕ состоялось и заявка публично НЕ подана. Подтверждений конфиденциальной подачи S-1 нет ни в одном первоисточнике — распространённое утверждение восходит к новости о найме Morgan Stanley, J.P. Morgan и Citi (сентябрь 2025). Размещение рассматривается на 2027 год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Идущий pre-IPO раунд: до $3 млрд по оценке от $12 млрд (Bloomberg). Две задачи раунда — зафиксировать более высокую оценку перед размещением и профинансировать новые мощности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Series E более $1.5 млрд, 18.11.2025, лид TWG Global; post-money около $5.9 млрд — расчёт Forge, эмитентом не подтверждён. Предыдущий раунд: Series D $480 млн @ $2.5 млрд, 19.02.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Привлечено раздельно: акционерный капитал ~$2.3–2.4 млрд, долг ~$3.4 млрд. Заём на $926 млн под закупку GPU получил рейтинг Moody's Baa2 — инвестиционный уровень, до которого не дотягивал ни один частный неоклауд. Рейтинг допускает к займу пенсионные фонды и страховые компании, то есть расширяет круг кредиторов и удешевляет капитал</t>
   </si>
   <si>
     <t xml:space="preserve">• Выручка: $425 млн (2024) → run-rate $760 млн (конец 2025) → более $1.5 млрд ожидается в 2026. Валовая маржа 1П2025 около 50% (около 61% без продаж железа), убыток TTM около $175 млн</t>
   </si>
   <si>
-    <t xml:space="preserve">• Контракт с Microsoft от 03.11.2025 назван многомиллиардным, сумма НЕ раскрыта. Бэклог компания не раскрывает — публичной цифры не существует</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Мощность более 320 МВт, заявленная цель — 3 ГВт к 2030 году</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• РИСК 1 — структура капитала: долг примерно равен акционерному капиталу и обеспечен быстро дешевеющим железом. Цена часа H100 упала с $7–10 до менее $2–4. Срок амортизации GPU в отрасли не устоялся: Amazon сократил с 6 до 5 лет, CoreWeave держит 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• РИСК 2 — сжатие мультипликаторов уже реализовалось: CoreWeave разместилась по $40, выросла втрое к июню 2025 и потеряла 51% от пика к августу 2026 (минус 33% за три месяца)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• РИСК 3 — концентрация клиентов не раскрывается; круговая связь с NVIDIA, которая одновременно инвестор, поставщик чипов и держатель лизинга дата-центров</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• ПОСЛЕ ДАТЫ ОТСЕЧКИ (в расчёте не учтено): 28.08.2026 привлечён ещё $1 млрд долга (JPMorgan) — совокупный долг вырос примерно до $3.4 млрд, больше всего акционерного капитала. 31.08.2026 объявлен шестилетний контракт с Anthropic на сумму около $35 млрд (350 МВт, Nueces County, Техас). Контракт кратно меняет масштаб бизнеса и одновременно резко усиливает концентрацию клиентов — требует пересчёта модели</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Тезисы преимущества: статус NVIDIA Exemplar Cloud и четыре года подряд звание партнёра года NVIDIA; инвестиционный рейтинг Baa2 по долгу под залог GPU; работающий self-serve сегмент (1-Click Clusters, около 30 секунд до доступа) с маржой 61% против 50% по компании</t>
+    <t xml:space="preserve">• Контракт с Microsoft от 03.11.2025 назван многомиллиардным, сумма НЕ раскрыта. Мощность более 320 МВт, заявленная цель — 3 ГВт к 2030 году</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 1 — концентрация: после сделки будущее компании определяется одним клиентом. Контракт построен на допущении, что спрос на ИИ будет расти достаточно быстро, чтобы выкупить зарезервированные мощности по зафиксированным ценам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 2 — связанность участников: Hut 8 строит, NVIDIA арендует площадку, поставляет чипы и одновременно является инвестором Lambda. Риски внутри этого круга не независимы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 3 — структура капитала: долг превышает акционерный капитал и обеспечен быстро дешевеющим железом (час H100 подешевел с $7–10 до менее $2–4). Срок амортизации GPU в отрасли не устоялся: Amazon сократил с 6 до 5 лет, CoreWeave держит 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• РИСК 4 — сжатие мультипликаторов сектора уже реализовалось: акции CoreWeave выросли втрое после IPO и потеряли 51% от пика к августу 2026 (минус 33% за три месяца)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Тезисы преимущества: законтрактованный на годы спрос от Anthropic; инвестиционный рейтинг Baa2 по долгу под залог GPU; статус NVIDIA Exemplar Cloud и четыре года подряд звание партнёра года NVIDIA; self-serve сегмент с маржой 61% против 50% по компании</t>
   </si>
 </sst>
 </file>
@@ -2816,42 +2816,42 @@
       </c>
       <c r="F20" s="6" t="n">
         <f aca="false">Lambda!B10</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G20" s="6" t="n">
         <f aca="false">Lambda!B11</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" s="6" t="n">
         <f aca="false">Lambda!B12</f>
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>78</v>
       </c>
       <c r="J20" s="6" t="n">
         <f aca="false">Lambda!B36</f>
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K20" s="8" t="n">
         <f aca="false">Lambda!B37</f>
-        <v>2.38095238095238</v>
+        <v>2.74074074074074</v>
       </c>
       <c r="L20" s="9" t="n">
         <f aca="false">Lambda!B38</f>
-        <v>1.38095238095238</v>
+        <v>1.74074074074074</v>
       </c>
       <c r="M20" s="9" t="n">
         <f aca="false">Lambda!B39</f>
-        <v>0.41481704664972</v>
+        <v>0.496742815701976</v>
       </c>
       <c r="N20" s="8" t="n">
         <f aca="false">Lambda!B40</f>
-        <v>0.714285714285714</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O20" s="8" t="n">
         <f aca="false">Lambda!C40</f>
-        <v>5.71428571428571</v>
+        <v>6.66666666666667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7673,7 +7673,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,7 +7681,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7741,7 +7741,7 @@
         <v>394</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>8.5</v>
+        <v>0.74</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>395</v>
@@ -7752,21 +7752,21 @@
         <v>396</v>
       </c>
       <c r="B19" s="21" t="n">
-        <v>8.3</v>
+        <v>8.5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B20" s="21" t="n">
-        <v>13.6</v>
+        <v>8.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>398</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7822,26 +7822,26 @@
         <v>1.5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="26" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.714285714285714</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.285714285714286</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.200936469941859</v>
+        <v>-0.236857171631112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7855,26 +7855,26 @@
         <v>2.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>5</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>22.5</v>
+        <v>35</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.14285714285714</v>
+        <v>2.59259259259259</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.14285714285714</v>
+        <v>1.59259259259259</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.356429691309786</v>
+        <v>0.463840337369668</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7888,26 +7888,26 @@
         <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>6.5</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>4.95238095238095</v>
+        <v>5.77777777777778</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>3.95238095238095</v>
+        <v>4.77777777777778</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.579495156361438</v>
+        <v>0.650615627779178</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7968,22 +7968,22 @@
         <v>400</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.761904761904762</v>
+        <v>0.814814814814815</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.238095238095238</v>
+        <v>-0.185185185185185</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.165805878116593</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-0.127619509940034</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
         <v>133</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>401</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>27.5</v>
+        <v>39</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.61904761904762</v>
+        <v>2.88888888888889</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.61904761904762</v>
+        <v>1.88888888888889</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.469797004390423</v>
+        <v>0.528594650593345</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8026,19 +8026,19 @@
         <v>402</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>5.71428571428571</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>4.71428571428571</v>
+        <v>5.66666666666667</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.645412693099038</v>
+        <v>0.719501256105151</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.38095238095238</v>
+        <v>2.74074074074074</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.38095238095238</v>
+        <v>1.74074074074074</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.41481704664972</v>
+        <v>0.496742815701976</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8096,11 +8096,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.714285714285714</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>5.71428571428571</v>
+        <v>6.66666666666667</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.08333333333333</v>
+        <v>2.46666666666667</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -225,7 +225,7 @@
     <t xml:space="preserve">Раунд $16 млрд, объявлен 02.02.2026; лиды Dragoneer, DST Global, Sequoia; Alphabet вложила ~$13 млрд</t>
   </si>
   <si>
-    <t xml:space="preserve">3–4 года (IPO / спин-офф 2029–30)</t>
+    <t xml:space="preserve">3 года (IPO / спин-офф 2029)</t>
   </si>
   <si>
     <t xml:space="preserve">Plata</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">Series C $405 млн, анонс 16.04.2026; лид Bicycle Capital, вошли QIA, BTG Pactual, Valor Capital</t>
   </si>
   <si>
-    <t xml:space="preserve">3–4 года (IPO 2029–30)</t>
+    <t xml:space="preserve">2 года (IPO 2028)</t>
   </si>
   <si>
     <t xml:space="preserve">Moonshot AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Series F более $3.5 млрд, объявлен 29.07.2026; среди лидов — государственный National AI Industry Investment Fund</t>
   </si>
   <si>
-    <t xml:space="preserve">1–2 года (IPO Гонконг)</t>
+    <t xml:space="preserve">1.5–2 года (IPO Гонконг)</t>
   </si>
   <si>
     <t xml:space="preserve">Higgsfield AI</t>
@@ -261,7 +261,7 @@
     <t xml:space="preserve">Series B $400 млн, закрыт 17.08.2026; лид DST Global, вошли Goldman Sachs Alternatives, Intel Capital, Mirae Asset</t>
   </si>
   <si>
-    <t xml:space="preserve">2–3 года (IPO / M&amp;A 2029)</t>
+    <t xml:space="preserve">3–4 года (IPO / M&amp;A 2030)</t>
   </si>
   <si>
     <t xml:space="preserve">Lambda</t>
@@ -273,7 +273,7 @@
     <t xml:space="preserve">Series E более $1.5 млрд, закрыт 18.11.2025; лид TWG Global совместно с US Innovative Technology Fund</t>
   </si>
   <si>
-    <t xml:space="preserve">2–3 года (IPO 2027)</t>
+    <t xml:space="preserve">1.5 года (IPO 2027)</t>
   </si>
   <si>
     <t xml:space="preserve">По 1X Technologies и Positron AI последние закрытые раунды устарели, поэтому премия 8–15% считается не от них, а от оценки идущего раунда (1X — Series C ~$10 млрд; Positron — первый транш ~$3.5 млрд).</t>
@@ -948,7 +948,7 @@
     <t xml:space="preserve">• Риски: перенос площадки в Брисбене и сдвиг сроков к 2029–2030, аудит ANAO по австралийской сделке, временный CEO (Виктор Пенг с 10.02.2026), недоказанная отказоустойчивость фотонного подхода</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Подтверждённых закрытых сделок вторичного рынка нет: расчётные оценки площадок расходятся в 2.4 раза ($152 / $215 / $364 за акцию). Применена премия 8–15% к оценке раунда.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Индикативный диапазон фонда. Подтверждённых закрытых сделок нет: расчётные оценки площадок расходятся в 2.4 раза ($152 / $215 / $364 за акцию), нижняя из них соответствует примерно этому уровню. К оценке раунда ($126 млрд) диапазон соответствует премии 19–23%.</t>
   </si>
   <si>
     <t xml:space="preserve">Uber</t>
@@ -972,10 +972,10 @@
     <t xml:space="preserve">Замедление экспансии после отзывов и расследований, оценка возвращается к уровню раунда 2026 года</t>
   </si>
   <si>
-    <t xml:space="preserve">Спин-офф или IPO при доле около 15% рынка ride-hailing США</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нижняя часть прогноза Deepwater ($350–850 млрд к 2030)</t>
+    <t xml:space="preserve">Спин-офф или IPO при доле около 20% рынка ride-hailing США</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Середина прогноза Deepwater ($350–850 млрд к 2030)</t>
   </si>
   <si>
     <t xml:space="preserve">• Раунд $16 млрд @ $126 млрд post-money, объявлен 02.02.2026; лиды Dragoneer, DST Global, Sequoia. Часть источников (Fortune) даёт заголовок $110 млрд — это pre-money</t>
@@ -1008,7 +1008,7 @@
     <t xml:space="preserve">• Конкуренция: Baidu Apollo Go более 250 тыс. поездок в неделю; Pony.ai заявила безубыточность юнит-экономики в Гуанчжоу</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Публичных котировок нет: компания листингуется на EquityZen и Hiive, но цены за пейволлом. Применена премия 8–15% к оценке раунда. Единственная документированная вторичная сделка прошла внутри Series B по $3.1 млрд.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Индикативный диапазон фонда; к оценке раунда ($5 млрд) соответствует премии 18–24%. Публичных котировок нет: компания листингуется на EquityZen и Hiive, но цены за пейволлом. Единственная документированная вторичная сделка прошла внутри Series B по $3.1 млрд.</t>
   </si>
   <si>
     <t xml:space="preserve">Nu Holdings</t>
@@ -1035,7 +1035,7 @@
     <t xml:space="preserve">Рост просрочки обгоняет портфель, оценка сжимается к мультипликатору Inter&amp;Co</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO по публичному ориентиру основателей (~$10 млрд) с поправкой на достигнутую прибыльность</t>
+    <t xml:space="preserve">IPO выше публичного ориентира основателей (~$10 млрд) на достигнутой прибыльности</t>
   </si>
   <si>
     <t xml:space="preserve">Доля рынка карт Мексики уровня Nubank в Бразилии при мультипликаторе 8x</t>
@@ -1071,7 +1071,7 @@
     <t xml:space="preserve">• Перед сделкой обязательно запросить квартальную отчётность Banco Plata (prime.platacard.mx): чистый результат, ICAP, стоимость риска</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Ликвидного вторичного рынка нет, официальных котировок не существует (Forge показывает оценку $800 млн при реальных $35 млрд). Нижняя граница — премия 8% к закрытому раунду, верхняя отражает идущий pre-IPO раунд по pre-money $50 млрд (финальный клозинг 27.08.2026, уже после даты отсечки).</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Индикативный диапазон фонда. Он НИЖЕ оценки закрытого раунда ($35 млрд) на 14–26%: дисконт отражает нерешённый механизм переноса прав зарубежных акционеров при демонтаже структуры VIE и ограничения на участие инвесторов из США. Ликвидного вторичного рынка нет, официальных котировок не существует (Forge показывает оценку $800 млн при реальных $35 млрд). Для справки: идущий pre-IPO раунд обсуждался по pre-money $50 млрд.</t>
   </si>
   <si>
     <t xml:space="preserve">Anthropic</t>
@@ -1101,10 +1101,10 @@
     <t xml:space="preserve">Годовая выручка выросла со $100 млн до $300 млн за март–июнь 2026, более 70% приходится на API. ВАЖНО: текущий мультипликатор — около 117x выручки против 15–21x у OpenAI и Anthropic, то есть тезис «дешёвая альтернатива Западу» по оценке НЕ подтверждается. Базовый сценарий закладывает четырёхкратный рост выручки к листингу и сжатие мультипликатора.</t>
   </si>
   <si>
-    <t xml:space="preserve">Дисконт за нерешённый механизм переноса прав иностранных акционеров при демонтаже VIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO в Гонконге между MiniMax (~$33 млрд) и Zhipu AI (~$112 млрд)</t>
+    <t xml:space="preserve">Механизм переноса прав иностранных акционеров решён не в пользу держателей офшорных долей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO в Гонконге ближе к MiniMax (~$33 млрд), чем к Zhipu AI (~$112 млрд)</t>
   </si>
   <si>
     <t xml:space="preserve">Оценка на уровне Zhipu AI после листинга</t>
@@ -1143,7 +1143,7 @@
     <t xml:space="preserve">• Легальные прокси для западного инвестора: акции Alibaba (~36% Moonshot), Tencent, Meituan, либо публичные Zhipu AI и MiniMax на HKEX</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Подтверждённых сделок нет: листинги на Forge, EquityZen и Nasdaq Private Market есть, котировок нет. Данные агрегаторов противоречат друг другу вдвое и противоречат подтверждённым раундам — не использованы. Применена премия 8–15% к оценке раунда.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Подтверждённых сделок нет: листинги на Forge, EquityZen и Nasdaq Private Market есть, котировок нет. Данные агрегаторов противоречат друг другу вдвое и противоречат подтверждённым раундам — не использованы. Индикативный диапазон фонда соответствует уровню оценки раунда плюс 2–11%.</t>
   </si>
   <si>
     <t xml:space="preserve">Luma AI</t>
@@ -1212,7 +1212,7 @@
     <t xml:space="preserve">• Отраслевые прогнозы рынка ИИ-видео некорректны (дают «$2 млрд к 2030», хотя четыре игрока уже делают ~$1.65 млрд в год) — в модели не использованы</t>
   </si>
   <si>
-    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Диапазон отражает идущий pre-IPO раунд до $3 млрд по оценке от $12 млрд (Bloomberg) и подписанный 31.08.2026 контракт с Anthropic примерно на $35 млрд, которого на момент этих переговоров ещё не было. Закрытый раунд ноября 2025 ($5.9 млрд) устарел — подход тот же, что по 1X и Positron. Оговорка: оценка $5.9 млрд — расчёт Forge, эмитентом не подтверждена; котировки площадок ($39.32 Forge против $43.16 NPM) не переводятся в оценку без fully diluted share count.</t>
+    <t xml:space="preserve">Диапазон — фактические котировки вторичного рынка. Индикативный диапазон фонда: между оценкой закрытого раунда ноября 2025 ($5.9 млрд, премия 44–53%) и идущим pre-IPO раундом до $3 млрд по оценке от $12 млрд (Bloomberg). Закрытый раунд устарел — подход тот же, что по 1X и Positron. Диапазон ниже обсуждаемой оценки раунда, то есть предполагает вход до её фиксации. Оговорка: оценка $5.9 млрд — расчёт Forge, эмитентом не подтверждена; котировки площадок ($39.32 Forge против $43.16 NPM) не переводятся в оценку без fully diluted share count.</t>
   </si>
   <si>
     <t xml:space="preserve">CoreWeave</t>
@@ -1242,7 +1242,7 @@
     <t xml:space="preserve">Сдвиг ввода мощностей Beacon Point и продолжение сжатия мультипликаторов сектора</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO 2027 при законтрактованном бэклоге около $35 млрд, мультипликатор к бэклогу с дисконтом к CoreWeave (0.74x)</t>
+    <t xml:space="preserve">IPO 2027 при законтрактованном бэклоге около $35 млрд, мультипликатор к бэклогу с большим дисконтом к CoreWeave (0.74x)</t>
   </si>
   <si>
     <t xml:space="preserve">Мультипликатор уровня Nebius при полной загрузке 1 ГВт</t>
@@ -2584,42 +2584,42 @@
       </c>
       <c r="F16" s="6" t="n">
         <f aca="false">Waymo!B10</f>
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G16" s="6" t="n">
         <f aca="false">Waymo!B11</f>
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H16" s="6" t="n">
         <f aca="false">Waymo!B12</f>
-        <v>140.5</v>
+        <v>152.5</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>62</v>
       </c>
       <c r="J16" s="6" t="n">
         <f aca="false">Waymo!B36</f>
-        <v>310</v>
+        <v>457.5</v>
       </c>
       <c r="K16" s="8" t="n">
         <f aca="false">Waymo!B37</f>
-        <v>2.20640569395018</v>
+        <v>3</v>
       </c>
       <c r="L16" s="9" t="n">
         <f aca="false">Waymo!B38</f>
-        <v>1.20640569395018</v>
+        <v>2</v>
       </c>
       <c r="M16" s="9" t="n">
         <f aca="false">Waymo!B39</f>
-        <v>0.253706333606649</v>
+        <v>0.442249570307408</v>
       </c>
       <c r="N16" s="8" t="n">
         <f aca="false">Waymo!B40</f>
-        <v>0.889679715302491</v>
+        <v>0.983606557377049</v>
       </c>
       <c r="O16" s="8" t="n">
         <f aca="false">Waymo!C40</f>
-        <v>4.98220640569395</v>
+        <v>5.57377049180328</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2642,42 +2642,42 @@
       </c>
       <c r="F17" s="6" t="n">
         <f aca="false">Plata!B10</f>
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="G17" s="6" t="n">
         <f aca="false">Plata!B11</f>
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="H17" s="6" t="n">
         <f aca="false">Plata!B12</f>
-        <v>5.575</v>
+        <v>6.05</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>66</v>
       </c>
       <c r="J17" s="6" t="n">
         <f aca="false">Plata!B36</f>
-        <v>12.85</v>
+        <v>15.125</v>
       </c>
       <c r="K17" s="8" t="n">
         <f aca="false">Plata!B37</f>
-        <v>2.30493273542601</v>
+        <v>2.5</v>
       </c>
       <c r="L17" s="9" t="n">
         <f aca="false">Plata!B38</f>
-        <v>1.30493273542601</v>
+        <v>1.5</v>
       </c>
       <c r="M17" s="9" t="n">
         <f aca="false">Plata!B39</f>
-        <v>0.269453053461715</v>
+        <v>0.58113883008419</v>
       </c>
       <c r="N17" s="8" t="n">
         <f aca="false">Plata!B40</f>
-        <v>0.717488789237668</v>
+        <v>0.661157024793388</v>
       </c>
       <c r="O17" s="8" t="n">
         <f aca="false">Plata!C40</f>
-        <v>4.66367713004484</v>
+        <v>4.29752066115703</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2700,22 +2700,22 @@
       </c>
       <c r="F18" s="6" t="n">
         <f aca="false">'Moonshot AI'!B10</f>
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G18" s="6" t="n">
         <f aca="false">'Moonshot AI'!B11</f>
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H18" s="6" t="n">
         <f aca="false">'Moonshot AI'!B12</f>
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>70</v>
       </c>
       <c r="J18" s="6" t="n">
         <f aca="false">'Moonshot AI'!B36</f>
-        <v>88</v>
+        <v>61.6</v>
       </c>
       <c r="K18" s="8" t="n">
         <f aca="false">'Moonshot AI'!B37</f>
@@ -2727,15 +2727,15 @@
       </c>
       <c r="M18" s="9" t="n">
         <f aca="false">'Moonshot AI'!B39</f>
-        <v>0.691538111622984</v>
+        <v>0.569170385885172</v>
       </c>
       <c r="N18" s="8" t="n">
         <f aca="false">'Moonshot AI'!B40</f>
-        <v>0.675</v>
+        <v>0.857142857142857</v>
       </c>
       <c r="O18" s="8" t="n">
         <f aca="false">'Moonshot AI'!C40</f>
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2758,42 +2758,42 @@
       </c>
       <c r="F19" s="6" t="n">
         <f aca="false">Higgsfield!B10</f>
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="G19" s="6" t="n">
         <f aca="false">Higgsfield!B11</f>
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H19" s="6" t="n">
         <f aca="false">Higgsfield!B12</f>
-        <v>6.025</v>
+        <v>5.75</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>74</v>
       </c>
       <c r="J19" s="6" t="n">
         <f aca="false">Higgsfield!B36</f>
-        <v>15.65</v>
+        <v>20.7</v>
       </c>
       <c r="K19" s="8" t="n">
         <f aca="false">Higgsfield!B37</f>
-        <v>2.59751037344398</v>
+        <v>3.6</v>
       </c>
       <c r="L19" s="9" t="n">
         <f aca="false">Higgsfield!B38</f>
-        <v>1.59751037344398</v>
+        <v>2.6</v>
       </c>
       <c r="M19" s="9" t="n">
         <f aca="false">Higgsfield!B39</f>
-        <v>0.464950385062174</v>
+        <v>0.441927988088433</v>
       </c>
       <c r="N19" s="8" t="n">
         <f aca="false">Higgsfield!B40</f>
-        <v>0.497925311203319</v>
+        <v>0.521739130434783</v>
       </c>
       <c r="O19" s="8" t="n">
         <f aca="false">Higgsfield!C40</f>
-        <v>7.46887966804979</v>
+        <v>9.56521739130435</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2816,42 +2816,42 @@
       </c>
       <c r="F20" s="6" t="n">
         <f aca="false">Lambda!B10</f>
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="G20" s="6" t="n">
         <f aca="false">Lambda!B11</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H20" s="6" t="n">
         <f aca="false">Lambda!B12</f>
-        <v>13.5</v>
+        <v>8.75</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>78</v>
       </c>
       <c r="J20" s="6" t="n">
         <f aca="false">Lambda!B36</f>
-        <v>37</v>
+        <v>18.375</v>
       </c>
       <c r="K20" s="8" t="n">
         <f aca="false">Lambda!B37</f>
-        <v>2.74074074074074</v>
+        <v>2.1</v>
       </c>
       <c r="L20" s="9" t="n">
         <f aca="false">Lambda!B38</f>
-        <v>1.74074074074074</v>
+        <v>1.1</v>
       </c>
       <c r="M20" s="9" t="n">
         <f aca="false">Lambda!B39</f>
-        <v>0.496742815701976</v>
+        <v>0.639882997800068</v>
       </c>
       <c r="N20" s="8" t="n">
         <f aca="false">Lambda!B40</f>
-        <v>0.666666666666667</v>
+        <v>0.685714285714286</v>
       </c>
       <c r="O20" s="8" t="n">
         <f aca="false">Lambda!C40</f>
-        <v>6.66666666666667</v>
+        <v>10.2857142857143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5264,7 +5264,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5272,7 +5272,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>140.5</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5396,32 +5396,32 @@
         <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="26" t="n">
         <v>25</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.889679715302491</v>
+        <v>0.983606557377049</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.110320284697509</v>
+        <v>-0.0163934426229508</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.0456812087220062</v>
+        <v>-0.00823059263907056</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5429,32 +5429,32 @@
         <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>280</v>
+        <v>420</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>1.99288256227758</v>
+        <v>2.75409836065574</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>0.99288256227758</v>
+        <v>1.75409836065574</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.217772610845543</v>
+        <v>0.401715305792211</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5468,26 +5468,26 @@
         <v>4.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>22</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>660</v>
+        <v>770</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>4.69750889679715</v>
+        <v>5.04918032786885</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>3.69750889679715</v>
+        <v>4.04918032786885</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.410275345515255</v>
+        <v>0.433082877242528</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5539,28 +5539,28 @@
         <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>310</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>1.06761565836299</v>
+        <v>1.04918032786885</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>0.0676156583629892</v>
+        <v>0.0491803278688525</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>0.0265165931495233</v>
+        <v>0.0242950394631678</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5568,28 +5568,28 @@
         <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>311</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>340</v>
+        <v>495</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.41992882562278</v>
+        <v>3.24590163934426</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.41992882562278</v>
+        <v>2.24590163934426</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.287235130153444</v>
+        <v>0.480625137564128</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5606,19 +5606,19 @@
         <v>312</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>4.98220640569395</v>
+        <v>5.57377049180328</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>3.98220640569395</v>
+        <v>4.57377049180328</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.428836722581161</v>
+        <v>0.464909876729523</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>310</v>
+        <v>457.5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.20640569395018</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.20640569395018</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.253706333606649</v>
+        <v>0.442249570307408</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.889679715302491</v>
+        <v>0.983606557377049</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>4.98220640569395</v>
+        <v>5.57377049180328</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.13793103448276</v>
+        <v>2.95161290322581</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5854,7 +5854,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5862,7 +5862,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>5.575</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5986,10 +5986,10 @@
         <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D25" s="25" t="n">
         <v>1</v>
@@ -6003,15 +6003,15 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.717488789237668</v>
+        <v>0.661157024793388</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.282511210762332</v>
+        <v>-0.338842975206612</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.124359081517876</v>
+        <v>-0.241067628209734</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6019,32 +6019,32 @@
         <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.00896860986547</v>
+        <v>1.98347107438017</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.00896860986547</v>
+        <v>0.983471074380165</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.220572996095137</v>
+        <v>0.408357580439061</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6052,10 +6052,10 @@
         <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="25" t="n">
         <v>2.6</v>
@@ -6069,15 +6069,15 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>4.19730941704036</v>
+        <v>3.86776859504132</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>3.19730941704036</v>
+        <v>2.86776859504132</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.375428429644104</v>
+        <v>0.471790014936723</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6129,10 +6129,10 @@
         <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>331</v>
@@ -6142,15 +6142,15 @@
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.896860986547085</v>
+        <v>0.826446280991735</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.103139013452915</v>
+        <v>-0.173553719008265</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.0426074293387878</v>
+        <v>-0.11933699440776</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6158,28 +6158,28 @@
         <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>332</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>14.5</v>
+        <v>18.25</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.60089686098655</v>
+        <v>3.01652892561983</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.60089686098655</v>
+        <v>2.01652892561983</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.314034018722216</v>
+        <v>0.736815743140254</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6187,10 +6187,10 @@
         <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>333</v>
@@ -6200,15 +6200,15 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>4.66367713004484</v>
+        <v>4.29752066115703</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>3.66367713004484</v>
+        <v>3.29752066115702</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.408011908871801</v>
+        <v>0.516768919857198</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>12.85</v>
+        <v>15.125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.30493273542601</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.30493273542601</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.269453053461715</v>
+        <v>0.58113883008419</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6266,11 +6266,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.717488789237668</v>
+        <v>0.661157024793388</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>4.66367713004484</v>
+        <v>4.29752066115703</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.23478260869565</v>
+        <v>2.43951612903226</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6444,7 +6444,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6452,7 +6452,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6607,23 +6607,23 @@
         <v>0.6</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.675</v>
+        <v>0.857142857142857</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.325</v>
+        <v>-0.142857142857143</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.325</v>
+        <v>-0.142857142857143</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6631,32 +6631,32 @@
         <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="D26" s="25" t="n">
         <v>1.2</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.1</v>
+        <v>2.35714285714286</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.1</v>
+        <v>1.35714285714286</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.639882997800068</v>
+        <v>0.632269799268895</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6664,7 +6664,7 @@
         <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>2.5</v>
@@ -6681,15 +6681,15 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>5</v>
+        <v>7.14285714285714</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>4</v>
+        <v>6.14285714285714</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.903653938715879</v>
+        <v>1.19557757174337</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6750,19 +6750,19 @@
         <v>354</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.75</v>
+        <v>0.928571428571429</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.25</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.25</v>
+        <v>-0.0714285714285714</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6770,28 +6770,28 @@
         <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>355</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>92</v>
+        <v>57.2</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.3</v>
+        <v>2.04285714285714</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.3</v>
+        <v>1.04285714285714</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.742416161578685</v>
+        <v>0.504107426853512</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6799,7 +6799,7 @@
         <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>2.5</v>
@@ -6812,15 +6812,15 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.941170672751477</v>
+        <v>1.23884746347022</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>88</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.691538111622984</v>
+        <v>0.569170385885172</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6878,11 +6878,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.675</v>
+        <v>0.857142857142857</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.0952380952381</v>
+        <v>2.05333333333333</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7061,7 +7061,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7069,7 +7069,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>6.025</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7232,15 +7232,15 @@
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.497925311203319</v>
+        <v>0.521739130434783</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.502074688796681</v>
+        <v>-0.478260869565217</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.371783311809605</v>
+        <v>-0.351909572719927</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7248,32 +7248,32 @@
         <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>15</v>
+        <v>19.8</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.4896265560166</v>
+        <v>3.44347826086957</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.4896265560166</v>
+        <v>2.44347826086957</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.440302395893987</v>
+        <v>0.423730579232139</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7281,32 +7281,32 @@
         <v>134</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="C27" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>25</v>
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>6.63900414937759</v>
+        <v>8.69565217391304</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>5.63900414937759</v>
+        <v>7.69565217391304</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.717459696556446</v>
+        <v>0.617088591727101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7371,15 +7371,15 @@
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.580912863070539</v>
+        <v>0.608695652173913</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.419087136929461</v>
+        <v>-0.391304347826087</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.303789350599289</v>
+        <v>-0.281764611273275</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7387,28 +7387,28 @@
         <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>379</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>16.3</v>
+        <v>21.6</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.70539419087137</v>
+        <v>3.75652173913044</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.70539419087137</v>
+        <v>2.75652173913044</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.488991509258602</v>
+        <v>0.459568710827752</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7416,28 +7416,28 @@
         <v>134</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>380</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>7.46887966804979</v>
+        <v>9.56521739130435</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>6.46887966804979</v>
+        <v>8.56521739130435</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.776239651542579</v>
+        <v>0.651703875249193</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>15.65</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.59751037344398</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.59751037344398</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.464950385062174</v>
+        <v>0.441927988088433</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7495,11 +7495,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.497925311203319</v>
+        <v>0.521739130434783</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>7.46887966804979</v>
+        <v>9.56521739130435</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.5241935483871</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7673,7 +7673,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,7 +7681,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">AVERAGE(B10:B11)</f>
-        <v>13.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7816,32 +7816,32 @@
         <v>131</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C25" s="24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="26" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="27" t="n">
         <f aca="false">D25*E25</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G25" s="28" t="n">
         <f aca="false">F25/B12</f>
-        <v>0.666666666666667</v>
+        <v>0.685714285714286</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">G25-1</f>
-        <v>-0.333333333333333</v>
+        <v>-0.314285714285714</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">G25^(1/C25)-1</f>
-        <v>-0.236857171631112</v>
+        <v>-0.314285714285714</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,32 +7849,32 @@
         <v>133</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="E26" s="26" t="n">
         <v>5</v>
       </c>
       <c r="F26" s="27" t="n">
         <f aca="false">D26*E26</f>
-        <v>35</v>
+        <v>17.5</v>
       </c>
       <c r="G26" s="28" t="n">
         <f aca="false">F26/B12</f>
-        <v>2.59259259259259</v>
+        <v>2</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">G26-1</f>
-        <v>1.59259259259259</v>
+        <v>1</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">G26^(1/C26)-1</f>
-        <v>0.463840337369668</v>
+        <v>0.587401051968199</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7899,15 +7899,15 @@
       </c>
       <c r="G27" s="28" t="n">
         <f aca="false">F27/B12</f>
-        <v>5.77777777777778</v>
+        <v>8.91428571428572</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">G27-1</f>
-        <v>4.77777777777778</v>
+        <v>7.91428571428572</v>
       </c>
       <c r="I27" s="29" t="n">
         <f aca="false">G27^(1/C27)-1</f>
-        <v>0.650615627779178</v>
+        <v>0.86832876330165</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7959,28 +7959,28 @@
         <v>131</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>400</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">E32/B12</f>
-        <v>0.814814814814815</v>
+        <v>0.8</v>
       </c>
       <c r="G32" s="29" t="n">
         <f aca="false">F32-1</f>
-        <v>-0.185185185185185</v>
+        <v>-0.2</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">F32^(1/C32)-1</f>
-        <v>-0.127619509940034</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7988,28 +7988,28 @@
         <v>133</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C33" s="24" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>401</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>39</v>
+        <v>19.25</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">E33/B12</f>
-        <v>2.88888888888889</v>
+        <v>2.2</v>
       </c>
       <c r="G33" s="29" t="n">
         <f aca="false">F33-1</f>
-        <v>1.88888888888889</v>
+        <v>1.2</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">F33^(1/C33)-1</f>
-        <v>0.528594650593345</v>
+        <v>0.691538111622984</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8030,15 +8030,15 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">E34/B12</f>
-        <v>6.66666666666667</v>
+        <v>10.2857142857143</v>
       </c>
       <c r="G34" s="29" t="n">
         <f aca="false">F34-1</f>
-        <v>5.66666666666667</v>
+        <v>9.28571428571429</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">F34^(1/C34)-1</f>
-        <v>0.719501256105151</v>
+        <v>0.946300278058653</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="B36" s="17" t="n">
         <f aca="false">AVERAGE(F26,E33)</f>
-        <v>37</v>
+        <v>18.375</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">B36/B12</f>
-        <v>2.74074074074074</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="B38" s="31" t="n">
         <f aca="false">B37-1</f>
-        <v>1.74074074074074</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="B39" s="31" t="n">
         <f aca="false">B37^(1/C26)-1</f>
-        <v>0.496742815701976</v>
+        <v>0.639882997800068</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8096,11 +8096,11 @@
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">MIN(G25,F32)</f>
-        <v>0.666666666666667</v>
+        <v>0.685714285714286</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">MAX(G27,F34)</f>
-        <v>6.66666666666667</v>
+        <v>10.2857142857143</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="B41" s="30" t="n">
         <f aca="false">B36/B11</f>
-        <v>2.46666666666667</v>
+        <v>2.04166666666667</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="421">
   <si>
     <t xml:space="preserve">Veligera Capital — pipeline сделок: расчёт доходности</t>
   </si>
@@ -1029,7 +1029,7 @@
     <t xml:space="preserve">P/S — нижняя граница для необанка Латинской Америки</t>
   </si>
   <si>
-    <t xml:space="preserve">Аннуализированная выручка около $600 млн на кредитном портфеле $800 млн (данные компании, публично не аудированы). Базовый сценарий: рост выручки в 2.7 раза к 2030 году и выход в прибыль, мультипликатор ниже Nubank из-за одного рынка и меньшего масштаба.</t>
+    <t xml:space="preserve">По презентации компании (метрики на сентябрь 2025): годовая выручка ARR $504 млн, валовый кредитный портфель $660 млн, 2.6 млн активных клиентов при доле активных около 90%, рост выручки +233% и портфеля +241% г/г. Юнит-экономика: CAC $3.5, LTV $243, чистая прибыль на клиента после OPEX и фондирования $70, чистая маржа 45%. Данные компании, публично не аудированы. Базовый сценарий: рост выручки примерно втрое к 2028 году и выход в прибыль, мультипликатор ниже Nubank из-за одного рынка и меньшего масштаба.</t>
   </si>
   <si>
     <t xml:space="preserve">Рост просрочки обгоняет портфель, оценка сжимается к мультипликатору Inter&amp;Co</t>
@@ -1041,7 +1041,22 @@
     <t xml:space="preserve">Доля рынка карт Мексики уровня Nubank в Бразилии при мультипликаторе 8x</t>
   </si>
   <si>
-    <t xml:space="preserve">• Series C $405 млн @ $5.0 млрд post-money, анонс 16.04.2026, лид Bicycle Capital</t>
+    <t xml:space="preserve">• Series C $405 млн @ $5.0 млрд post-money, анонс 16.04.2026, лид Bicycle Capital. РАСХОЖДЕНИЕ С ПРЕЗЕНТАЦИЕЙ КОМПАНИИ: в ней Series C датирована февралём 2026, объём $200–300 млн, оценка $5 млрд указана как PRE-money. Перед сделкой уточнить окончательные параметры раунда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Раунды по презентации: Seed $272 млн @ $317 млн (Baring Ventures, июль 2022), Seed follow-on $8 млн @ $708 млн (август 2024), Series A $190 млн @ $1 489 млн (Kora, март 2025), Series B $93 млн @ $3 093 млн (Kora, октябрь 2025). Всего привлечено $563 млн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Сравнение с Nubank Mexico на сопоставимом этапе (презентация): 3-й год работы — 2.8 млн активных клиентов против 1.4 млн; доход на клиента $231 против $107; чистая процентная маржа 20% против 3%; кредитный портфель $4.7 млрд против $0.9 млрд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Рынок по презентации: TAM $176 млрд, SAM 2030 $150 млрд, текущий доступный рынок $36 млрд; 63% взрослого населения не имеет доступа к кредитным продуктам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ВНИМАНИЕ по презентации: стоимость риска по IFRS 30.2% LTM и стоимость фондирования 22.3% LTM. Прогноз компании на 2030 год — снижение до 17.1% и 6.8% соответственно; это ключевое допущение всей модели роста</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Команда: Нери Толлардо (CEO, ранее директор по стратегии Тинькофф банка, Morgan Stanley), Даниил Анисимов (CBO, ранее розничный банкинг Тинькофф), Андрей Шелехин (CTO, ранее IT-департамент Тинькофф), Надежда Шульга (CRO, Сбер, OTP, Citi)</t>
   </si>
   <si>
     <t xml:space="preserve">• Траектория оценки: $1.5 млрд (03.2025) → $3.1 млрд (10.2025) → $5.0 млрд (04.2026) — рост в 3.3 раза за 13 месяцев</t>
@@ -1218,7 +1233,7 @@
     <t xml:space="preserve">CoreWeave</t>
   </si>
   <si>
-    <t xml:space="preserve">EV/Sales 2026E — главный аналог, выручка Q2'26 $2.58 млрд (+112%)</t>
+    <t xml:space="preserve">EV/Revenue — главный публичный аналог</t>
   </si>
   <si>
     <t xml:space="preserve">CoreWeave по бэклогу</t>
@@ -1236,7 +1251,7 @@
     <t xml:space="preserve">Together AI</t>
   </si>
   <si>
-    <t xml:space="preserve">Выручка: $425 млн (2024) → run-rate $760 млн (конец 2025) → более $1.5 млрд ожидается по итогам 2026. Базовый сценарий строится на разгоне контракта с Anthropic: $35 млрд за шесть лет дают в среднем около $5.8 млрд выручки в год после ввода площадки, плюс действующая база и контракт с Microsoft. Мультипликатор 5x — с дисконтом к CoreWeave (6–8x на 2026E) за меньший масштаб и более высокую концентрацию клиентов.</t>
+    <t xml:space="preserve">Выручка: ~$250 млн (2023) → $425 млн (2024) → ~$760 млн (2025) → более $1.5 млрд ожидается по итогам 2026. Вход по середине диапазона соответствует примерно 5.7x прогнозной выручки 2026 года против 9.2x у публичного CoreWeave; идущий раунд от $12 млрд — это около 8x. Базовый сценарий строится на разгоне контракта с Anthropic: $35 млрд за шесть лет дают в среднем около $5.8 млрд выручки в год после ввода площадки, плюс действующая база и контракт с Microsoft. Мультипликатор 5x — с дисконтом к CoreWeave (6–8x на 2026E) за меньший масштаб и более высокую концентрацию клиентов.</t>
   </si>
   <si>
     <t xml:space="preserve">Сдвиг ввода мощностей Beacon Point и продолжение сжатия мультипликаторов сектора</t>
@@ -5776,7 +5791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -6347,6 +6362,31 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6469,7 +6509,7 @@
         <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6498,13 +6538,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6515,40 +6555,40 @@
         <v>21</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>1.9</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6694,7 +6734,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6747,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>26</v>
@@ -6776,7 +6816,7 @@
         <v>1.75</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>57.2</v>
@@ -6805,7 +6845,7 @@
         <v>2.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>210</v>
@@ -6909,57 +6949,57 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7086,7 +7126,7 @@
         <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7115,57 +7155,57 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>40</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>33</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>26.7</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>17.7</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>7.7</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7311,7 +7351,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7364,7 +7404,7 @@
         <v>1.5</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>3.5</v>
@@ -7393,7 +7433,7 @@
         <v>3.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>21.6</v>
@@ -7422,7 +7462,7 @@
         <v>4.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>55</v>
@@ -7526,52 +7566,52 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7698,7 +7738,7 @@
         <v>108</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7727,46 +7767,46 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>7</v>
+        <v>9.2</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>0.74</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>8.5</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>8.3</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7912,7 +7952,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7965,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>7</v>
@@ -7994,7 +8034,7 @@
         <v>1.5</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>19.25</v>
@@ -8023,7 +8063,7 @@
         <v>3.5</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>90</v>
@@ -8127,67 +8167,67 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
+++ b/investment-pipeline/Veligera_Pipeline_Upside_Model.xlsx
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Waymo</t>
   </si>
   <si>
-    <t xml:space="preserve">Беспилотное такси</t>
+    <t xml:space="preserve">Беспилотное такси (Alphabet / Google)</t>
   </si>
   <si>
     <t xml:space="preserve">Раунд $16 млрд, объявлен 02.02.2026; лиды Dragoneer, DST Global, Sequoia; Alphabet вложила ~$13 млрд</t>
